--- a/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
+++ b/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Thing" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="133">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -220,10 +220,10 @@
     <t xml:space="preserve"> -</t>
   </si>
   <si>
-    <t xml:space="preserve">paper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EvolutionHeart</t>
+    <t xml:space="preserve">meat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency</t>
   </si>
   <si>
     <t xml:space="preserve">noWish,noShop,noDrop</t>
@@ -340,35 +340,16 @@
     <t xml:space="preserve">testchara_evo_stage1</t>
   </si>
   <si>
-    <t xml:space="preserve">Bob</t>
+    <t xml:space="preserve">Tester1</t>
   </si>
   <si>
     <t xml:space="preserve">@chara</t>
   </si>
   <si>
-    <t xml:space="preserve">meat</t>
-  </si>
-  <si>
     <t xml:space="preserve">Friend</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">evolve#</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">testchara_evo_stage2#evolution_heart_a</t>
-    </r>
+    <t xml:space="preserve">evolve#testchara_evo_stage2#evolution_heart_a</t>
   </si>
   <si>
     <t xml:space="preserve">UniqueChara</t>
@@ -389,32 +370,16 @@
     <t xml:space="preserve">testchara_evo_stage2</t>
   </si>
   <si>
-    <t xml:space="preserve">Bobber</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">evolve#</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">testchara_evo_stage3#evolution_heart_b</t>
-    </r>
+    <t xml:space="preserve">Tester2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evolve#testchara_evo_stage3#evolution_heart_b</t>
   </si>
   <si>
     <t xml:space="preserve">testchara_evo_stage3</t>
   </si>
   <si>
-    <t xml:space="preserve">Bobbest</t>
+    <t xml:space="preserve">Tester3</t>
   </si>
   <si>
     <t xml:space="preserve">group</t>
@@ -468,7 +433,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -519,6 +484,11 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FFC9A26D"/>
       <name val="JetBrains Mono"/>
@@ -544,11 +514,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -603,11 +568,6 @@
       <name val="Liberation Mono;Courier New;DejaVu Sans Mono;Lucida Sans Typewriter"/>
       <family val="3"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Liberation Mono;Courier New;DejaVu Sans Mono;Lucida Sans Typewriter"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -677,7 +637,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -714,6 +674,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -730,10 +694,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -742,11 +702,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -766,7 +730,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -790,7 +754,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -798,7 +762,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -806,7 +770,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -818,7 +782,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1022,7 +986,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="14.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="1" width="28.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="0" width="46.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="1" width="46.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1444,11 +1408,11 @@
       <c r="U4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Y4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="10" t="n">
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="11" t="n">
         <v>250000</v>
       </c>
       <c r="AB4" s="1" t="n">
@@ -1467,7 +1431,7 @@
       <c r="AG4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" s="1" t="s">
+      <c r="AH4" s="9" t="s">
         <v>66</v>
       </c>
       <c r="AJ4" s="1" t="n">
@@ -1482,7 +1446,7 @@
       </c>
       <c r="AW4" s="1"/>
       <c r="AX4" s="1"/>
-      <c r="AZ4" s="11" t="s">
+      <c r="AZ4" s="12" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1511,11 +1475,11 @@
       <c r="U5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="Y5" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="10" t="n">
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="11" t="n">
         <v>250000</v>
       </c>
       <c r="AB5" s="1" t="n">
@@ -1534,7 +1498,7 @@
       <c r="AG5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="1" t="s">
+      <c r="AH5" s="9" t="s">
         <v>66</v>
       </c>
       <c r="AJ5" s="1" t="n">
@@ -1549,7 +1513,7 @@
       </c>
       <c r="AW5" s="1"/>
       <c r="AX5" s="1"/>
-      <c r="AZ5" s="11" t="s">
+      <c r="AZ5" s="12" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1578,11 +1542,11 @@
       <c r="U6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Y6" s="1" t="s">
+      <c r="Y6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="10" t="n">
+      <c r="Z6" s="10"/>
+      <c r="AA6" s="11" t="n">
         <v>250000</v>
       </c>
       <c r="AB6" s="1" t="n">
@@ -1601,7 +1565,7 @@
       <c r="AG6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH6" s="1" t="s">
+      <c r="AH6" s="9" t="s">
         <v>66</v>
       </c>
       <c r="AJ6" s="1" t="n">
@@ -1616,21 +1580,21 @@
       </c>
       <c r="AW6" s="1"/>
       <c r="AX6" s="1"/>
-      <c r="AZ6" s="11" t="s">
+      <c r="AZ6" s="12" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="I7" s="9"/>
+      <c r="I7" s="10"/>
       <c r="K7" s="1"/>
       <c r="M7" s="7"/>
       <c r="S7" s="8"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="11"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
@@ -1643,18 +1607,17 @@
       <c r="AV7" s="1"/>
       <c r="AW7" s="1"/>
       <c r="AX7" s="1"/>
-      <c r="AZ7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="12"/>
+      <c r="I8" s="13"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="12"/>
+      <c r="L8" s="13"/>
       <c r="M8" s="1"/>
       <c r="S8" s="8"/>
       <c r="U8" s="1"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="Y8" s="12"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="Y8" s="13"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
@@ -1664,10 +1627,9 @@
       <c r="AG8" s="1"/>
       <c r="AJ8" s="1"/>
       <c r="AT8" s="8"/>
-      <c r="AZ8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13"/>
+      <c r="A9" s="14"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="I9" s="1"/>
@@ -1676,13 +1638,13 @@
       <c r="S9" s="8"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
-      <c r="W9" s="12"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="9"/>
+      <c r="W9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="10"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="12"/>
+      <c r="AB9" s="13"/>
       <c r="AC9" s="1"/>
-      <c r="AD9" s="13"/>
+      <c r="AD9" s="14"/>
       <c r="AE9" s="8"/>
       <c r="AF9" s="1"/>
       <c r="AJ9" s="1"/>
@@ -1690,10 +1652,9 @@
       <c r="AV9" s="1"/>
       <c r="AW9" s="1"/>
       <c r="AX9" s="1"/>
-      <c r="AZ9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13"/>
+      <c r="A10" s="14"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="I10" s="1"/>
@@ -1702,13 +1663,13 @@
       <c r="S10" s="8"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
-      <c r="W10" s="12"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="9"/>
+      <c r="W10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="10"/>
       <c r="AA10" s="1"/>
-      <c r="AB10" s="12"/>
+      <c r="AB10" s="13"/>
       <c r="AC10" s="1"/>
-      <c r="AD10" s="13"/>
+      <c r="AD10" s="14"/>
       <c r="AE10" s="8"/>
       <c r="AF10" s="1"/>
       <c r="AJ10" s="1"/>
@@ -1716,10 +1677,9 @@
       <c r="AV10" s="1"/>
       <c r="AW10" s="1"/>
       <c r="AX10" s="1"/>
-      <c r="AZ10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13"/>
+      <c r="A11" s="14"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="I11" s="1"/>
@@ -1728,13 +1688,13 @@
       <c r="S11" s="8"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
-      <c r="W11" s="12"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="9"/>
+      <c r="W11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="10"/>
       <c r="AA11" s="1"/>
-      <c r="AB11" s="12"/>
+      <c r="AB11" s="13"/>
       <c r="AC11" s="1"/>
-      <c r="AD11" s="13"/>
+      <c r="AD11" s="14"/>
       <c r="AE11" s="8"/>
       <c r="AF11" s="1"/>
       <c r="AJ11" s="1"/>
@@ -1742,10 +1702,10 @@
       <c r="AV11" s="1"/>
       <c r="AW11" s="1"/>
       <c r="AX11" s="1"/>
-      <c r="AZ11" s="9"/>
+      <c r="AZ11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="I12" s="1"/>
@@ -1754,13 +1714,13 @@
       <c r="S12" s="8"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-      <c r="W12" s="12"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="9"/>
+      <c r="W12" s="13"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="10"/>
       <c r="AA12" s="1"/>
-      <c r="AB12" s="12"/>
+      <c r="AB12" s="13"/>
       <c r="AC12" s="1"/>
-      <c r="AD12" s="13"/>
+      <c r="AD12" s="14"/>
       <c r="AE12" s="8"/>
       <c r="AF12" s="1"/>
       <c r="AJ12" s="1"/>
@@ -1768,10 +1728,9 @@
       <c r="AV12" s="1"/>
       <c r="AW12" s="1"/>
       <c r="AX12" s="1"/>
-      <c r="AZ12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="I13" s="1"/>
@@ -1780,13 +1739,13 @@
       <c r="S13" s="8"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
-      <c r="W13" s="12"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="9"/>
+      <c r="W13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="10"/>
       <c r="AA13" s="1"/>
-      <c r="AB13" s="12"/>
+      <c r="AB13" s="13"/>
       <c r="AC13" s="1"/>
-      <c r="AD13" s="13"/>
+      <c r="AD13" s="14"/>
       <c r="AE13" s="8"/>
       <c r="AF13" s="1"/>
       <c r="AJ13" s="1"/>
@@ -1794,10 +1753,9 @@
       <c r="AV13" s="1"/>
       <c r="AW13" s="1"/>
       <c r="AX13" s="1"/>
-      <c r="AZ13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13"/>
+      <c r="A14" s="14"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="I14" s="1"/>
@@ -1806,13 +1764,13 @@
       <c r="S14" s="8"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
-      <c r="W14" s="12"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="9"/>
+      <c r="W14" s="13"/>
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="10"/>
       <c r="AA14" s="1"/>
-      <c r="AB14" s="12"/>
+      <c r="AB14" s="13"/>
       <c r="AC14" s="1"/>
-      <c r="AD14" s="13"/>
+      <c r="AD14" s="14"/>
       <c r="AE14" s="8"/>
       <c r="AF14" s="1"/>
       <c r="AJ14" s="1"/>
@@ -1820,7 +1778,6 @@
       <c r="AV14" s="1"/>
       <c r="AW14" s="1"/>
       <c r="AX14" s="1"/>
-      <c r="AZ14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1"/>
@@ -1831,7 +1788,7 @@
       <c r="S15" s="8"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
-      <c r="V15" s="12"/>
+      <c r="V15" s="13"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
@@ -1844,50 +1801,48 @@
       <c r="AV15" s="1"/>
       <c r="AW15" s="1"/>
       <c r="AX15" s="1"/>
-      <c r="AZ15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13"/>
+      <c r="A16" s="14"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="I16" s="12"/>
+      <c r="I16" s="13"/>
       <c r="K16" s="1"/>
       <c r="M16" s="7"/>
       <c r="S16" s="8"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="Y16" s="12"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="13"/>
+      <c r="Y16" s="13"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
       <c r="AF16" s="1"/>
-      <c r="AH16" s="12"/>
-      <c r="AI16" s="13"/>
+      <c r="AH16" s="13"/>
+      <c r="AI16" s="14"/>
       <c r="AJ16" s="1"/>
       <c r="AP16" s="1"/>
       <c r="AT16" s="8"/>
       <c r="AV16" s="1"/>
       <c r="AW16" s="1"/>
       <c r="AX16" s="1"/>
-      <c r="AY16" s="13"/>
-      <c r="AZ16" s="1"/>
+      <c r="AY16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="15"/>
+      <c r="D17" s="15"/>
       <c r="E17" s="1"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="13"/>
       <c r="K17" s="1"/>
       <c r="M17" s="7"/>
       <c r="N17" s="1"/>
       <c r="S17" s="8"/>
       <c r="U17" s="1"/>
-      <c r="V17" s="12"/>
+      <c r="V17" s="13"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
@@ -1895,29 +1850,28 @@
       <c r="AD17" s="1"/>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1"/>
-      <c r="AI17" s="13"/>
+      <c r="AI17" s="14"/>
       <c r="AJ17" s="1"/>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
       <c r="AT17" s="8"/>
-      <c r="AY17" s="13"/>
-      <c r="AZ17" s="1"/>
+      <c r="AY17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="14"/>
+      <c r="D18" s="15"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="13"/>
       <c r="K18" s="1"/>
       <c r="M18" s="7"/>
       <c r="N18" s="1"/>
       <c r="S18" s="8"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
-      <c r="V18" s="12"/>
-      <c r="Y18" s="12"/>
+      <c r="V18" s="13"/>
+      <c r="Y18" s="13"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
@@ -1925,202 +1879,192 @@
       <c r="AD18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
-      <c r="AI18" s="13"/>
+      <c r="AI18" s="14"/>
       <c r="AJ18" s="1"/>
       <c r="AT18" s="8"/>
       <c r="AV18" s="1"/>
-      <c r="AY18" s="13"/>
-      <c r="AZ18" s="1"/>
+      <c r="AY18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="I19" s="12"/>
+      <c r="I19" s="13"/>
       <c r="K19" s="1"/>
       <c r="M19" s="7"/>
       <c r="S19" s="8"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
-      <c r="V19" s="12"/>
+      <c r="V19" s="13"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
       <c r="AF19" s="1"/>
-      <c r="AI19" s="13"/>
+      <c r="AI19" s="14"/>
       <c r="AJ19" s="1"/>
       <c r="AP19" s="1"/>
       <c r="AT19" s="8"/>
       <c r="AV19" s="1"/>
       <c r="AW19" s="1"/>
       <c r="AX19" s="1"/>
-      <c r="AY19" s="13"/>
-      <c r="AZ19" s="1"/>
+      <c r="AY19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13"/>
-      <c r="I20" s="12"/>
+      <c r="A20" s="14"/>
+      <c r="I20" s="13"/>
       <c r="K20" s="1"/>
       <c r="M20" s="7"/>
       <c r="S20" s="8"/>
       <c r="U20" s="1"/>
-      <c r="V20" s="12"/>
-      <c r="Y20" s="12"/>
+      <c r="V20" s="13"/>
+      <c r="Y20" s="13"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
       <c r="AF20" s="1"/>
-      <c r="AI20" s="13"/>
+      <c r="AI20" s="14"/>
       <c r="AT20" s="8"/>
-      <c r="AY20" s="13"/>
-      <c r="AZ20" s="1"/>
+      <c r="AY20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13"/>
-      <c r="I21" s="12"/>
+      <c r="A21" s="14"/>
+      <c r="I21" s="13"/>
       <c r="K21" s="1"/>
       <c r="M21" s="7"/>
       <c r="S21" s="8"/>
       <c r="U21" s="1"/>
-      <c r="V21" s="12"/>
+      <c r="V21" s="13"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
       <c r="AF21" s="1"/>
-      <c r="AI21" s="13"/>
+      <c r="AI21" s="14"/>
       <c r="AT21" s="8"/>
-      <c r="AY21" s="13"/>
-      <c r="AZ21" s="1"/>
+      <c r="AY21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="I22" s="12"/>
+      <c r="A22" s="14"/>
+      <c r="I22" s="13"/>
       <c r="K22" s="1"/>
       <c r="M22" s="7"/>
       <c r="S22" s="8"/>
       <c r="U22" s="1"/>
-      <c r="V22" s="12"/>
-      <c r="Y22" s="12"/>
+      <c r="V22" s="13"/>
+      <c r="Y22" s="13"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
       <c r="AF22" s="1"/>
-      <c r="AI22" s="13"/>
+      <c r="AI22" s="14"/>
       <c r="AT22" s="8"/>
-      <c r="AY22" s="13"/>
-      <c r="AZ22" s="1"/>
+      <c r="AY22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="I23" s="12"/>
+      <c r="A23" s="14"/>
+      <c r="I23" s="13"/>
       <c r="K23" s="1"/>
       <c r="M23" s="7"/>
       <c r="S23" s="8"/>
       <c r="U23" s="1"/>
-      <c r="V23" s="12"/>
+      <c r="V23" s="13"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
       <c r="AF23" s="1"/>
-      <c r="AI23" s="13"/>
+      <c r="AI23" s="14"/>
       <c r="AT23" s="8"/>
-      <c r="AY23" s="13"/>
-      <c r="AZ23" s="1"/>
+      <c r="AY23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="I24" s="12"/>
+      <c r="A24" s="14"/>
+      <c r="I24" s="13"/>
       <c r="K24" s="1"/>
       <c r="M24" s="7"/>
       <c r="S24" s="8"/>
       <c r="U24" s="1"/>
-      <c r="V24" s="12"/>
+      <c r="V24" s="13"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
       <c r="AF24" s="1"/>
-      <c r="AI24" s="13"/>
+      <c r="AI24" s="14"/>
       <c r="AT24" s="8"/>
-      <c r="AY24" s="13"/>
-      <c r="AZ24" s="1"/>
+      <c r="AY24" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
-      <c r="I25" s="12"/>
+      <c r="A25" s="14"/>
+      <c r="I25" s="13"/>
       <c r="K25" s="1"/>
       <c r="M25" s="7"/>
       <c r="S25" s="8"/>
       <c r="U25" s="1"/>
-      <c r="V25" s="12"/>
+      <c r="V25" s="13"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
       <c r="AF25" s="1"/>
-      <c r="AI25" s="13"/>
+      <c r="AI25" s="14"/>
       <c r="AT25" s="8"/>
-      <c r="AY25" s="13"/>
-      <c r="AZ25" s="1"/>
+      <c r="AY25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13"/>
-      <c r="I26" s="12"/>
+      <c r="A26" s="14"/>
+      <c r="I26" s="13"/>
       <c r="K26" s="1"/>
       <c r="M26" s="7"/>
       <c r="S26" s="8"/>
       <c r="U26" s="1"/>
-      <c r="V26" s="12"/>
+      <c r="V26" s="13"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
       <c r="AF26" s="1"/>
-      <c r="AI26" s="13"/>
+      <c r="AI26" s="14"/>
       <c r="AT26" s="8"/>
-      <c r="AY26" s="13"/>
-      <c r="AZ26" s="1"/>
+      <c r="AY26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="I27" s="12"/>
+      <c r="A27" s="14"/>
+      <c r="I27" s="13"/>
       <c r="K27" s="1"/>
       <c r="M27" s="7"/>
       <c r="S27" s="8"/>
       <c r="U27" s="1"/>
-      <c r="V27" s="12"/>
+      <c r="V27" s="13"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
       <c r="AF27" s="1"/>
-      <c r="AI27" s="13"/>
+      <c r="AI27" s="14"/>
       <c r="AT27" s="8"/>
-      <c r="AY27" s="13"/>
-      <c r="AZ27" s="1"/>
+      <c r="AY27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="12"/>
+      <c r="I28" s="13"/>
       <c r="K28" s="1"/>
       <c r="M28" s="7"/>
       <c r="S28" s="8"/>
       <c r="U28" s="1"/>
-      <c r="V28" s="12"/>
-      <c r="Y28" s="12"/>
+      <c r="V28" s="13"/>
+      <c r="Y28" s="13"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
@@ -2128,16 +2072,15 @@
       <c r="AD28" s="1"/>
       <c r="AF28" s="1"/>
       <c r="AT28" s="8"/>
-      <c r="AZ28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I29" s="12"/>
+      <c r="I29" s="13"/>
       <c r="K29" s="1"/>
       <c r="M29" s="7"/>
       <c r="S29" s="8"/>
       <c r="U29" s="1"/>
-      <c r="V29" s="12"/>
-      <c r="Y29" s="12"/>
+      <c r="V29" s="13"/>
+      <c r="Y29" s="13"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
@@ -2145,16 +2088,15 @@
       <c r="AD29" s="1"/>
       <c r="AF29" s="1"/>
       <c r="AT29" s="8"/>
-      <c r="AZ29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I30" s="12"/>
+      <c r="I30" s="13"/>
       <c r="K30" s="1"/>
       <c r="M30" s="7"/>
       <c r="S30" s="8"/>
       <c r="U30" s="1"/>
-      <c r="V30" s="12"/>
-      <c r="Y30" s="12"/>
+      <c r="V30" s="13"/>
+      <c r="Y30" s="13"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
@@ -2162,16 +2104,15 @@
       <c r="AD30" s="1"/>
       <c r="AF30" s="1"/>
       <c r="AT30" s="8"/>
-      <c r="AZ30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I31" s="12"/>
+      <c r="I31" s="13"/>
       <c r="K31" s="1"/>
       <c r="M31" s="7"/>
       <c r="S31" s="8"/>
       <c r="U31" s="1"/>
-      <c r="V31" s="12"/>
-      <c r="Y31" s="12"/>
+      <c r="V31" s="13"/>
+      <c r="Y31" s="13"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -2179,16 +2120,15 @@
       <c r="AD31" s="1"/>
       <c r="AF31" s="1"/>
       <c r="AT31" s="8"/>
-      <c r="AZ31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I32" s="12"/>
+      <c r="I32" s="13"/>
       <c r="K32" s="1"/>
       <c r="M32" s="7"/>
       <c r="S32" s="8"/>
       <c r="U32" s="1"/>
-      <c r="V32" s="12"/>
-      <c r="Y32" s="12"/>
+      <c r="V32" s="13"/>
+      <c r="Y32" s="13"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
@@ -2196,18 +2136,17 @@
       <c r="AD32" s="1"/>
       <c r="AF32" s="1"/>
       <c r="AT32" s="8"/>
-      <c r="AZ32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F33" s="12"/>
-      <c r="I33" s="12"/>
+      <c r="F33" s="13"/>
+      <c r="I33" s="13"/>
       <c r="K33" s="1"/>
       <c r="M33" s="7"/>
       <c r="S33" s="8"/>
       <c r="U33" s="1"/>
-      <c r="V33" s="12"/>
-      <c r="W33" s="12"/>
-      <c r="Y33" s="12"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="Y33" s="13"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -2215,18 +2154,17 @@
       <c r="AD33" s="1"/>
       <c r="AF33" s="1"/>
       <c r="AT33" s="8"/>
-      <c r="AZ33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F34" s="12"/>
-      <c r="I34" s="12"/>
+      <c r="F34" s="13"/>
+      <c r="I34" s="13"/>
       <c r="K34" s="1"/>
       <c r="M34" s="7"/>
       <c r="S34" s="8"/>
       <c r="U34" s="1"/>
-      <c r="V34" s="12"/>
-      <c r="W34" s="12"/>
-      <c r="Y34" s="12"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="Y34" s="13"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
@@ -2234,18 +2172,17 @@
       <c r="AD34" s="1"/>
       <c r="AF34" s="1"/>
       <c r="AT34" s="8"/>
-      <c r="AZ34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F35" s="12"/>
-      <c r="I35" s="12"/>
+      <c r="F35" s="13"/>
+      <c r="I35" s="13"/>
       <c r="K35" s="1"/>
       <c r="M35" s="7"/>
       <c r="S35" s="8"/>
       <c r="U35" s="1"/>
-      <c r="V35" s="12"/>
-      <c r="W35" s="12"/>
-      <c r="Y35" s="12"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="Y35" s="13"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
@@ -2253,18 +2190,17 @@
       <c r="AD35" s="1"/>
       <c r="AF35" s="1"/>
       <c r="AT35" s="8"/>
-      <c r="AZ35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F36" s="12"/>
-      <c r="I36" s="12"/>
+      <c r="F36" s="13"/>
+      <c r="I36" s="13"/>
       <c r="K36" s="1"/>
       <c r="M36" s="7"/>
       <c r="S36" s="8"/>
       <c r="U36" s="1"/>
-      <c r="V36" s="12"/>
-      <c r="W36" s="12"/>
-      <c r="Y36" s="12"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="Y36" s="13"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
@@ -2272,17 +2208,16 @@
       <c r="AD36" s="1"/>
       <c r="AF36" s="1"/>
       <c r="AT36" s="8"/>
-      <c r="AZ36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F37" s="12"/>
-      <c r="I37" s="12"/>
+      <c r="F37" s="13"/>
+      <c r="I37" s="13"/>
       <c r="K37" s="1"/>
       <c r="M37" s="7"/>
       <c r="S37" s="8"/>
       <c r="U37" s="1"/>
-      <c r="V37" s="12"/>
-      <c r="W37" s="12"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
@@ -2290,18 +2225,17 @@
       <c r="AD37" s="1"/>
       <c r="AF37" s="1"/>
       <c r="AT37" s="8"/>
-      <c r="AY37" s="12"/>
-      <c r="AZ37" s="1"/>
+      <c r="AY37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F38" s="12"/>
-      <c r="I38" s="12"/>
+      <c r="F38" s="13"/>
+      <c r="I38" s="13"/>
       <c r="K38" s="1"/>
       <c r="M38" s="7"/>
       <c r="S38" s="8"/>
       <c r="U38" s="1"/>
-      <c r="V38" s="12"/>
-      <c r="W38" s="12"/>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
@@ -2309,18 +2243,17 @@
       <c r="AD38" s="1"/>
       <c r="AF38" s="1"/>
       <c r="AT38" s="8"/>
-      <c r="AY38" s="12"/>
-      <c r="AZ38" s="1"/>
+      <c r="AY38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F39" s="12"/>
-      <c r="I39" s="12"/>
+      <c r="F39" s="13"/>
+      <c r="I39" s="13"/>
       <c r="K39" s="1"/>
       <c r="M39" s="7"/>
       <c r="S39" s="8"/>
       <c r="U39" s="1"/>
-      <c r="V39" s="12"/>
-      <c r="W39" s="12"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
@@ -2328,83 +2261,79 @@
       <c r="AD39" s="1"/>
       <c r="AF39" s="1"/>
       <c r="AT39" s="8"/>
-      <c r="AY39" s="12"/>
-      <c r="AZ39" s="1"/>
+      <c r="AY39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="I40" s="12"/>
+      <c r="A40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="I40" s="13"/>
       <c r="K40" s="1"/>
       <c r="M40" s="7"/>
       <c r="S40" s="8"/>
       <c r="U40" s="1"/>
-      <c r="V40" s="12"/>
-      <c r="W40" s="12"/>
-      <c r="Y40" s="12"/>
+      <c r="V40" s="13"/>
+      <c r="W40" s="13"/>
+      <c r="Y40" s="13"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
       <c r="AF40" s="1"/>
-      <c r="AI40" s="12"/>
+      <c r="AI40" s="13"/>
       <c r="AT40" s="8"/>
-      <c r="AY40" s="12"/>
-      <c r="AZ40" s="1"/>
+      <c r="AY40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13"/>
-      <c r="F41" s="12"/>
-      <c r="I41" s="12"/>
+      <c r="A41" s="14"/>
+      <c r="F41" s="13"/>
+      <c r="I41" s="13"/>
       <c r="K41" s="1"/>
       <c r="M41" s="7"/>
       <c r="S41" s="8"/>
       <c r="U41" s="1"/>
-      <c r="V41" s="12"/>
-      <c r="W41" s="12"/>
-      <c r="Y41" s="12"/>
+      <c r="V41" s="13"/>
+      <c r="W41" s="13"/>
+      <c r="Y41" s="13"/>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
       <c r="AF41" s="1"/>
-      <c r="AI41" s="13"/>
+      <c r="AI41" s="14"/>
       <c r="AT41" s="8"/>
-      <c r="AY41" s="13"/>
-      <c r="AZ41" s="1"/>
+      <c r="AY41" s="14"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13"/>
-      <c r="I42" s="12"/>
+      <c r="A42" s="14"/>
+      <c r="I42" s="13"/>
       <c r="K42" s="1"/>
       <c r="M42" s="7"/>
       <c r="S42" s="8"/>
       <c r="U42" s="1"/>
-      <c r="V42" s="12"/>
-      <c r="W42" s="12"/>
-      <c r="Y42" s="12"/>
+      <c r="V42" s="13"/>
+      <c r="W42" s="13"/>
+      <c r="Y42" s="13"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
       <c r="AF42" s="1"/>
-      <c r="AI42" s="13"/>
+      <c r="AI42" s="14"/>
       <c r="AT42" s="8"/>
-      <c r="AY42" s="13"/>
-      <c r="AZ42" s="1"/>
+      <c r="AY42" s="14"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F43" s="12"/>
+      <c r="F43" s="13"/>
       <c r="I43" s="1"/>
       <c r="K43" s="1"/>
       <c r="M43" s="7"/>
       <c r="S43" s="8"/>
       <c r="U43" s="1"/>
-      <c r="V43" s="12"/>
-      <c r="W43" s="12"/>
+      <c r="V43" s="13"/>
+      <c r="W43" s="13"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
@@ -2412,25 +2341,23 @@
       <c r="AD43" s="1"/>
       <c r="AF43" s="1"/>
       <c r="AT43" s="8"/>
-      <c r="AZ43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F44" s="12"/>
+      <c r="F44" s="13"/>
       <c r="I44" s="1"/>
       <c r="K44" s="1"/>
       <c r="M44" s="7"/>
       <c r="S44" s="8"/>
       <c r="U44" s="1"/>
-      <c r="V44" s="12"/>
-      <c r="W44" s="12"/>
+      <c r="V44" s="13"/>
+      <c r="W44" s="13"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
       <c r="AF44" s="1"/>
-      <c r="AH44" s="12"/>
+      <c r="AH44" s="13"/>
       <c r="AT44" s="8"/>
-      <c r="AZ44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I45" s="1"/>
@@ -2445,7 +2372,6 @@
       <c r="AD45" s="1"/>
       <c r="AF45" s="1"/>
       <c r="AT45" s="8"/>
-      <c r="AZ45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I46" s="1"/>
@@ -2459,10 +2385,9 @@
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
       <c r="AF46" s="1"/>
-      <c r="AL46" s="12"/>
-      <c r="AM46" s="12"/>
+      <c r="AL46" s="13"/>
+      <c r="AM46" s="13"/>
       <c r="AT46" s="8"/>
-      <c r="AZ46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I47" s="1"/>
@@ -2470,7 +2395,7 @@
       <c r="M47" s="7"/>
       <c r="S47" s="8"/>
       <c r="U47" s="1"/>
-      <c r="Y47" s="12"/>
+      <c r="Y47" s="13"/>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
@@ -2480,7 +2405,6 @@
       <c r="AL47" s="1"/>
       <c r="AN47" s="1"/>
       <c r="AT47" s="8"/>
-      <c r="AZ47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I48" s="1"/>
@@ -2489,7 +2413,7 @@
       <c r="S48" s="8"/>
       <c r="U48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AA48" s="12"/>
+      <c r="AA48" s="13"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
@@ -2498,7 +2422,6 @@
       <c r="AN48" s="1"/>
       <c r="AP48" s="1"/>
       <c r="AX48" s="1"/>
-      <c r="AZ48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="1"/>
@@ -2507,17 +2430,16 @@
       <c r="S49" s="8"/>
       <c r="U49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AA49" s="12"/>
+      <c r="AA49" s="13"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
       <c r="AF49" s="1"/>
-      <c r="AI49" s="12"/>
+      <c r="AI49" s="13"/>
       <c r="AL49" s="1"/>
       <c r="AN49" s="1"/>
       <c r="AP49" s="1"/>
       <c r="AX49" s="1"/>
-      <c r="AZ49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I50" s="1"/>
@@ -2531,12 +2453,11 @@
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
       <c r="AF50" s="1"/>
-      <c r="AI50" s="12"/>
+      <c r="AI50" s="13"/>
       <c r="AL50" s="1"/>
       <c r="AN50" s="1"/>
       <c r="AP50" s="1"/>
       <c r="AX50" s="1"/>
-      <c r="AZ50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I51" s="1"/>
@@ -2544,20 +2465,19 @@
       <c r="M51" s="7"/>
       <c r="S51" s="8"/>
       <c r="U51" s="1"/>
-      <c r="Y51" s="12"/>
+      <c r="Y51" s="13"/>
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
       <c r="AF51" s="1"/>
-      <c r="AI51" s="12"/>
+      <c r="AI51" s="13"/>
       <c r="AL51" s="1"/>
       <c r="AM51" s="1"/>
       <c r="AN51" s="1"/>
       <c r="AP51" s="1"/>
       <c r="AX51" s="1"/>
-      <c r="AZ51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I52" s="1"/>
@@ -2566,18 +2486,17 @@
       <c r="S52" s="8"/>
       <c r="U52" s="1"/>
       <c r="Z52" s="1"/>
-      <c r="AA52" s="12"/>
+      <c r="AA52" s="13"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
       <c r="AF52" s="1"/>
-      <c r="AI52" s="12"/>
+      <c r="AI52" s="13"/>
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
       <c r="AN52" s="1"/>
       <c r="AP52" s="1"/>
       <c r="AX52" s="1"/>
-      <c r="AZ52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I53" s="1"/>
@@ -2591,13 +2510,12 @@
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
       <c r="AF53" s="1"/>
-      <c r="AI53" s="12"/>
+      <c r="AI53" s="13"/>
       <c r="AL53" s="1"/>
       <c r="AM53" s="1"/>
       <c r="AN53" s="1"/>
       <c r="AP53" s="1"/>
       <c r="AX53" s="1"/>
-      <c r="AZ53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I54" s="1"/>
@@ -2605,20 +2523,19 @@
       <c r="M54" s="7"/>
       <c r="S54" s="8"/>
       <c r="U54" s="1"/>
-      <c r="Y54" s="12"/>
+      <c r="Y54" s="13"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
       <c r="AF54" s="1"/>
-      <c r="AI54" s="12"/>
+      <c r="AI54" s="13"/>
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
       <c r="AN54" s="1"/>
       <c r="AP54" s="1"/>
       <c r="AX54" s="1"/>
-      <c r="AZ54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I55" s="1"/>
@@ -2627,18 +2544,17 @@
       <c r="S55" s="8"/>
       <c r="U55" s="1"/>
       <c r="Z55" s="1"/>
-      <c r="AA55" s="12"/>
+      <c r="AA55" s="13"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
       <c r="AF55" s="1"/>
-      <c r="AI55" s="12"/>
+      <c r="AI55" s="13"/>
       <c r="AL55" s="1"/>
       <c r="AM55" s="1"/>
       <c r="AN55" s="1"/>
       <c r="AP55" s="1"/>
       <c r="AX55" s="1"/>
-      <c r="AZ55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I56" s="1"/>
@@ -2652,13 +2568,12 @@
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
       <c r="AF56" s="1"/>
-      <c r="AI56" s="12"/>
+      <c r="AI56" s="13"/>
       <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
       <c r="AN56" s="1"/>
       <c r="AP56" s="1"/>
       <c r="AX56" s="1"/>
-      <c r="AZ56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I57" s="1"/>
@@ -2666,20 +2581,19 @@
       <c r="M57" s="7"/>
       <c r="S57" s="8"/>
       <c r="U57" s="1"/>
-      <c r="Y57" s="12"/>
+      <c r="Y57" s="13"/>
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
       <c r="AF57" s="1"/>
-      <c r="AI57" s="12"/>
+      <c r="AI57" s="13"/>
       <c r="AL57" s="1"/>
       <c r="AM57" s="1"/>
       <c r="AN57" s="1"/>
       <c r="AP57" s="1"/>
       <c r="AX57" s="1"/>
-      <c r="AZ57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I58" s="1"/>
@@ -2693,13 +2607,12 @@
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
       <c r="AF58" s="1"/>
-      <c r="AI58" s="12"/>
+      <c r="AI58" s="13"/>
       <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
       <c r="AN58" s="1"/>
       <c r="AP58" s="1"/>
       <c r="AX58" s="1"/>
-      <c r="AZ58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I59" s="1"/>
@@ -2707,20 +2620,19 @@
       <c r="M59" s="7"/>
       <c r="S59" s="8"/>
       <c r="U59" s="1"/>
-      <c r="Y59" s="12"/>
+      <c r="Y59" s="13"/>
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
       <c r="AF59" s="1"/>
-      <c r="AI59" s="12"/>
+      <c r="AI59" s="13"/>
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
       <c r="AN59" s="1"/>
       <c r="AP59" s="1"/>
       <c r="AX59" s="1"/>
-      <c r="AZ59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I60" s="1"/>
@@ -2734,12 +2646,11 @@
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
       <c r="AF60" s="1"/>
-      <c r="AI60" s="12"/>
+      <c r="AI60" s="13"/>
       <c r="AL60" s="1"/>
       <c r="AM60" s="1"/>
       <c r="AP60" s="1"/>
       <c r="AX60" s="1"/>
-      <c r="AZ60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I61" s="1"/>
@@ -2753,12 +2664,11 @@
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
       <c r="AF61" s="1"/>
-      <c r="AI61" s="12"/>
+      <c r="AI61" s="13"/>
       <c r="AL61" s="1"/>
       <c r="AM61" s="1"/>
       <c r="AP61" s="1"/>
       <c r="AX61" s="1"/>
-      <c r="AZ61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I62" s="1"/>
@@ -2766,17 +2676,16 @@
       <c r="M62" s="7"/>
       <c r="S62" s="8"/>
       <c r="U62" s="1"/>
-      <c r="Y62" s="12"/>
+      <c r="Y62" s="13"/>
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
       <c r="AF62" s="1"/>
-      <c r="AI62" s="12"/>
-      <c r="AL62" s="12"/>
-      <c r="AM62" s="12"/>
-      <c r="AZ62" s="1"/>
+      <c r="AI62" s="13"/>
+      <c r="AL62" s="13"/>
+      <c r="AM62" s="13"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I63" s="1"/>
@@ -2784,22 +2693,21 @@
       <c r="M63" s="7"/>
       <c r="S63" s="8"/>
       <c r="U63" s="1"/>
-      <c r="Y63" s="12"/>
+      <c r="Y63" s="13"/>
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
       <c r="AF63" s="1"/>
-      <c r="AI63" s="12"/>
-      <c r="AK63" s="12"/>
+      <c r="AI63" s="13"/>
+      <c r="AK63" s="13"/>
       <c r="AL63" s="1"/>
       <c r="AM63" s="1"/>
-      <c r="AZ63" s="1"/>
     </row>
     <row r="64" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="15"/>
-      <c r="C64" s="14"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="15"/>
       <c r="E64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -2808,12 +2716,12 @@
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
-      <c r="S64" s="16"/>
+      <c r="S64" s="17"/>
       <c r="U64" s="1"/>
-      <c r="V64" s="17"/>
-      <c r="W64" s="12"/>
-      <c r="Z64" s="12"/>
-      <c r="AA64" s="12"/>
+      <c r="V64" s="18"/>
+      <c r="W64" s="13"/>
+      <c r="Z64" s="13"/>
+      <c r="AA64" s="13"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
@@ -2824,11 +2732,10 @@
       <c r="AL64" s="1"/>
       <c r="AN64" s="1"/>
       <c r="AT64" s="8"/>
-      <c r="AZ64" s="1"/>
     </row>
     <row r="65" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="15"/>
-      <c r="C65" s="14"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="15"/>
       <c r="E65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -2837,12 +2744,12 @@
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
-      <c r="S65" s="16"/>
+      <c r="S65" s="17"/>
       <c r="U65" s="1"/>
-      <c r="V65" s="17"/>
-      <c r="W65" s="12"/>
-      <c r="Z65" s="12"/>
-      <c r="AA65" s="12"/>
+      <c r="V65" s="18"/>
+      <c r="W65" s="13"/>
+      <c r="Z65" s="13"/>
+      <c r="AA65" s="13"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
@@ -2853,11 +2760,10 @@
       <c r="AL65" s="1"/>
       <c r="AN65" s="1"/>
       <c r="AT65" s="8"/>
-      <c r="AZ65" s="1"/>
     </row>
     <row r="66" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="15"/>
-      <c r="C66" s="14"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="15"/>
       <c r="E66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -2866,12 +2772,12 @@
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
-      <c r="S66" s="16"/>
+      <c r="S66" s="17"/>
       <c r="U66" s="1"/>
-      <c r="V66" s="17"/>
-      <c r="W66" s="12"/>
-      <c r="Z66" s="12"/>
-      <c r="AA66" s="12"/>
+      <c r="V66" s="18"/>
+      <c r="W66" s="13"/>
+      <c r="Z66" s="13"/>
+      <c r="AA66" s="13"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
@@ -2882,13 +2788,12 @@
       <c r="AL66" s="1"/>
       <c r="AN66" s="1"/>
       <c r="AT66" s="8"/>
-      <c r="AZ66" s="1"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I67" s="1"/>
       <c r="K67" s="1"/>
       <c r="M67" s="1"/>
-      <c r="S67" s="16"/>
+      <c r="S67" s="17"/>
       <c r="U67" s="1"/>
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
@@ -2897,13 +2802,12 @@
       <c r="AE67" s="1"/>
       <c r="AF67" s="1"/>
       <c r="AT67" s="8"/>
-      <c r="AZ67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I68" s="1"/>
       <c r="K68" s="1"/>
       <c r="M68" s="1"/>
-      <c r="S68" s="16"/>
+      <c r="S68" s="17"/>
       <c r="U68" s="1"/>
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
@@ -2913,14 +2817,13 @@
       <c r="AE68" s="1"/>
       <c r="AF68" s="1"/>
       <c r="AT68" s="8"/>
-      <c r="AZ68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D69" s="14"/>
+      <c r="D69" s="15"/>
       <c r="I69" s="1"/>
       <c r="K69" s="1"/>
       <c r="M69" s="1"/>
-      <c r="S69" s="16"/>
+      <c r="S69" s="17"/>
       <c r="U69" s="1"/>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
@@ -2931,7 +2834,6 @@
       <c r="AG69" s="1"/>
       <c r="AJ69" s="1"/>
       <c r="AV69" s="1"/>
-      <c r="AZ69" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3335,319 +3237,319 @@
       <c r="AW3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="16" t="n">
         <v>7869001</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="15"/>
+      <c r="D4" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12" t="s">
+      <c r="N4" s="13"/>
+      <c r="O4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="P4" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="13"/>
+      <c r="U4" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="V4" s="12" t="s">
+      <c r="W4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="W4" s="12" t="s">
+      <c r="X4" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="X4" s="12" t="s">
+      <c r="Y4" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="Y4" s="12" t="s">
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12" t="s">
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF4" s="13"/>
+      <c r="AG4" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH4" s="13"/>
+      <c r="AI4" s="13"/>
+      <c r="AJ4" s="13"/>
+      <c r="AK4" s="13"/>
+      <c r="AL4" s="13"/>
+      <c r="AM4" s="13"/>
+      <c r="AN4" s="10"/>
+      <c r="AO4" s="13"/>
+      <c r="AP4" s="13"/>
+      <c r="AQ4" s="13"/>
+      <c r="AR4" s="13"/>
+      <c r="AS4" s="13"/>
+      <c r="AT4" s="13"/>
+      <c r="AU4" s="13"/>
+      <c r="AV4" s="13"/>
+      <c r="AW4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH4" s="12"/>
-      <c r="AI4" s="12"/>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="12"/>
-      <c r="AL4" s="12"/>
-      <c r="AM4" s="12"/>
-      <c r="AN4" s="9"/>
-      <c r="AO4" s="12"/>
-      <c r="AP4" s="12"/>
-      <c r="AQ4" s="12"/>
-      <c r="AR4" s="12"/>
-      <c r="AS4" s="12"/>
-      <c r="AT4" s="12"/>
-      <c r="AU4" s="12"/>
-      <c r="AV4" s="12"/>
-      <c r="AW4" s="12"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="B5" s="16" t="n">
+        <v>7869002</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>7869002</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12" t="s">
+      <c r="E5" s="15"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
       <c r="M5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12" t="s">
+      <c r="N5" s="13"/>
+      <c r="O5" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="P5" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="P5" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="S5" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12" t="s">
+      <c r="T5" s="13"/>
+      <c r="U5" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="V5" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="W5" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD5" s="13"/>
+      <c r="AE5" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF5" s="13"/>
+      <c r="AG5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH5" s="13"/>
+      <c r="AI5" s="13"/>
+      <c r="AJ5" s="13"/>
+      <c r="AK5" s="13"/>
+      <c r="AL5" s="13"/>
+      <c r="AM5" s="13"/>
+      <c r="AN5" s="10"/>
+      <c r="AO5" s="13"/>
+      <c r="AP5" s="13"/>
+      <c r="AQ5" s="13"/>
+      <c r="AR5" s="13"/>
+      <c r="AS5" s="13"/>
+      <c r="AT5" s="13"/>
+      <c r="AU5" s="13"/>
+      <c r="AV5" s="13"/>
+      <c r="AW5" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="V5" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="W5" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="X5" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y5" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF5" s="12"/>
-      <c r="AG5" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="12"/>
-      <c r="AJ5" s="12"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="12"/>
-      <c r="AM5" s="12"/>
-      <c r="AN5" s="9"/>
-      <c r="AO5" s="12"/>
-      <c r="AP5" s="12"/>
-      <c r="AQ5" s="12"/>
-      <c r="AR5" s="12"/>
-      <c r="AS5" s="12"/>
-      <c r="AT5" s="12"/>
-      <c r="AU5" s="12"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="12"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="B6" s="16" t="n">
+        <v>7869003</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="15" t="n">
-        <v>7869003</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
       <c r="M6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12" t="s">
+      <c r="N6" s="13"/>
+      <c r="O6" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="P6" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="P6" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="S6" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12" t="s">
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="W6" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="W6" s="12" t="s">
+      <c r="X6" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="X6" s="12" t="s">
+      <c r="Y6" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="Y6" s="12" t="s">
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="AD6" s="12"/>
-      <c r="AE6" s="12" t="s">
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="12" t="s">
+      <c r="AF6" s="13"/>
+      <c r="AG6" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="AH6" s="12"/>
-      <c r="AI6" s="12"/>
-      <c r="AJ6" s="12"/>
-      <c r="AK6" s="12"/>
-      <c r="AL6" s="12"/>
-      <c r="AM6" s="12"/>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="12"/>
-      <c r="AQ6" s="12"/>
-      <c r="AR6" s="12"/>
-      <c r="AS6" s="12"/>
-      <c r="AT6" s="12"/>
-      <c r="AU6" s="12"/>
-      <c r="AV6" s="12"/>
-      <c r="AW6" s="12"/>
+      <c r="AH6" s="13"/>
+      <c r="AI6" s="13"/>
+      <c r="AJ6" s="13"/>
+      <c r="AK6" s="13"/>
+      <c r="AL6" s="13"/>
+      <c r="AM6" s="13"/>
+      <c r="AN6" s="13"/>
+      <c r="AO6" s="13"/>
+      <c r="AP6" s="13"/>
+      <c r="AQ6" s="13"/>
+      <c r="AR6" s="13"/>
+      <c r="AS6" s="13"/>
+      <c r="AT6" s="13"/>
+      <c r="AU6" s="13"/>
+      <c r="AV6" s="13"/>
+      <c r="AW6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="15"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="12"/>
-      <c r="J7" s="12"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="13"/>
+      <c r="J7" s="13"/>
       <c r="M7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="V7" s="18"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="V7" s="19"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="12"/>
+      <c r="Y7" s="13"/>
       <c r="Z7" s="1"/>
-      <c r="AB7" s="12"/>
-      <c r="AD7" s="12"/>
+      <c r="AB7" s="13"/>
+      <c r="AD7" s="13"/>
       <c r="AE7" s="1"/>
-      <c r="AG7" s="12"/>
-      <c r="AR7" s="12"/>
+      <c r="AG7" s="13"/>
+      <c r="AR7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="12"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="13"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="12"/>
+      <c r="J8" s="13"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
       <c r="T8" s="1"/>
-      <c r="V8" s="18"/>
+      <c r="V8" s="19"/>
       <c r="W8" s="1"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
       <c r="AA8" s="1"/>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="12"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
       <c r="AF8" s="1"/>
-      <c r="AG8" s="12"/>
+      <c r="AG8" s="13"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
@@ -3657,7 +3559,7 @@
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
-      <c r="AR8" s="12"/>
+      <c r="AR8" s="13"/>
       <c r="AS8" s="1"/>
       <c r="AT8" s="1"/>
       <c r="AU8" s="1"/>
@@ -3665,439 +3567,439 @@
       <c r="AW8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="15"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="12"/>
-      <c r="J9" s="12"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="13"/>
+      <c r="J9" s="13"/>
       <c r="M9" s="1"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="V9" s="18"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="V9" s="19"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AB9" s="12"/>
-      <c r="AD9" s="12"/>
-      <c r="AG9" s="12"/>
-      <c r="AR9" s="12"/>
+      <c r="AB9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AG9" s="13"/>
+      <c r="AR9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="15"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="12"/>
-      <c r="J10" s="12"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="13"/>
+      <c r="J10" s="13"/>
       <c r="M10" s="1"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="V10" s="18"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="V10" s="19"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AB10" s="12"/>
-      <c r="AD10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AR10" s="12"/>
+      <c r="AB10" s="13"/>
+      <c r="AD10" s="13"/>
+      <c r="AG10" s="13"/>
+      <c r="AR10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="15"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="12"/>
-      <c r="J11" s="12"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="13"/>
+      <c r="J11" s="13"/>
       <c r="M11" s="1"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="V11" s="18"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="V11" s="19"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AB11" s="12"/>
-      <c r="AD11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AR11" s="12"/>
+      <c r="AB11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AG11" s="13"/>
+      <c r="AR11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="15"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="12"/>
-      <c r="J12" s="12"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="13"/>
+      <c r="J12" s="13"/>
       <c r="M12" s="1"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="V12" s="18"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="V12" s="19"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-      <c r="AB12" s="12"/>
-      <c r="AD12" s="12"/>
-      <c r="AG12" s="12"/>
-      <c r="AR12" s="12"/>
+      <c r="AB12" s="13"/>
+      <c r="AD12" s="13"/>
+      <c r="AG12" s="13"/>
+      <c r="AR12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="15"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="14"/>
-      <c r="J13" s="12"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="15"/>
+      <c r="J13" s="13"/>
       <c r="M13" s="1"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="12"/>
+      <c r="S13" s="13"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
-      <c r="AB13" s="12"/>
-      <c r="AD13" s="12"/>
-      <c r="AE13" s="12"/>
-      <c r="AG13" s="12"/>
+      <c r="AB13" s="13"/>
+      <c r="AD13" s="13"/>
+      <c r="AE13" s="13"/>
+      <c r="AG13" s="13"/>
       <c r="AQ13" s="1"/>
       <c r="AR13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="14"/>
-      <c r="J14" s="12"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="15"/>
+      <c r="J14" s="13"/>
       <c r="M14" s="1"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
       <c r="R14" s="1"/>
-      <c r="S14" s="12"/>
+      <c r="S14" s="13"/>
       <c r="W14" s="1"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="12"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="13"/>
       <c r="Z14" s="1"/>
-      <c r="AB14" s="12"/>
-      <c r="AD14" s="12"/>
-      <c r="AE14" s="12"/>
-      <c r="AG14" s="12"/>
+      <c r="AB14" s="13"/>
+      <c r="AD14" s="13"/>
+      <c r="AE14" s="13"/>
+      <c r="AG14" s="13"/>
       <c r="AQ14" s="1"/>
       <c r="AR14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="15"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="14"/>
-      <c r="J15" s="12"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="15"/>
+      <c r="J15" s="13"/>
       <c r="M15" s="1"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="12"/>
+      <c r="S15" s="13"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
-      <c r="AB15" s="12"/>
-      <c r="AD15" s="12"/>
-      <c r="AE15" s="12"/>
-      <c r="AG15" s="12"/>
+      <c r="AB15" s="13"/>
+      <c r="AD15" s="13"/>
+      <c r="AE15" s="13"/>
+      <c r="AG15" s="13"/>
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="15"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="14"/>
-      <c r="J16" s="12"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="15"/>
+      <c r="J16" s="13"/>
       <c r="M16" s="1"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
       <c r="R16" s="1"/>
-      <c r="S16" s="12"/>
+      <c r="S16" s="13"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-      <c r="Y16" s="12"/>
+      <c r="Y16" s="13"/>
       <c r="Z16" s="1"/>
-      <c r="AB16" s="12"/>
-      <c r="AD16" s="12"/>
-      <c r="AE16" s="12"/>
-      <c r="AG16" s="12"/>
+      <c r="AB16" s="13"/>
+      <c r="AD16" s="13"/>
+      <c r="AE16" s="13"/>
+      <c r="AG16" s="13"/>
       <c r="AQ16" s="1"/>
       <c r="AR16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="15"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="14"/>
-      <c r="J17" s="12"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="15"/>
+      <c r="J17" s="13"/>
       <c r="M17" s="1"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
       <c r="R17" s="1"/>
-      <c r="S17" s="12"/>
+      <c r="S17" s="13"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-      <c r="AB17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AG17" s="12"/>
+      <c r="AB17" s="13"/>
+      <c r="AD17" s="13"/>
+      <c r="AE17" s="13"/>
+      <c r="AG17" s="13"/>
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="15"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="14"/>
-      <c r="J18" s="12"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="15"/>
+      <c r="J18" s="13"/>
       <c r="M18" s="1"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
       <c r="R18" s="1"/>
-      <c r="S18" s="12"/>
+      <c r="S18" s="13"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
-      <c r="AB18" s="12"/>
-      <c r="AD18" s="12"/>
-      <c r="AE18" s="12"/>
-      <c r="AG18" s="12"/>
+      <c r="AB18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+      <c r="AG18" s="13"/>
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="15"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="14"/>
-      <c r="J19" s="12"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="15"/>
+      <c r="J19" s="13"/>
       <c r="M19" s="1"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
       <c r="R19" s="1"/>
-      <c r="S19" s="12"/>
+      <c r="S19" s="13"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
-      <c r="AB19" s="12"/>
-      <c r="AD19" s="12"/>
-      <c r="AE19" s="12"/>
-      <c r="AG19" s="12"/>
+      <c r="AB19" s="13"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="13"/>
+      <c r="AG19" s="13"/>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="15"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="12"/>
-      <c r="J20" s="12"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="13"/>
+      <c r="J20" s="13"/>
       <c r="M20" s="1"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
       <c r="R20" s="1"/>
-      <c r="S20" s="12"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="12"/>
+      <c r="S20" s="13"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="13"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
-      <c r="AB20" s="12"/>
-      <c r="AD20" s="12"/>
-      <c r="AG20" s="12"/>
+      <c r="AB20" s="13"/>
+      <c r="AD20" s="13"/>
+      <c r="AG20" s="13"/>
       <c r="AQ20" s="1"/>
       <c r="AR20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="15"/>
-      <c r="C21" s="22"/>
-      <c r="J21" s="12"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="23"/>
+      <c r="J21" s="13"/>
       <c r="M21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="12"/>
+      <c r="Q21" s="13"/>
       <c r="R21" s="1"/>
-      <c r="S21" s="12"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="12"/>
+      <c r="S21" s="13"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="13"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="12"/>
-      <c r="AA21" s="12"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
       <c r="AE21" s="1"/>
-      <c r="AG21" s="12"/>
+      <c r="AG21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="15"/>
-      <c r="C22" s="22"/>
-      <c r="J22" s="12"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="23"/>
+      <c r="J22" s="13"/>
       <c r="M22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="12"/>
+      <c r="Q22" s="13"/>
       <c r="R22" s="1"/>
-      <c r="S22" s="12"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="12"/>
+      <c r="S22" s="13"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="13"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="12"/>
-      <c r="AA22" s="12"/>
-      <c r="AB22" s="12"/>
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="13"/>
+      <c r="AB22" s="13"/>
       <c r="AE22" s="1"/>
-      <c r="AG22" s="12"/>
+      <c r="AG22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="15"/>
-      <c r="C23" s="22"/>
-      <c r="J23" s="12"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="23"/>
+      <c r="J23" s="13"/>
       <c r="M23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="12"/>
+      <c r="Q23" s="13"/>
       <c r="R23" s="1"/>
-      <c r="S23" s="12"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="12"/>
+      <c r="S23" s="13"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="13"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="Z23" s="12"/>
-      <c r="AA23" s="12"/>
-      <c r="AB23" s="12"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="13"/>
       <c r="AE23" s="1"/>
-      <c r="AG23" s="12"/>
+      <c r="AG23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="15"/>
-      <c r="C24" s="22"/>
-      <c r="J24" s="12"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="23"/>
+      <c r="J24" s="13"/>
       <c r="M24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="12"/>
+      <c r="Q24" s="13"/>
       <c r="R24" s="1"/>
-      <c r="S24" s="12"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="12"/>
+      <c r="S24" s="13"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="13"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="12"/>
-      <c r="AA24" s="12"/>
-      <c r="AB24" s="12"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="13"/>
+      <c r="AB24" s="13"/>
       <c r="AE24" s="1"/>
-      <c r="AG24" s="12"/>
+      <c r="AG24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="15"/>
-      <c r="C25" s="22"/>
-      <c r="J25" s="12"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="23"/>
+      <c r="J25" s="13"/>
       <c r="M25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="12"/>
+      <c r="Q25" s="13"/>
       <c r="R25" s="1"/>
-      <c r="S25" s="12"/>
-      <c r="V25" s="17"/>
-      <c r="W25" s="12"/>
+      <c r="S25" s="13"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="13"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="Z25" s="12"/>
-      <c r="AA25" s="12"/>
-      <c r="AB25" s="12"/>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="13"/>
+      <c r="AB25" s="13"/>
       <c r="AE25" s="1"/>
-      <c r="AG25" s="12"/>
+      <c r="AG25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="15"/>
-      <c r="C26" s="22"/>
-      <c r="J26" s="12"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="23"/>
+      <c r="J26" s="13"/>
       <c r="M26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="12"/>
+      <c r="Q26" s="13"/>
       <c r="R26" s="1"/>
-      <c r="S26" s="12"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="12"/>
+      <c r="S26" s="13"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="13"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="Z26" s="12"/>
-      <c r="AA26" s="12"/>
-      <c r="AB26" s="12"/>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="13"/>
       <c r="AE26" s="1"/>
-      <c r="AG26" s="12"/>
+      <c r="AG26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="15"/>
-      <c r="C27" s="22"/>
-      <c r="J27" s="12"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="23"/>
+      <c r="J27" s="13"/>
       <c r="M27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="12"/>
+      <c r="Q27" s="13"/>
       <c r="R27" s="1"/>
-      <c r="S27" s="12"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="12"/>
+      <c r="S27" s="13"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="13"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="12"/>
-      <c r="AA27" s="12"/>
-      <c r="AB27" s="12"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
       <c r="AE27" s="1"/>
-      <c r="AG27" s="12"/>
+      <c r="AG27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="15"/>
-      <c r="C28" s="22"/>
-      <c r="J28" s="12"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="23"/>
+      <c r="J28" s="13"/>
       <c r="M28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="12"/>
+      <c r="Q28" s="13"/>
       <c r="R28" s="1"/>
-      <c r="S28" s="12"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="12"/>
+      <c r="S28" s="13"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="13"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="AB28" s="12"/>
-      <c r="AD28" s="12"/>
+      <c r="AB28" s="13"/>
+      <c r="AD28" s="13"/>
       <c r="AE28" s="1"/>
-      <c r="AG28" s="12"/>
+      <c r="AG28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="15"/>
-      <c r="C29" s="22"/>
-      <c r="J29" s="12"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="23"/>
+      <c r="J29" s="13"/>
       <c r="M29" s="1"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="12"/>
+      <c r="Q29" s="13"/>
       <c r="R29" s="1"/>
-      <c r="S29" s="12"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="12"/>
+      <c r="S29" s="13"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="13"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="12"/>
-      <c r="AB29" s="12"/>
-      <c r="AD29" s="12"/>
+      <c r="Y29" s="13"/>
+      <c r="AB29" s="13"/>
+      <c r="AD29" s="13"/>
       <c r="AE29" s="1"/>
-      <c r="AG29" s="12"/>
+      <c r="AG29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="15"/>
-      <c r="C30" s="12"/>
-      <c r="J30" s="12"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="13"/>
+      <c r="J30" s="13"/>
       <c r="M30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="V30" s="17"/>
+      <c r="V30" s="18"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
@@ -4106,161 +4008,161 @@
       <c r="AL30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="15"/>
-      <c r="C31" s="12"/>
-      <c r="J31" s="12"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="13"/>
+      <c r="J31" s="13"/>
       <c r="M31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="V31" s="17"/>
+      <c r="V31" s="18"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="AA31" s="1"/>
-      <c r="AB31" s="12"/>
+      <c r="AB31" s="13"/>
       <c r="AG31" s="1"/>
       <c r="AL31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="12"/>
-      <c r="J32" s="12"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="13"/>
+      <c r="J32" s="13"/>
       <c r="M32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="V32" s="17"/>
+      <c r="V32" s="18"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-      <c r="Y32" s="12"/>
+      <c r="Y32" s="13"/>
       <c r="AA32" s="1"/>
       <c r="AG32" s="1"/>
       <c r="AL32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="15"/>
-      <c r="C33" s="14"/>
-      <c r="J33" s="12"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="15"/>
+      <c r="J33" s="13"/>
       <c r="M33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="12"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="13"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="AG33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="15"/>
-      <c r="C34" s="14"/>
-      <c r="J34" s="12"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="15"/>
+      <c r="J34" s="13"/>
       <c r="M34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="12"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="13"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="AB34" s="12"/>
+      <c r="AB34" s="13"/>
       <c r="AG34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="15"/>
-      <c r="C35" s="14"/>
-      <c r="J35" s="12"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="15"/>
+      <c r="J35" s="13"/>
       <c r="M35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="12"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="13"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="AD35" s="12"/>
+      <c r="AD35" s="13"/>
       <c r="AG35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="14"/>
-      <c r="J36" s="12"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="15"/>
+      <c r="J36" s="13"/>
       <c r="M36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="V36" s="17"/>
-      <c r="W36" s="12"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="13"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="AG36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="14"/>
-      <c r="J37" s="12"/>
+      <c r="A37" s="14"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="15"/>
+      <c r="J37" s="13"/>
       <c r="M37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="12"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="13"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
       <c r="AG37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="14"/>
-      <c r="J38" s="12"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="15"/>
+      <c r="J38" s="13"/>
       <c r="M38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-      <c r="V38" s="17"/>
-      <c r="W38" s="12"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="13"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="AB38" s="12"/>
+      <c r="AB38" s="13"/>
       <c r="AG38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="14"/>
-      <c r="J39" s="12"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="15"/>
+      <c r="J39" s="13"/>
       <c r="M39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
-      <c r="V39" s="17"/>
-      <c r="W39" s="12"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="13"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="AB39" s="12"/>
-      <c r="AD39" s="12"/>
+      <c r="AB39" s="13"/>
+      <c r="AD39" s="13"/>
       <c r="AG39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="15"/>
-      <c r="C40" s="14"/>
-      <c r="J40" s="12"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="15"/>
+      <c r="J40" s="13"/>
       <c r="M40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -4272,190 +4174,190 @@
       <c r="AG40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="15"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="12"/>
-      <c r="J41" s="12"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="13"/>
+      <c r="J41" s="13"/>
       <c r="M41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="W41" s="1"/>
-      <c r="X41" s="12"/>
+      <c r="X41" s="13"/>
       <c r="Y41" s="1"/>
-      <c r="AD41" s="12"/>
+      <c r="AD41" s="13"/>
       <c r="AG41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="15"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="12"/>
-      <c r="J42" s="12"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="13"/>
+      <c r="J42" s="13"/>
       <c r="M42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="W42" s="1"/>
-      <c r="X42" s="12"/>
+      <c r="X42" s="13"/>
       <c r="Y42" s="1"/>
-      <c r="AD42" s="12"/>
+      <c r="AD42" s="13"/>
       <c r="AG42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="15"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="12"/>
-      <c r="J43" s="12"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="13"/>
+      <c r="J43" s="13"/>
       <c r="M43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="W43" s="1"/>
-      <c r="X43" s="12"/>
+      <c r="X43" s="13"/>
       <c r="Y43" s="1"/>
-      <c r="AD43" s="12"/>
+      <c r="AD43" s="13"/>
       <c r="AG43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="15"/>
-      <c r="C44" s="14"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="15"/>
       <c r="J44" s="1"/>
       <c r="M44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
-      <c r="V44" s="17"/>
-      <c r="W44" s="12"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="13"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
-      <c r="Z44" s="12"/>
-      <c r="AA44" s="12"/>
-      <c r="AB44" s="12"/>
+      <c r="Z44" s="13"/>
+      <c r="AA44" s="13"/>
+      <c r="AB44" s="13"/>
       <c r="AG44" s="1"/>
       <c r="AL44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="15"/>
-      <c r="C45" s="14"/>
-      <c r="E45" s="14"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="15"/>
+      <c r="E45" s="15"/>
       <c r="J45" s="1"/>
       <c r="M45" s="1"/>
-      <c r="P45" s="12"/>
+      <c r="P45" s="13"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
-      <c r="U45" s="12"/>
-      <c r="V45" s="12"/>
-      <c r="W45" s="12"/>
+      <c r="U45" s="13"/>
+      <c r="V45" s="13"/>
+      <c r="W45" s="13"/>
       <c r="X45" s="1"/>
-      <c r="Y45" s="12"/>
-      <c r="AD45" s="12"/>
+      <c r="Y45" s="13"/>
+      <c r="AD45" s="13"/>
       <c r="AG45" s="1"/>
       <c r="AM45" s="1"/>
-      <c r="AN45" s="9"/>
+      <c r="AN45" s="10"/>
       <c r="AP45" s="1"/>
-      <c r="AQ45" s="12"/>
+      <c r="AQ45" s="13"/>
       <c r="AR45" s="1"/>
       <c r="AT45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="15"/>
-      <c r="C46" s="14"/>
-      <c r="E46" s="14"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="15"/>
+      <c r="E46" s="15"/>
       <c r="J46" s="1"/>
       <c r="M46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-      <c r="V46" s="12"/>
-      <c r="W46" s="12"/>
+      <c r="V46" s="13"/>
+      <c r="W46" s="13"/>
       <c r="X46" s="1"/>
-      <c r="Y46" s="12"/>
+      <c r="Y46" s="13"/>
       <c r="AG46" s="1"/>
       <c r="AM46" s="1"/>
-      <c r="AN46" s="9"/>
-      <c r="AP46" s="12"/>
-      <c r="AQ46" s="12"/>
+      <c r="AN46" s="10"/>
+      <c r="AP46" s="13"/>
+      <c r="AQ46" s="13"/>
       <c r="AR46" s="1"/>
       <c r="AT46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="15"/>
-      <c r="C47" s="14"/>
-      <c r="E47" s="14"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="15"/>
+      <c r="E47" s="15"/>
       <c r="J47" s="1"/>
       <c r="M47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-      <c r="V47" s="12"/>
-      <c r="W47" s="12"/>
+      <c r="V47" s="13"/>
+      <c r="W47" s="13"/>
       <c r="X47" s="1"/>
-      <c r="Y47" s="12"/>
+      <c r="Y47" s="13"/>
       <c r="AG47" s="1"/>
       <c r="AM47" s="1"/>
-      <c r="AN47" s="9"/>
-      <c r="AP47" s="12"/>
+      <c r="AN47" s="10"/>
+      <c r="AP47" s="13"/>
       <c r="AQ47" s="1"/>
       <c r="AR47" s="1"/>
       <c r="AT47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="15"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="14"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="15"/>
       <c r="J48" s="1"/>
       <c r="M48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
-      <c r="V48" s="12"/>
-      <c r="W48" s="12"/>
+      <c r="V48" s="13"/>
+      <c r="W48" s="13"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="AB48" s="12"/>
+      <c r="AB48" s="13"/>
       <c r="AG48" s="1"/>
       <c r="AM48" s="1"/>
-      <c r="AN48" s="9"/>
-      <c r="AP48" s="12"/>
-      <c r="AQ48" s="12"/>
+      <c r="AN48" s="10"/>
+      <c r="AP48" s="13"/>
+      <c r="AQ48" s="13"/>
       <c r="AT48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="15"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="14"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="15"/>
       <c r="J49" s="1"/>
       <c r="M49" s="1"/>
-      <c r="P49" s="12"/>
+      <c r="P49" s="13"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-      <c r="W49" s="12"/>
-      <c r="X49" s="12"/>
-      <c r="Y49" s="12"/>
-      <c r="AD49" s="12"/>
+      <c r="W49" s="13"/>
+      <c r="X49" s="13"/>
+      <c r="Y49" s="13"/>
+      <c r="AD49" s="13"/>
       <c r="AG49" s="1"/>
       <c r="AM49" s="1"/>
-      <c r="AN49" s="9"/>
-      <c r="AP49" s="12"/>
-      <c r="AQ49" s="12"/>
+      <c r="AN49" s="10"/>
+      <c r="AP49" s="13"/>
+      <c r="AQ49" s="13"/>
       <c r="AR49" s="1"/>
       <c r="AT49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="15"/>
-      <c r="C50" s="14"/>
-      <c r="E50" s="14"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="15"/>
+      <c r="E50" s="15"/>
       <c r="J50" s="1"/>
       <c r="M50" s="1"/>
       <c r="P50" s="1"/>
@@ -4465,20 +4367,20 @@
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="AB50" s="12"/>
+      <c r="AB50" s="13"/>
       <c r="AG50" s="1"/>
       <c r="AM50" s="1"/>
-      <c r="AN50" s="9"/>
-      <c r="AP50" s="12"/>
-      <c r="AQ50" s="12"/>
+      <c r="AN50" s="10"/>
+      <c r="AP50" s="13"/>
+      <c r="AQ50" s="13"/>
       <c r="AR50" s="1"/>
       <c r="AT50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="14"/>
-      <c r="E51" s="14"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="15"/>
+      <c r="E51" s="15"/>
       <c r="J51" s="1"/>
       <c r="M51" s="1"/>
       <c r="P51" s="1"/>
@@ -4489,57 +4391,57 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="AG51" s="1"/>
-      <c r="AM51" s="12"/>
-      <c r="AN51" s="9"/>
+      <c r="AM51" s="13"/>
+      <c r="AN51" s="10"/>
       <c r="AP51" s="1"/>
-      <c r="AQ51" s="12"/>
+      <c r="AQ51" s="13"/>
       <c r="AR51" s="1"/>
-      <c r="AT51" s="12"/>
+      <c r="AT51" s="13"/>
     </row>
     <row r="52" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="12"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="13"/>
       <c r="J52" s="1"/>
       <c r="M52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-      <c r="W52" s="12"/>
+      <c r="W52" s="13"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="AG52" s="1"/>
-      <c r="AM52" s="12"/>
+      <c r="AM52" s="13"/>
       <c r="AR52" s="1"/>
-      <c r="AT52" s="12"/>
+      <c r="AT52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="15"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="14"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="15"/>
       <c r="J53" s="1"/>
       <c r="M53" s="1"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
-      <c r="U53" s="12"/>
-      <c r="V53" s="12"/>
+      <c r="U53" s="13"/>
+      <c r="V53" s="13"/>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="AB53" s="12"/>
+      <c r="AB53" s="13"/>
       <c r="AG53" s="1"/>
       <c r="AM53" s="1"/>
       <c r="AT53" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F69" s="12"/>
+      <c r="F69" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4565,144 +4467,144 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="G1" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="H1" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="I1" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="D4" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="E4" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="I4" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>130</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="1"/>
       <c r="D6" s="1"/>
     </row>
@@ -4742,437 +4644,437 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="D1" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="C4" s="30"/>
+      <c r="D4" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="12"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="12"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="12"/>
-      <c r="Y15" s="12"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -5196,10 +5098,10 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -5223,64 +5125,64 @@
       <c r="Y17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="12"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="12"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -5304,10 +5206,10 @@
       <c r="Y20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -5331,97 +5233,97 @@
       <c r="Y21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="12"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="13"/>
+      <c r="U23" s="13"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="12"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="12"/>
-      <c r="U25" s="12"/>
-      <c r="V25" s="12"/>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="12"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="13"/>
+      <c r="U25" s="13"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="29"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -5445,10 +5347,10 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -5472,172 +5374,172 @@
       <c r="Y27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="12"/>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12"/>
-      <c r="Y28" s="12"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="13"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="13"/>
+      <c r="U30" s="13"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
+      <c r="Y30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
-      <c r="W31" s="12"/>
-      <c r="X31" s="12"/>
-      <c r="Y31" s="12"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="13"/>
+      <c r="U31" s="13"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13"/>
+      <c r="X31" s="13"/>
+      <c r="Y31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="29"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
-      <c r="T32" s="12"/>
-      <c r="U32" s="12"/>
-      <c r="V32" s="12"/>
-      <c r="W32" s="12"/>
-      <c r="X32" s="12"/>
-      <c r="Y32" s="12"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
+      <c r="U32" s="13"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13"/>
+      <c r="X32" s="13"/>
+      <c r="Y32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="33"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="33"/>
-      <c r="V33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="33"/>
-      <c r="Y33" s="33"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="34"/>
+      <c r="S33" s="34"/>
+      <c r="T33" s="34"/>
+      <c r="U33" s="34"/>
+      <c r="V33" s="34"/>
+      <c r="W33" s="34"/>
+      <c r="X33" s="34"/>
+      <c r="Y33" s="34"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="29"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -5661,10 +5563,10 @@
       <c r="Y34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -5688,10 +5590,10 @@
       <c r="Y35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="29"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -5715,10 +5617,10 @@
       <c r="Y36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="29"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -5742,10 +5644,10 @@
       <c r="Y37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="29"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="34"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -5769,201 +5671,201 @@
       <c r="Y38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="29"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="34"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="35"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="29"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="34"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="35"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="29"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="34"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="29"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="34"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="29"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="34"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="35"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="29"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="34"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="29"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="34"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="35"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="29"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="34"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="35"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="29"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="34"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="35"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="29"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="34"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="35"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="29"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="34"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="35"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="29"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="34"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="35"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="29"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="34"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="35"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="29"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="34"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="35"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="34"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="35"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="34"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="35"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="29"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="34"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="35"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="29"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="34"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="35"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="34"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="35"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="29"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="34"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="35"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="29"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="34"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="35"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="29"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="34"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="35"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="29"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="34"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="35"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="29"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="34"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="35"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="29"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="34"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="35"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="29"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="34"/>
+      <c r="A64" s="30"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="35"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="29"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="34"/>
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="35"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="29"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="34"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="35"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="29"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="34"/>
+      <c r="A67" s="30"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="35"/>
     </row>
     <row r="68" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="13"/>
+      <c r="A68" s="14"/>
       <c r="B68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="13"/>
+      <c r="A69" s="14"/>
       <c r="B69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="13"/>
+      <c r="A70" s="14"/>
       <c r="B70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="13"/>
+      <c r="A71" s="14"/>
       <c r="B71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="13"/>
+      <c r="A72" s="14"/>
       <c r="B72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="13"/>
+      <c r="A73" s="14"/>
       <c r="B73" s="1"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5979,31 +5881,31 @@
       <c r="B77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="13"/>
+      <c r="A78" s="14"/>
       <c r="B78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="35"/>
+      <c r="A79" s="36"/>
       <c r="B79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="13"/>
+      <c r="A80" s="14"/>
       <c r="B80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="13"/>
+      <c r="A81" s="14"/>
       <c r="B81" s="1"/>
     </row>
     <row r="82" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="13"/>
+      <c r="A82" s="14"/>
       <c r="B82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="13"/>
+      <c r="A83" s="14"/>
       <c r="B83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="13"/>
+      <c r="A84" s="14"/>
       <c r="B84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
+++ b/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Thing" sheetId="1" state="visible" r:id="rId3"/>
@@ -349,7 +349,7 @@
     <t xml:space="preserve">Friend</t>
   </si>
   <si>
-    <t xml:space="preserve">evolve#testchara_evo_stage2#evolution_heart_a</t>
+    <t xml:space="preserve">evolve#testchara_evo_stage2#evolution_heart_a,addDrama_evoDialog</t>
   </si>
   <si>
     <t xml:space="preserve">UniqueChara</t>
@@ -373,7 +373,7 @@
     <t xml:space="preserve">Tester2</t>
   </si>
   <si>
-    <t xml:space="preserve">evolve#testchara_evo_stage3#evolution_heart_b</t>
+    <t xml:space="preserve">evolve#testchara_evo_stage3#evolution_heart_b,addDrama_evoDialog</t>
   </si>
   <si>
     <t xml:space="preserve">testchara_evo_stage3</t>
@@ -433,7 +433,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -482,11 +482,6 @@
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -637,7 +632,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -674,7 +669,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -690,7 +685,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -702,12 +697,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -726,35 +721,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -762,15 +753,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -782,7 +773,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1609,15 +1600,15 @@
       <c r="AX7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="13"/>
+      <c r="I8" s="9"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="13"/>
+      <c r="L8" s="9"/>
       <c r="M8" s="1"/>
       <c r="S8" s="8"/>
       <c r="U8" s="1"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="Y8" s="13"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="Y8" s="9"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
@@ -1629,7 +1620,7 @@
       <c r="AT8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="I9" s="1"/>
@@ -1638,13 +1629,13 @@
       <c r="S9" s="8"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
-      <c r="W9" s="13"/>
-      <c r="Y9" s="13"/>
+      <c r="W9" s="9"/>
+      <c r="Y9" s="9"/>
       <c r="Z9" s="10"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="13"/>
+      <c r="AB9" s="9"/>
       <c r="AC9" s="1"/>
-      <c r="AD9" s="14"/>
+      <c r="AD9" s="13"/>
       <c r="AE9" s="8"/>
       <c r="AF9" s="1"/>
       <c r="AJ9" s="1"/>
@@ -1654,7 +1645,7 @@
       <c r="AX9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="I10" s="1"/>
@@ -1663,13 +1654,13 @@
       <c r="S10" s="8"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
-      <c r="W10" s="13"/>
-      <c r="Y10" s="13"/>
+      <c r="W10" s="9"/>
+      <c r="Y10" s="9"/>
       <c r="Z10" s="10"/>
       <c r="AA10" s="1"/>
-      <c r="AB10" s="13"/>
+      <c r="AB10" s="9"/>
       <c r="AC10" s="1"/>
-      <c r="AD10" s="14"/>
+      <c r="AD10" s="13"/>
       <c r="AE10" s="8"/>
       <c r="AF10" s="1"/>
       <c r="AJ10" s="1"/>
@@ -1679,7 +1670,7 @@
       <c r="AX10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="I11" s="1"/>
@@ -1688,13 +1679,13 @@
       <c r="S11" s="8"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
-      <c r="W11" s="13"/>
-      <c r="Y11" s="13"/>
+      <c r="W11" s="9"/>
+      <c r="Y11" s="9"/>
       <c r="Z11" s="10"/>
       <c r="AA11" s="1"/>
-      <c r="AB11" s="13"/>
+      <c r="AB11" s="9"/>
       <c r="AC11" s="1"/>
-      <c r="AD11" s="14"/>
+      <c r="AD11" s="13"/>
       <c r="AE11" s="8"/>
       <c r="AF11" s="1"/>
       <c r="AJ11" s="1"/>
@@ -1705,7 +1696,7 @@
       <c r="AZ11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="I12" s="1"/>
@@ -1714,13 +1705,13 @@
       <c r="S12" s="8"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-      <c r="W12" s="13"/>
-      <c r="Y12" s="13"/>
+      <c r="W12" s="9"/>
+      <c r="Y12" s="9"/>
       <c r="Z12" s="10"/>
       <c r="AA12" s="1"/>
-      <c r="AB12" s="13"/>
+      <c r="AB12" s="9"/>
       <c r="AC12" s="1"/>
-      <c r="AD12" s="14"/>
+      <c r="AD12" s="13"/>
       <c r="AE12" s="8"/>
       <c r="AF12" s="1"/>
       <c r="AJ12" s="1"/>
@@ -1730,7 +1721,7 @@
       <c r="AX12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="I13" s="1"/>
@@ -1739,13 +1730,13 @@
       <c r="S13" s="8"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
-      <c r="W13" s="13"/>
-      <c r="Y13" s="13"/>
+      <c r="W13" s="9"/>
+      <c r="Y13" s="9"/>
       <c r="Z13" s="10"/>
       <c r="AA13" s="1"/>
-      <c r="AB13" s="13"/>
+      <c r="AB13" s="9"/>
       <c r="AC13" s="1"/>
-      <c r="AD13" s="14"/>
+      <c r="AD13" s="13"/>
       <c r="AE13" s="8"/>
       <c r="AF13" s="1"/>
       <c r="AJ13" s="1"/>
@@ -1755,7 +1746,7 @@
       <c r="AX13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14"/>
+      <c r="A14" s="13"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="I14" s="1"/>
@@ -1764,13 +1755,13 @@
       <c r="S14" s="8"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
-      <c r="W14" s="13"/>
-      <c r="Y14" s="13"/>
+      <c r="W14" s="9"/>
+      <c r="Y14" s="9"/>
       <c r="Z14" s="10"/>
       <c r="AA14" s="1"/>
-      <c r="AB14" s="13"/>
+      <c r="AB14" s="9"/>
       <c r="AC14" s="1"/>
-      <c r="AD14" s="14"/>
+      <c r="AD14" s="13"/>
       <c r="AE14" s="8"/>
       <c r="AF14" s="1"/>
       <c r="AJ14" s="1"/>
@@ -1788,7 +1779,7 @@
       <c r="S15" s="8"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
-      <c r="V15" s="13"/>
+      <c r="V15" s="9"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
@@ -1803,46 +1794,46 @@
       <c r="AX15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="I16" s="13"/>
+      <c r="I16" s="9"/>
       <c r="K16" s="1"/>
       <c r="M16" s="7"/>
       <c r="S16" s="8"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
-      <c r="V16" s="13"/>
-      <c r="W16" s="13"/>
-      <c r="Y16" s="13"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="Y16" s="9"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
       <c r="AF16" s="1"/>
-      <c r="AH16" s="13"/>
-      <c r="AI16" s="14"/>
+      <c r="AH16" s="9"/>
+      <c r="AI16" s="13"/>
       <c r="AJ16" s="1"/>
       <c r="AP16" s="1"/>
       <c r="AT16" s="8"/>
       <c r="AV16" s="1"/>
       <c r="AW16" s="1"/>
       <c r="AX16" s="1"/>
-      <c r="AY16" s="14"/>
+      <c r="AY16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15"/>
-      <c r="D17" s="15"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="D17" s="14"/>
       <c r="E17" s="1"/>
-      <c r="I17" s="13"/>
+      <c r="I17" s="9"/>
       <c r="K17" s="1"/>
       <c r="M17" s="7"/>
       <c r="N17" s="1"/>
       <c r="S17" s="8"/>
       <c r="U17" s="1"/>
-      <c r="V17" s="13"/>
+      <c r="V17" s="9"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
@@ -1850,28 +1841,28 @@
       <c r="AD17" s="1"/>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1"/>
-      <c r="AI17" s="14"/>
+      <c r="AI17" s="13"/>
       <c r="AJ17" s="1"/>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
       <c r="AT17" s="8"/>
-      <c r="AY17" s="14"/>
+      <c r="AY17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="15"/>
+      <c r="D18" s="14"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="13"/>
+      <c r="I18" s="9"/>
       <c r="K18" s="1"/>
       <c r="M18" s="7"/>
       <c r="N18" s="1"/>
       <c r="S18" s="8"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
-      <c r="V18" s="13"/>
-      <c r="Y18" s="13"/>
+      <c r="V18" s="9"/>
+      <c r="Y18" s="9"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
@@ -1879,192 +1870,192 @@
       <c r="AD18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
-      <c r="AI18" s="14"/>
+      <c r="AI18" s="13"/>
       <c r="AJ18" s="1"/>
       <c r="AT18" s="8"/>
       <c r="AV18" s="1"/>
-      <c r="AY18" s="14"/>
+      <c r="AY18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14"/>
+      <c r="A19" s="13"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="I19" s="13"/>
+      <c r="I19" s="9"/>
       <c r="K19" s="1"/>
       <c r="M19" s="7"/>
       <c r="S19" s="8"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
-      <c r="V19" s="13"/>
+      <c r="V19" s="9"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
       <c r="AF19" s="1"/>
-      <c r="AI19" s="14"/>
+      <c r="AI19" s="13"/>
       <c r="AJ19" s="1"/>
       <c r="AP19" s="1"/>
       <c r="AT19" s="8"/>
       <c r="AV19" s="1"/>
       <c r="AW19" s="1"/>
       <c r="AX19" s="1"/>
-      <c r="AY19" s="14"/>
+      <c r="AY19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14"/>
-      <c r="I20" s="13"/>
+      <c r="A20" s="13"/>
+      <c r="I20" s="9"/>
       <c r="K20" s="1"/>
       <c r="M20" s="7"/>
       <c r="S20" s="8"/>
       <c r="U20" s="1"/>
-      <c r="V20" s="13"/>
-      <c r="Y20" s="13"/>
+      <c r="V20" s="9"/>
+      <c r="Y20" s="9"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
       <c r="AF20" s="1"/>
-      <c r="AI20" s="14"/>
+      <c r="AI20" s="13"/>
       <c r="AT20" s="8"/>
-      <c r="AY20" s="14"/>
+      <c r="AY20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14"/>
-      <c r="I21" s="13"/>
+      <c r="A21" s="13"/>
+      <c r="I21" s="9"/>
       <c r="K21" s="1"/>
       <c r="M21" s="7"/>
       <c r="S21" s="8"/>
       <c r="U21" s="1"/>
-      <c r="V21" s="13"/>
+      <c r="V21" s="9"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
       <c r="AF21" s="1"/>
-      <c r="AI21" s="14"/>
+      <c r="AI21" s="13"/>
       <c r="AT21" s="8"/>
-      <c r="AY21" s="14"/>
+      <c r="AY21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14"/>
-      <c r="I22" s="13"/>
+      <c r="A22" s="13"/>
+      <c r="I22" s="9"/>
       <c r="K22" s="1"/>
       <c r="M22" s="7"/>
       <c r="S22" s="8"/>
       <c r="U22" s="1"/>
-      <c r="V22" s="13"/>
-      <c r="Y22" s="13"/>
+      <c r="V22" s="9"/>
+      <c r="Y22" s="9"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
       <c r="AF22" s="1"/>
-      <c r="AI22" s="14"/>
+      <c r="AI22" s="13"/>
       <c r="AT22" s="8"/>
-      <c r="AY22" s="14"/>
+      <c r="AY22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14"/>
-      <c r="I23" s="13"/>
+      <c r="A23" s="13"/>
+      <c r="I23" s="9"/>
       <c r="K23" s="1"/>
       <c r="M23" s="7"/>
       <c r="S23" s="8"/>
       <c r="U23" s="1"/>
-      <c r="V23" s="13"/>
+      <c r="V23" s="9"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
       <c r="AF23" s="1"/>
-      <c r="AI23" s="14"/>
+      <c r="AI23" s="13"/>
       <c r="AT23" s="8"/>
-      <c r="AY23" s="14"/>
+      <c r="AY23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14"/>
-      <c r="I24" s="13"/>
+      <c r="A24" s="13"/>
+      <c r="I24" s="9"/>
       <c r="K24" s="1"/>
       <c r="M24" s="7"/>
       <c r="S24" s="8"/>
       <c r="U24" s="1"/>
-      <c r="V24" s="13"/>
+      <c r="V24" s="9"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
       <c r="AF24" s="1"/>
-      <c r="AI24" s="14"/>
+      <c r="AI24" s="13"/>
       <c r="AT24" s="8"/>
-      <c r="AY24" s="14"/>
+      <c r="AY24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14"/>
-      <c r="I25" s="13"/>
+      <c r="A25" s="13"/>
+      <c r="I25" s="9"/>
       <c r="K25" s="1"/>
       <c r="M25" s="7"/>
       <c r="S25" s="8"/>
       <c r="U25" s="1"/>
-      <c r="V25" s="13"/>
+      <c r="V25" s="9"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
       <c r="AF25" s="1"/>
-      <c r="AI25" s="14"/>
+      <c r="AI25" s="13"/>
       <c r="AT25" s="8"/>
-      <c r="AY25" s="14"/>
+      <c r="AY25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14"/>
-      <c r="I26" s="13"/>
+      <c r="A26" s="13"/>
+      <c r="I26" s="9"/>
       <c r="K26" s="1"/>
       <c r="M26" s="7"/>
       <c r="S26" s="8"/>
       <c r="U26" s="1"/>
-      <c r="V26" s="13"/>
+      <c r="V26" s="9"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
       <c r="AF26" s="1"/>
-      <c r="AI26" s="14"/>
+      <c r="AI26" s="13"/>
       <c r="AT26" s="8"/>
-      <c r="AY26" s="14"/>
+      <c r="AY26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14"/>
-      <c r="I27" s="13"/>
+      <c r="A27" s="13"/>
+      <c r="I27" s="9"/>
       <c r="K27" s="1"/>
       <c r="M27" s="7"/>
       <c r="S27" s="8"/>
       <c r="U27" s="1"/>
-      <c r="V27" s="13"/>
+      <c r="V27" s="9"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
       <c r="AF27" s="1"/>
-      <c r="AI27" s="14"/>
+      <c r="AI27" s="13"/>
       <c r="AT27" s="8"/>
-      <c r="AY27" s="14"/>
+      <c r="AY27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="13"/>
+      <c r="I28" s="9"/>
       <c r="K28" s="1"/>
       <c r="M28" s="7"/>
       <c r="S28" s="8"/>
       <c r="U28" s="1"/>
-      <c r="V28" s="13"/>
-      <c r="Y28" s="13"/>
+      <c r="V28" s="9"/>
+      <c r="Y28" s="9"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
@@ -2074,13 +2065,13 @@
       <c r="AT28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I29" s="13"/>
+      <c r="I29" s="9"/>
       <c r="K29" s="1"/>
       <c r="M29" s="7"/>
       <c r="S29" s="8"/>
       <c r="U29" s="1"/>
-      <c r="V29" s="13"/>
-      <c r="Y29" s="13"/>
+      <c r="V29" s="9"/>
+      <c r="Y29" s="9"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
@@ -2090,13 +2081,13 @@
       <c r="AT29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I30" s="13"/>
+      <c r="I30" s="9"/>
       <c r="K30" s="1"/>
       <c r="M30" s="7"/>
       <c r="S30" s="8"/>
       <c r="U30" s="1"/>
-      <c r="V30" s="13"/>
-      <c r="Y30" s="13"/>
+      <c r="V30" s="9"/>
+      <c r="Y30" s="9"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
@@ -2106,13 +2097,13 @@
       <c r="AT30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I31" s="13"/>
+      <c r="I31" s="9"/>
       <c r="K31" s="1"/>
       <c r="M31" s="7"/>
       <c r="S31" s="8"/>
       <c r="U31" s="1"/>
-      <c r="V31" s="13"/>
-      <c r="Y31" s="13"/>
+      <c r="V31" s="9"/>
+      <c r="Y31" s="9"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -2122,13 +2113,13 @@
       <c r="AT31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I32" s="13"/>
+      <c r="I32" s="9"/>
       <c r="K32" s="1"/>
       <c r="M32" s="7"/>
       <c r="S32" s="8"/>
       <c r="U32" s="1"/>
-      <c r="V32" s="13"/>
-      <c r="Y32" s="13"/>
+      <c r="V32" s="9"/>
+      <c r="Y32" s="9"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
@@ -2138,15 +2129,15 @@
       <c r="AT32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F33" s="13"/>
-      <c r="I33" s="13"/>
+      <c r="F33" s="9"/>
+      <c r="I33" s="9"/>
       <c r="K33" s="1"/>
       <c r="M33" s="7"/>
       <c r="S33" s="8"/>
       <c r="U33" s="1"/>
-      <c r="V33" s="13"/>
-      <c r="W33" s="13"/>
-      <c r="Y33" s="13"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="Y33" s="9"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -2156,15 +2147,15 @@
       <c r="AT33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F34" s="13"/>
-      <c r="I34" s="13"/>
+      <c r="F34" s="9"/>
+      <c r="I34" s="9"/>
       <c r="K34" s="1"/>
       <c r="M34" s="7"/>
       <c r="S34" s="8"/>
       <c r="U34" s="1"/>
-      <c r="V34" s="13"/>
-      <c r="W34" s="13"/>
-      <c r="Y34" s="13"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="Y34" s="9"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
@@ -2174,15 +2165,15 @@
       <c r="AT34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F35" s="13"/>
-      <c r="I35" s="13"/>
+      <c r="F35" s="9"/>
+      <c r="I35" s="9"/>
       <c r="K35" s="1"/>
       <c r="M35" s="7"/>
       <c r="S35" s="8"/>
       <c r="U35" s="1"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="13"/>
-      <c r="Y35" s="13"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="Y35" s="9"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
@@ -2192,15 +2183,15 @@
       <c r="AT35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F36" s="13"/>
-      <c r="I36" s="13"/>
+      <c r="F36" s="9"/>
+      <c r="I36" s="9"/>
       <c r="K36" s="1"/>
       <c r="M36" s="7"/>
       <c r="S36" s="8"/>
       <c r="U36" s="1"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="13"/>
-      <c r="Y36" s="13"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="Y36" s="9"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
@@ -2210,14 +2201,14 @@
       <c r="AT36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F37" s="13"/>
-      <c r="I37" s="13"/>
+      <c r="F37" s="9"/>
+      <c r="I37" s="9"/>
       <c r="K37" s="1"/>
       <c r="M37" s="7"/>
       <c r="S37" s="8"/>
       <c r="U37" s="1"/>
-      <c r="V37" s="13"/>
-      <c r="W37" s="13"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
@@ -2225,17 +2216,17 @@
       <c r="AD37" s="1"/>
       <c r="AF37" s="1"/>
       <c r="AT37" s="8"/>
-      <c r="AY37" s="13"/>
+      <c r="AY37" s="9"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F38" s="13"/>
-      <c r="I38" s="13"/>
+      <c r="F38" s="9"/>
+      <c r="I38" s="9"/>
       <c r="K38" s="1"/>
       <c r="M38" s="7"/>
       <c r="S38" s="8"/>
       <c r="U38" s="1"/>
-      <c r="V38" s="13"/>
-      <c r="W38" s="13"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
@@ -2243,17 +2234,17 @@
       <c r="AD38" s="1"/>
       <c r="AF38" s="1"/>
       <c r="AT38" s="8"/>
-      <c r="AY38" s="13"/>
+      <c r="AY38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F39" s="13"/>
-      <c r="I39" s="13"/>
+      <c r="F39" s="9"/>
+      <c r="I39" s="9"/>
       <c r="K39" s="1"/>
       <c r="M39" s="7"/>
       <c r="S39" s="8"/>
       <c r="U39" s="1"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="13"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
@@ -2261,79 +2252,79 @@
       <c r="AD39" s="1"/>
       <c r="AF39" s="1"/>
       <c r="AT39" s="8"/>
-      <c r="AY39" s="13"/>
+      <c r="AY39" s="9"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="I40" s="13"/>
+      <c r="A40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="I40" s="9"/>
       <c r="K40" s="1"/>
       <c r="M40" s="7"/>
       <c r="S40" s="8"/>
       <c r="U40" s="1"/>
-      <c r="V40" s="13"/>
-      <c r="W40" s="13"/>
-      <c r="Y40" s="13"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="Y40" s="9"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
       <c r="AF40" s="1"/>
-      <c r="AI40" s="13"/>
+      <c r="AI40" s="9"/>
       <c r="AT40" s="8"/>
-      <c r="AY40" s="13"/>
+      <c r="AY40" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="14"/>
-      <c r="F41" s="13"/>
-      <c r="I41" s="13"/>
+      <c r="A41" s="13"/>
+      <c r="F41" s="9"/>
+      <c r="I41" s="9"/>
       <c r="K41" s="1"/>
       <c r="M41" s="7"/>
       <c r="S41" s="8"/>
       <c r="U41" s="1"/>
-      <c r="V41" s="13"/>
-      <c r="W41" s="13"/>
-      <c r="Y41" s="13"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="Y41" s="9"/>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
       <c r="AF41" s="1"/>
-      <c r="AI41" s="14"/>
+      <c r="AI41" s="13"/>
       <c r="AT41" s="8"/>
-      <c r="AY41" s="14"/>
+      <c r="AY41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="14"/>
-      <c r="I42" s="13"/>
+      <c r="A42" s="13"/>
+      <c r="I42" s="9"/>
       <c r="K42" s="1"/>
       <c r="M42" s="7"/>
       <c r="S42" s="8"/>
       <c r="U42" s="1"/>
-      <c r="V42" s="13"/>
-      <c r="W42" s="13"/>
-      <c r="Y42" s="13"/>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
+      <c r="Y42" s="9"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
       <c r="AF42" s="1"/>
-      <c r="AI42" s="14"/>
+      <c r="AI42" s="13"/>
       <c r="AT42" s="8"/>
-      <c r="AY42" s="14"/>
+      <c r="AY42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F43" s="13"/>
+      <c r="F43" s="9"/>
       <c r="I43" s="1"/>
       <c r="K43" s="1"/>
       <c r="M43" s="7"/>
       <c r="S43" s="8"/>
       <c r="U43" s="1"/>
-      <c r="V43" s="13"/>
-      <c r="W43" s="13"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
@@ -2343,20 +2334,20 @@
       <c r="AT43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F44" s="13"/>
+      <c r="F44" s="9"/>
       <c r="I44" s="1"/>
       <c r="K44" s="1"/>
       <c r="M44" s="7"/>
       <c r="S44" s="8"/>
       <c r="U44" s="1"/>
-      <c r="V44" s="13"/>
-      <c r="W44" s="13"/>
+      <c r="V44" s="9"/>
+      <c r="W44" s="9"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
       <c r="AF44" s="1"/>
-      <c r="AH44" s="13"/>
+      <c r="AH44" s="9"/>
       <c r="AT44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2385,8 +2376,8 @@
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
       <c r="AF46" s="1"/>
-      <c r="AL46" s="13"/>
-      <c r="AM46" s="13"/>
+      <c r="AL46" s="9"/>
+      <c r="AM46" s="9"/>
       <c r="AT46" s="8"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2395,7 +2386,7 @@
       <c r="M47" s="7"/>
       <c r="S47" s="8"/>
       <c r="U47" s="1"/>
-      <c r="Y47" s="13"/>
+      <c r="Y47" s="9"/>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
@@ -2413,7 +2404,7 @@
       <c r="S48" s="8"/>
       <c r="U48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AA48" s="13"/>
+      <c r="AA48" s="9"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
@@ -2430,12 +2421,12 @@
       <c r="S49" s="8"/>
       <c r="U49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AA49" s="13"/>
+      <c r="AA49" s="9"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
       <c r="AF49" s="1"/>
-      <c r="AI49" s="13"/>
+      <c r="AI49" s="9"/>
       <c r="AL49" s="1"/>
       <c r="AN49" s="1"/>
       <c r="AP49" s="1"/>
@@ -2453,7 +2444,7 @@
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
       <c r="AF50" s="1"/>
-      <c r="AI50" s="13"/>
+      <c r="AI50" s="9"/>
       <c r="AL50" s="1"/>
       <c r="AN50" s="1"/>
       <c r="AP50" s="1"/>
@@ -2465,14 +2456,14 @@
       <c r="M51" s="7"/>
       <c r="S51" s="8"/>
       <c r="U51" s="1"/>
-      <c r="Y51" s="13"/>
+      <c r="Y51" s="9"/>
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
       <c r="AF51" s="1"/>
-      <c r="AI51" s="13"/>
+      <c r="AI51" s="9"/>
       <c r="AL51" s="1"/>
       <c r="AM51" s="1"/>
       <c r="AN51" s="1"/>
@@ -2486,12 +2477,12 @@
       <c r="S52" s="8"/>
       <c r="U52" s="1"/>
       <c r="Z52" s="1"/>
-      <c r="AA52" s="13"/>
+      <c r="AA52" s="9"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
       <c r="AF52" s="1"/>
-      <c r="AI52" s="13"/>
+      <c r="AI52" s="9"/>
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
       <c r="AN52" s="1"/>
@@ -2510,7 +2501,7 @@
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
       <c r="AF53" s="1"/>
-      <c r="AI53" s="13"/>
+      <c r="AI53" s="9"/>
       <c r="AL53" s="1"/>
       <c r="AM53" s="1"/>
       <c r="AN53" s="1"/>
@@ -2523,14 +2514,14 @@
       <c r="M54" s="7"/>
       <c r="S54" s="8"/>
       <c r="U54" s="1"/>
-      <c r="Y54" s="13"/>
+      <c r="Y54" s="9"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
       <c r="AF54" s="1"/>
-      <c r="AI54" s="13"/>
+      <c r="AI54" s="9"/>
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
       <c r="AN54" s="1"/>
@@ -2544,12 +2535,12 @@
       <c r="S55" s="8"/>
       <c r="U55" s="1"/>
       <c r="Z55" s="1"/>
-      <c r="AA55" s="13"/>
+      <c r="AA55" s="9"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
       <c r="AF55" s="1"/>
-      <c r="AI55" s="13"/>
+      <c r="AI55" s="9"/>
       <c r="AL55" s="1"/>
       <c r="AM55" s="1"/>
       <c r="AN55" s="1"/>
@@ -2568,7 +2559,7 @@
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
       <c r="AF56" s="1"/>
-      <c r="AI56" s="13"/>
+      <c r="AI56" s="9"/>
       <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
       <c r="AN56" s="1"/>
@@ -2581,14 +2572,14 @@
       <c r="M57" s="7"/>
       <c r="S57" s="8"/>
       <c r="U57" s="1"/>
-      <c r="Y57" s="13"/>
+      <c r="Y57" s="9"/>
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
       <c r="AF57" s="1"/>
-      <c r="AI57" s="13"/>
+      <c r="AI57" s="9"/>
       <c r="AL57" s="1"/>
       <c r="AM57" s="1"/>
       <c r="AN57" s="1"/>
@@ -2607,7 +2598,7 @@
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
       <c r="AF58" s="1"/>
-      <c r="AI58" s="13"/>
+      <c r="AI58" s="9"/>
       <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
       <c r="AN58" s="1"/>
@@ -2620,14 +2611,14 @@
       <c r="M59" s="7"/>
       <c r="S59" s="8"/>
       <c r="U59" s="1"/>
-      <c r="Y59" s="13"/>
+      <c r="Y59" s="9"/>
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
       <c r="AF59" s="1"/>
-      <c r="AI59" s="13"/>
+      <c r="AI59" s="9"/>
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
       <c r="AN59" s="1"/>
@@ -2646,7 +2637,7 @@
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
       <c r="AF60" s="1"/>
-      <c r="AI60" s="13"/>
+      <c r="AI60" s="9"/>
       <c r="AL60" s="1"/>
       <c r="AM60" s="1"/>
       <c r="AP60" s="1"/>
@@ -2664,7 +2655,7 @@
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
       <c r="AF61" s="1"/>
-      <c r="AI61" s="13"/>
+      <c r="AI61" s="9"/>
       <c r="AL61" s="1"/>
       <c r="AM61" s="1"/>
       <c r="AP61" s="1"/>
@@ -2676,16 +2667,16 @@
       <c r="M62" s="7"/>
       <c r="S62" s="8"/>
       <c r="U62" s="1"/>
-      <c r="Y62" s="13"/>
+      <c r="Y62" s="9"/>
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
       <c r="AF62" s="1"/>
-      <c r="AI62" s="13"/>
-      <c r="AL62" s="13"/>
-      <c r="AM62" s="13"/>
+      <c r="AI62" s="9"/>
+      <c r="AL62" s="9"/>
+      <c r="AM62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I63" s="1"/>
@@ -2693,21 +2684,21 @@
       <c r="M63" s="7"/>
       <c r="S63" s="8"/>
       <c r="U63" s="1"/>
-      <c r="Y63" s="13"/>
+      <c r="Y63" s="9"/>
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
       <c r="AF63" s="1"/>
-      <c r="AI63" s="13"/>
-      <c r="AK63" s="13"/>
+      <c r="AI63" s="9"/>
+      <c r="AK63" s="9"/>
       <c r="AL63" s="1"/>
       <c r="AM63" s="1"/>
     </row>
     <row r="64" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="16"/>
-      <c r="C64" s="15"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="14"/>
       <c r="E64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -2716,12 +2707,12 @@
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
-      <c r="S64" s="17"/>
+      <c r="S64" s="16"/>
       <c r="U64" s="1"/>
-      <c r="V64" s="18"/>
-      <c r="W64" s="13"/>
-      <c r="Z64" s="13"/>
-      <c r="AA64" s="13"/>
+      <c r="V64" s="17"/>
+      <c r="W64" s="9"/>
+      <c r="Z64" s="9"/>
+      <c r="AA64" s="9"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
@@ -2734,8 +2725,8 @@
       <c r="AT64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="16"/>
-      <c r="C65" s="15"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="14"/>
       <c r="E65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -2744,12 +2735,12 @@
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
-      <c r="S65" s="17"/>
+      <c r="S65" s="16"/>
       <c r="U65" s="1"/>
-      <c r="V65" s="18"/>
-      <c r="W65" s="13"/>
-      <c r="Z65" s="13"/>
-      <c r="AA65" s="13"/>
+      <c r="V65" s="17"/>
+      <c r="W65" s="9"/>
+      <c r="Z65" s="9"/>
+      <c r="AA65" s="9"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
@@ -2762,8 +2753,8 @@
       <c r="AT65" s="8"/>
     </row>
     <row r="66" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="16"/>
-      <c r="C66" s="15"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="14"/>
       <c r="E66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -2772,12 +2763,12 @@
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
-      <c r="S66" s="17"/>
+      <c r="S66" s="16"/>
       <c r="U66" s="1"/>
-      <c r="V66" s="18"/>
-      <c r="W66" s="13"/>
-      <c r="Z66" s="13"/>
-      <c r="AA66" s="13"/>
+      <c r="V66" s="17"/>
+      <c r="W66" s="9"/>
+      <c r="Z66" s="9"/>
+      <c r="AA66" s="9"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
@@ -2793,7 +2784,7 @@
       <c r="I67" s="1"/>
       <c r="K67" s="1"/>
       <c r="M67" s="1"/>
-      <c r="S67" s="17"/>
+      <c r="S67" s="16"/>
       <c r="U67" s="1"/>
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
@@ -2807,7 +2798,7 @@
       <c r="I68" s="1"/>
       <c r="K68" s="1"/>
       <c r="M68" s="1"/>
-      <c r="S68" s="17"/>
+      <c r="S68" s="16"/>
       <c r="U68" s="1"/>
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
@@ -2819,11 +2810,11 @@
       <c r="AT68" s="8"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D69" s="15"/>
+      <c r="D69" s="14"/>
       <c r="I69" s="1"/>
       <c r="K69" s="1"/>
       <c r="M69" s="1"/>
-      <c r="S69" s="17"/>
+      <c r="S69" s="16"/>
       <c r="U69" s="1"/>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
@@ -3237,319 +3228,319 @@
       <c r="AW3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="15" t="n">
         <v>7869001</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="13" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13" t="s">
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
       <c r="M4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13" t="s">
+      <c r="N4" s="9"/>
+      <c r="O4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="P4" s="13" t="n">
+      <c r="P4" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" s="13" t="n">
+      <c r="Q4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="13" t="n">
+      <c r="R4" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13" t="s">
+      <c r="T4" s="9"/>
+      <c r="U4" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="V4" s="13" t="s">
+      <c r="V4" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="W4" s="13" t="s">
+      <c r="W4" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="X4" s="13" t="s">
+      <c r="X4" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="Y4" s="13" t="s">
+      <c r="Y4" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13" t="s">
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="13" t="s">
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="AF4" s="13"/>
-      <c r="AG4" s="13" t="s">
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="13"/>
-      <c r="AI4" s="13"/>
-      <c r="AJ4" s="13"/>
-      <c r="AK4" s="13"/>
-      <c r="AL4" s="13"/>
-      <c r="AM4" s="13"/>
+      <c r="AH4" s="9"/>
+      <c r="AI4" s="9"/>
+      <c r="AJ4" s="9"/>
+      <c r="AK4" s="9"/>
+      <c r="AL4" s="9"/>
+      <c r="AM4" s="9"/>
       <c r="AN4" s="10"/>
-      <c r="AO4" s="13"/>
-      <c r="AP4" s="13"/>
-      <c r="AQ4" s="13"/>
-      <c r="AR4" s="13"/>
-      <c r="AS4" s="13"/>
-      <c r="AT4" s="13"/>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="13"/>
-      <c r="AW4" s="13"/>
+      <c r="AO4" s="9"/>
+      <c r="AP4" s="9"/>
+      <c r="AQ4" s="9"/>
+      <c r="AR4" s="9"/>
+      <c r="AS4" s="9"/>
+      <c r="AT4" s="9"/>
+      <c r="AU4" s="9"/>
+      <c r="AV4" s="9"/>
+      <c r="AW4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="15" t="n">
         <v>7869002</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
       <c r="M5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13" t="s">
+      <c r="N5" s="9"/>
+      <c r="O5" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="P5" s="13" t="n">
+      <c r="P5" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="Q5" s="13" t="n">
+      <c r="Q5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="13" t="n">
+      <c r="R5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="S5" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13" t="s">
+      <c r="T5" s="9"/>
+      <c r="U5" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="V5" s="13" t="s">
+      <c r="V5" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="W5" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="X5" s="13" t="s">
+      <c r="X5" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Y5" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13" t="s">
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="AD5" s="13"/>
-      <c r="AE5" s="13" t="s">
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="AF5" s="13"/>
-      <c r="AG5" s="13" t="s">
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AH5" s="13"/>
-      <c r="AI5" s="13"/>
-      <c r="AJ5" s="13"/>
-      <c r="AK5" s="13"/>
-      <c r="AL5" s="13"/>
-      <c r="AM5" s="13"/>
+      <c r="AH5" s="9"/>
+      <c r="AI5" s="9"/>
+      <c r="AJ5" s="9"/>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
       <c r="AN5" s="10"/>
-      <c r="AO5" s="13"/>
-      <c r="AP5" s="13"/>
-      <c r="AQ5" s="13"/>
-      <c r="AR5" s="13"/>
-      <c r="AS5" s="13"/>
-      <c r="AT5" s="13"/>
-      <c r="AU5" s="13"/>
-      <c r="AV5" s="13"/>
-      <c r="AW5" s="13"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>7869003</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="13" t="s">
+      <c r="C6" s="14"/>
+      <c r="D6" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
       <c r="M6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13" t="s">
+      <c r="N6" s="9"/>
+      <c r="O6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="P6" s="13" t="n">
+      <c r="P6" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="Q6" s="13" t="n">
+      <c r="Q6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="13" t="n">
+      <c r="R6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="S6" s="13" t="s">
+      <c r="S6" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13" t="s">
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="W6" s="13" t="s">
+      <c r="W6" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="X6" s="13" t="s">
+      <c r="X6" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="Y6" s="13" t="s">
+      <c r="Y6" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13" t="s">
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13" t="s">
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13" t="s">
+      <c r="AF6" s="9"/>
+      <c r="AG6" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="13"/>
-      <c r="AO6" s="13"/>
-      <c r="AP6" s="13"/>
-      <c r="AQ6" s="13"/>
-      <c r="AR6" s="13"/>
-      <c r="AS6" s="13"/>
-      <c r="AT6" s="13"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="13"/>
+      <c r="AH6" s="9"/>
+      <c r="AI6" s="9"/>
+      <c r="AJ6" s="9"/>
+      <c r="AK6" s="9"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="16"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="13"/>
-      <c r="J7" s="13"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="9"/>
+      <c r="J7" s="9"/>
       <c r="M7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="V7" s="19"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="V7" s="18"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="13"/>
+      <c r="Y7" s="9"/>
       <c r="Z7" s="1"/>
-      <c r="AB7" s="13"/>
-      <c r="AD7" s="13"/>
+      <c r="AB7" s="9"/>
+      <c r="AD7" s="9"/>
       <c r="AE7" s="1"/>
-      <c r="AG7" s="13"/>
-      <c r="AR7" s="13"/>
+      <c r="AG7" s="9"/>
+      <c r="AR7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="13"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="9"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="13"/>
+      <c r="J8" s="9"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
       <c r="T8" s="1"/>
-      <c r="V8" s="19"/>
+      <c r="V8" s="18"/>
       <c r="W8" s="1"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
       <c r="AA8" s="1"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
       <c r="AF8" s="1"/>
-      <c r="AG8" s="13"/>
+      <c r="AG8" s="9"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
@@ -3559,7 +3550,7 @@
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
-      <c r="AR8" s="13"/>
+      <c r="AR8" s="9"/>
       <c r="AS8" s="1"/>
       <c r="AT8" s="1"/>
       <c r="AU8" s="1"/>
@@ -3567,439 +3558,439 @@
       <c r="AW8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="16"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="13"/>
-      <c r="J9" s="13"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="9"/>
+      <c r="J9" s="9"/>
       <c r="M9" s="1"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="V9" s="19"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="V9" s="18"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AB9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AG9" s="13"/>
-      <c r="AR9" s="13"/>
+      <c r="AB9" s="9"/>
+      <c r="AD9" s="9"/>
+      <c r="AG9" s="9"/>
+      <c r="AR9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="16"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="13"/>
-      <c r="J10" s="13"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="9"/>
+      <c r="J10" s="9"/>
       <c r="M10" s="1"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="V10" s="19"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="V10" s="18"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AB10" s="13"/>
-      <c r="AD10" s="13"/>
-      <c r="AG10" s="13"/>
-      <c r="AR10" s="13"/>
+      <c r="AB10" s="9"/>
+      <c r="AD10" s="9"/>
+      <c r="AG10" s="9"/>
+      <c r="AR10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="16"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="13"/>
-      <c r="J11" s="13"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="9"/>
+      <c r="J11" s="9"/>
       <c r="M11" s="1"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="V11" s="19"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="V11" s="18"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AB11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AG11" s="13"/>
-      <c r="AR11" s="13"/>
+      <c r="AB11" s="9"/>
+      <c r="AD11" s="9"/>
+      <c r="AG11" s="9"/>
+      <c r="AR11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="16"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="13"/>
-      <c r="J12" s="13"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="9"/>
+      <c r="J12" s="9"/>
       <c r="M12" s="1"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="V12" s="19"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="V12" s="18"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-      <c r="AB12" s="13"/>
-      <c r="AD12" s="13"/>
-      <c r="AG12" s="13"/>
-      <c r="AR12" s="13"/>
+      <c r="AB12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AG12" s="9"/>
+      <c r="AR12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="15"/>
-      <c r="J13" s="13"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="14"/>
+      <c r="J13" s="9"/>
       <c r="M13" s="1"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="13"/>
+      <c r="S13" s="9"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
-      <c r="AB13" s="13"/>
-      <c r="AD13" s="13"/>
-      <c r="AE13" s="13"/>
-      <c r="AG13" s="13"/>
+      <c r="AB13" s="9"/>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="9"/>
+      <c r="AG13" s="9"/>
       <c r="AQ13" s="1"/>
       <c r="AR13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="16"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="15"/>
-      <c r="J14" s="13"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="14"/>
+      <c r="J14" s="9"/>
       <c r="M14" s="1"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
       <c r="R14" s="1"/>
-      <c r="S14" s="13"/>
+      <c r="S14" s="9"/>
       <c r="W14" s="1"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="13"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="9"/>
       <c r="Z14" s="1"/>
-      <c r="AB14" s="13"/>
-      <c r="AD14" s="13"/>
-      <c r="AE14" s="13"/>
-      <c r="AG14" s="13"/>
+      <c r="AB14" s="9"/>
+      <c r="AD14" s="9"/>
+      <c r="AE14" s="9"/>
+      <c r="AG14" s="9"/>
       <c r="AQ14" s="1"/>
       <c r="AR14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="16"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="15"/>
-      <c r="J15" s="13"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="14"/>
+      <c r="J15" s="9"/>
       <c r="M15" s="1"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="13"/>
+      <c r="S15" s="9"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
-      <c r="AB15" s="13"/>
-      <c r="AD15" s="13"/>
-      <c r="AE15" s="13"/>
-      <c r="AG15" s="13"/>
+      <c r="AB15" s="9"/>
+      <c r="AD15" s="9"/>
+      <c r="AE15" s="9"/>
+      <c r="AG15" s="9"/>
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="16"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="15"/>
-      <c r="J16" s="13"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="14"/>
+      <c r="J16" s="9"/>
       <c r="M16" s="1"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
       <c r="R16" s="1"/>
-      <c r="S16" s="13"/>
+      <c r="S16" s="9"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-      <c r="Y16" s="13"/>
+      <c r="Y16" s="9"/>
       <c r="Z16" s="1"/>
-      <c r="AB16" s="13"/>
-      <c r="AD16" s="13"/>
-      <c r="AE16" s="13"/>
-      <c r="AG16" s="13"/>
+      <c r="AB16" s="9"/>
+      <c r="AD16" s="9"/>
+      <c r="AE16" s="9"/>
+      <c r="AG16" s="9"/>
       <c r="AQ16" s="1"/>
       <c r="AR16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="16"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="15"/>
-      <c r="J17" s="13"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="14"/>
+      <c r="J17" s="9"/>
       <c r="M17" s="1"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
       <c r="R17" s="1"/>
-      <c r="S17" s="13"/>
+      <c r="S17" s="9"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-      <c r="AB17" s="13"/>
-      <c r="AD17" s="13"/>
-      <c r="AE17" s="13"/>
-      <c r="AG17" s="13"/>
+      <c r="AB17" s="9"/>
+      <c r="AD17" s="9"/>
+      <c r="AE17" s="9"/>
+      <c r="AG17" s="9"/>
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="16"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="15"/>
-      <c r="J18" s="13"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="14"/>
+      <c r="J18" s="9"/>
       <c r="M18" s="1"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
       <c r="R18" s="1"/>
-      <c r="S18" s="13"/>
+      <c r="S18" s="9"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
-      <c r="AB18" s="13"/>
-      <c r="AD18" s="13"/>
-      <c r="AE18" s="13"/>
-      <c r="AG18" s="13"/>
+      <c r="AB18" s="9"/>
+      <c r="AD18" s="9"/>
+      <c r="AE18" s="9"/>
+      <c r="AG18" s="9"/>
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="16"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="15"/>
-      <c r="J19" s="13"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="14"/>
+      <c r="J19" s="9"/>
       <c r="M19" s="1"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
       <c r="R19" s="1"/>
-      <c r="S19" s="13"/>
+      <c r="S19" s="9"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
-      <c r="AB19" s="13"/>
-      <c r="AD19" s="13"/>
-      <c r="AE19" s="13"/>
-      <c r="AG19" s="13"/>
+      <c r="AB19" s="9"/>
+      <c r="AD19" s="9"/>
+      <c r="AE19" s="9"/>
+      <c r="AG19" s="9"/>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="16"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="13"/>
-      <c r="J20" s="13"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="9"/>
+      <c r="J20" s="9"/>
       <c r="M20" s="1"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
       <c r="R20" s="1"/>
-      <c r="S20" s="13"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="13"/>
+      <c r="S20" s="9"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="9"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
-      <c r="AB20" s="13"/>
-      <c r="AD20" s="13"/>
-      <c r="AG20" s="13"/>
+      <c r="AB20" s="9"/>
+      <c r="AD20" s="9"/>
+      <c r="AG20" s="9"/>
       <c r="AQ20" s="1"/>
       <c r="AR20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="16"/>
-      <c r="C21" s="23"/>
-      <c r="J21" s="13"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="22"/>
+      <c r="J21" s="9"/>
       <c r="M21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="13"/>
+      <c r="Q21" s="9"/>
       <c r="R21" s="1"/>
-      <c r="S21" s="13"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="13"/>
+      <c r="S21" s="9"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="9"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="13"/>
-      <c r="AA21" s="13"/>
+      <c r="Z21" s="9"/>
+      <c r="AA21" s="9"/>
       <c r="AE21" s="1"/>
-      <c r="AG21" s="13"/>
+      <c r="AG21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="16"/>
-      <c r="C22" s="23"/>
-      <c r="J22" s="13"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="22"/>
+      <c r="J22" s="9"/>
       <c r="M22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="13"/>
+      <c r="Q22" s="9"/>
       <c r="R22" s="1"/>
-      <c r="S22" s="13"/>
-      <c r="V22" s="18"/>
-      <c r="W22" s="13"/>
+      <c r="S22" s="9"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="9"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="13"/>
-      <c r="AA22" s="13"/>
-      <c r="AB22" s="13"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
       <c r="AE22" s="1"/>
-      <c r="AG22" s="13"/>
+      <c r="AG22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="16"/>
-      <c r="C23" s="23"/>
-      <c r="J23" s="13"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="22"/>
+      <c r="J23" s="9"/>
       <c r="M23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="13"/>
+      <c r="Q23" s="9"/>
       <c r="R23" s="1"/>
-      <c r="S23" s="13"/>
-      <c r="V23" s="18"/>
-      <c r="W23" s="13"/>
+      <c r="S23" s="9"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="9"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="Z23" s="13"/>
-      <c r="AA23" s="13"/>
-      <c r="AB23" s="13"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
       <c r="AE23" s="1"/>
-      <c r="AG23" s="13"/>
+      <c r="AG23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="16"/>
-      <c r="C24" s="23"/>
-      <c r="J24" s="13"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="22"/>
+      <c r="J24" s="9"/>
       <c r="M24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="13"/>
+      <c r="Q24" s="9"/>
       <c r="R24" s="1"/>
-      <c r="S24" s="13"/>
-      <c r="V24" s="18"/>
-      <c r="W24" s="13"/>
+      <c r="S24" s="9"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="9"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="13"/>
-      <c r="AA24" s="13"/>
-      <c r="AB24" s="13"/>
+      <c r="Z24" s="9"/>
+      <c r="AA24" s="9"/>
+      <c r="AB24" s="9"/>
       <c r="AE24" s="1"/>
-      <c r="AG24" s="13"/>
+      <c r="AG24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="16"/>
-      <c r="C25" s="23"/>
-      <c r="J25" s="13"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="22"/>
+      <c r="J25" s="9"/>
       <c r="M25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="13"/>
+      <c r="Q25" s="9"/>
       <c r="R25" s="1"/>
-      <c r="S25" s="13"/>
-      <c r="V25" s="18"/>
-      <c r="W25" s="13"/>
+      <c r="S25" s="9"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="9"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="Z25" s="13"/>
-      <c r="AA25" s="13"/>
-      <c r="AB25" s="13"/>
+      <c r="Z25" s="9"/>
+      <c r="AA25" s="9"/>
+      <c r="AB25" s="9"/>
       <c r="AE25" s="1"/>
-      <c r="AG25" s="13"/>
+      <c r="AG25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16"/>
-      <c r="C26" s="23"/>
-      <c r="J26" s="13"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="22"/>
+      <c r="J26" s="9"/>
       <c r="M26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="13"/>
+      <c r="Q26" s="9"/>
       <c r="R26" s="1"/>
-      <c r="S26" s="13"/>
-      <c r="V26" s="18"/>
-      <c r="W26" s="13"/>
+      <c r="S26" s="9"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="9"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="Z26" s="13"/>
-      <c r="AA26" s="13"/>
-      <c r="AB26" s="13"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
       <c r="AE26" s="1"/>
-      <c r="AG26" s="13"/>
+      <c r="AG26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16"/>
-      <c r="C27" s="23"/>
-      <c r="J27" s="13"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="22"/>
+      <c r="J27" s="9"/>
       <c r="M27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="13"/>
+      <c r="Q27" s="9"/>
       <c r="R27" s="1"/>
-      <c r="S27" s="13"/>
-      <c r="V27" s="18"/>
-      <c r="W27" s="13"/>
+      <c r="S27" s="9"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="9"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="13"/>
-      <c r="AA27" s="13"/>
-      <c r="AB27" s="13"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
       <c r="AE27" s="1"/>
-      <c r="AG27" s="13"/>
+      <c r="AG27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="16"/>
-      <c r="C28" s="23"/>
-      <c r="J28" s="13"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="22"/>
+      <c r="J28" s="9"/>
       <c r="M28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="13"/>
+      <c r="Q28" s="9"/>
       <c r="R28" s="1"/>
-      <c r="S28" s="13"/>
-      <c r="V28" s="18"/>
-      <c r="W28" s="13"/>
+      <c r="S28" s="9"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="9"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="AB28" s="13"/>
-      <c r="AD28" s="13"/>
+      <c r="AB28" s="9"/>
+      <c r="AD28" s="9"/>
       <c r="AE28" s="1"/>
-      <c r="AG28" s="13"/>
+      <c r="AG28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="16"/>
-      <c r="C29" s="23"/>
-      <c r="J29" s="13"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="22"/>
+      <c r="J29" s="9"/>
       <c r="M29" s="1"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="13"/>
+      <c r="Q29" s="9"/>
       <c r="R29" s="1"/>
-      <c r="S29" s="13"/>
-      <c r="V29" s="18"/>
-      <c r="W29" s="13"/>
+      <c r="S29" s="9"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="9"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="13"/>
-      <c r="AB29" s="13"/>
-      <c r="AD29" s="13"/>
+      <c r="Y29" s="9"/>
+      <c r="AB29" s="9"/>
+      <c r="AD29" s="9"/>
       <c r="AE29" s="1"/>
-      <c r="AG29" s="13"/>
+      <c r="AG29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="16"/>
-      <c r="C30" s="13"/>
-      <c r="J30" s="13"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="9"/>
+      <c r="J30" s="9"/>
       <c r="M30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="V30" s="18"/>
+      <c r="V30" s="17"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
@@ -4008,161 +3999,161 @@
       <c r="AL30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="16"/>
-      <c r="C31" s="13"/>
-      <c r="J31" s="13"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="9"/>
+      <c r="J31" s="9"/>
       <c r="M31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="V31" s="18"/>
+      <c r="V31" s="17"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="AA31" s="1"/>
-      <c r="AB31" s="13"/>
+      <c r="AB31" s="9"/>
       <c r="AG31" s="1"/>
       <c r="AL31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="13"/>
-      <c r="J32" s="13"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="9"/>
+      <c r="J32" s="9"/>
       <c r="M32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="V32" s="18"/>
+      <c r="V32" s="17"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-      <c r="Y32" s="13"/>
+      <c r="Y32" s="9"/>
       <c r="AA32" s="1"/>
       <c r="AG32" s="1"/>
       <c r="AL32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="16"/>
-      <c r="C33" s="15"/>
-      <c r="J33" s="13"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="14"/>
+      <c r="J33" s="9"/>
       <c r="M33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="V33" s="18"/>
-      <c r="W33" s="13"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="9"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="AG33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="16"/>
-      <c r="C34" s="15"/>
-      <c r="J34" s="13"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="14"/>
+      <c r="J34" s="9"/>
       <c r="M34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="V34" s="18"/>
-      <c r="W34" s="13"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="9"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="AB34" s="13"/>
+      <c r="AB34" s="9"/>
       <c r="AG34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="16"/>
-      <c r="C35" s="15"/>
-      <c r="J35" s="13"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="14"/>
+      <c r="J35" s="9"/>
       <c r="M35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="V35" s="18"/>
-      <c r="W35" s="13"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="9"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="AD35" s="13"/>
+      <c r="AD35" s="9"/>
       <c r="AG35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="15"/>
-      <c r="J36" s="13"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="14"/>
+      <c r="J36" s="9"/>
       <c r="M36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="V36" s="18"/>
-      <c r="W36" s="13"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="9"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="AG36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="15"/>
-      <c r="J37" s="13"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="14"/>
+      <c r="J37" s="9"/>
       <c r="M37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-      <c r="V37" s="18"/>
-      <c r="W37" s="13"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="9"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
       <c r="AG37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="15"/>
-      <c r="J38" s="13"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="14"/>
+      <c r="J38" s="9"/>
       <c r="M38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-      <c r="V38" s="18"/>
-      <c r="W38" s="13"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="9"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="AB38" s="13"/>
+      <c r="AB38" s="9"/>
       <c r="AG38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="15"/>
-      <c r="J39" s="13"/>
+      <c r="A39" s="13"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="14"/>
+      <c r="J39" s="9"/>
       <c r="M39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
-      <c r="V39" s="18"/>
-      <c r="W39" s="13"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="9"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="AB39" s="13"/>
-      <c r="AD39" s="13"/>
+      <c r="AB39" s="9"/>
+      <c r="AD39" s="9"/>
       <c r="AG39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="16"/>
-      <c r="C40" s="15"/>
-      <c r="J40" s="13"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="14"/>
+      <c r="J40" s="9"/>
       <c r="M40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -4174,190 +4165,190 @@
       <c r="AG40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="16"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="13"/>
-      <c r="J41" s="13"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="9"/>
+      <c r="J41" s="9"/>
       <c r="M41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="W41" s="1"/>
-      <c r="X41" s="13"/>
+      <c r="X41" s="9"/>
       <c r="Y41" s="1"/>
-      <c r="AD41" s="13"/>
+      <c r="AD41" s="9"/>
       <c r="AG41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="16"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="13"/>
-      <c r="J42" s="13"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="9"/>
+      <c r="J42" s="9"/>
       <c r="M42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="W42" s="1"/>
-      <c r="X42" s="13"/>
+      <c r="X42" s="9"/>
       <c r="Y42" s="1"/>
-      <c r="AD42" s="13"/>
+      <c r="AD42" s="9"/>
       <c r="AG42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="16"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="13"/>
-      <c r="J43" s="13"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="9"/>
+      <c r="J43" s="9"/>
       <c r="M43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="W43" s="1"/>
-      <c r="X43" s="13"/>
+      <c r="X43" s="9"/>
       <c r="Y43" s="1"/>
-      <c r="AD43" s="13"/>
+      <c r="AD43" s="9"/>
       <c r="AG43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="16"/>
-      <c r="C44" s="15"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="14"/>
       <c r="J44" s="1"/>
       <c r="M44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
-      <c r="V44" s="18"/>
-      <c r="W44" s="13"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="9"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
-      <c r="Z44" s="13"/>
-      <c r="AA44" s="13"/>
-      <c r="AB44" s="13"/>
+      <c r="Z44" s="9"/>
+      <c r="AA44" s="9"/>
+      <c r="AB44" s="9"/>
       <c r="AG44" s="1"/>
       <c r="AL44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="16"/>
-      <c r="C45" s="15"/>
-      <c r="E45" s="15"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="14"/>
+      <c r="E45" s="14"/>
       <c r="J45" s="1"/>
       <c r="M45" s="1"/>
-      <c r="P45" s="13"/>
+      <c r="P45" s="9"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
-      <c r="U45" s="13"/>
-      <c r="V45" s="13"/>
-      <c r="W45" s="13"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
       <c r="X45" s="1"/>
-      <c r="Y45" s="13"/>
-      <c r="AD45" s="13"/>
+      <c r="Y45" s="9"/>
+      <c r="AD45" s="9"/>
       <c r="AG45" s="1"/>
       <c r="AM45" s="1"/>
       <c r="AN45" s="10"/>
       <c r="AP45" s="1"/>
-      <c r="AQ45" s="13"/>
+      <c r="AQ45" s="9"/>
       <c r="AR45" s="1"/>
       <c r="AT45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="16"/>
-      <c r="C46" s="15"/>
-      <c r="E46" s="15"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="14"/>
+      <c r="E46" s="14"/>
       <c r="J46" s="1"/>
       <c r="M46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-      <c r="V46" s="13"/>
-      <c r="W46" s="13"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
       <c r="X46" s="1"/>
-      <c r="Y46" s="13"/>
+      <c r="Y46" s="9"/>
       <c r="AG46" s="1"/>
       <c r="AM46" s="1"/>
       <c r="AN46" s="10"/>
-      <c r="AP46" s="13"/>
-      <c r="AQ46" s="13"/>
+      <c r="AP46" s="9"/>
+      <c r="AQ46" s="9"/>
       <c r="AR46" s="1"/>
       <c r="AT46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="16"/>
-      <c r="C47" s="15"/>
-      <c r="E47" s="15"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="14"/>
+      <c r="E47" s="14"/>
       <c r="J47" s="1"/>
       <c r="M47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="13"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="9"/>
       <c r="X47" s="1"/>
-      <c r="Y47" s="13"/>
+      <c r="Y47" s="9"/>
       <c r="AG47" s="1"/>
       <c r="AM47" s="1"/>
       <c r="AN47" s="10"/>
-      <c r="AP47" s="13"/>
+      <c r="AP47" s="9"/>
       <c r="AQ47" s="1"/>
       <c r="AR47" s="1"/>
       <c r="AT47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="16"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="14"/>
       <c r="J48" s="1"/>
       <c r="M48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
+      <c r="V48" s="9"/>
+      <c r="W48" s="9"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="AB48" s="13"/>
+      <c r="AB48" s="9"/>
       <c r="AG48" s="1"/>
       <c r="AM48" s="1"/>
       <c r="AN48" s="10"/>
-      <c r="AP48" s="13"/>
-      <c r="AQ48" s="13"/>
+      <c r="AP48" s="9"/>
+      <c r="AQ48" s="9"/>
       <c r="AT48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="16"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="14"/>
       <c r="J49" s="1"/>
       <c r="M49" s="1"/>
-      <c r="P49" s="13"/>
+      <c r="P49" s="9"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="13"/>
-      <c r="AD49" s="13"/>
+      <c r="W49" s="9"/>
+      <c r="X49" s="9"/>
+      <c r="Y49" s="9"/>
+      <c r="AD49" s="9"/>
       <c r="AG49" s="1"/>
       <c r="AM49" s="1"/>
       <c r="AN49" s="10"/>
-      <c r="AP49" s="13"/>
-      <c r="AQ49" s="13"/>
+      <c r="AP49" s="9"/>
+      <c r="AQ49" s="9"/>
       <c r="AR49" s="1"/>
       <c r="AT49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="16"/>
-      <c r="C50" s="15"/>
-      <c r="E50" s="15"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="14"/>
+      <c r="E50" s="14"/>
       <c r="J50" s="1"/>
       <c r="M50" s="1"/>
       <c r="P50" s="1"/>
@@ -4367,20 +4358,20 @@
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="AB50" s="13"/>
+      <c r="AB50" s="9"/>
       <c r="AG50" s="1"/>
       <c r="AM50" s="1"/>
       <c r="AN50" s="10"/>
-      <c r="AP50" s="13"/>
-      <c r="AQ50" s="13"/>
+      <c r="AP50" s="9"/>
+      <c r="AQ50" s="9"/>
       <c r="AR50" s="1"/>
       <c r="AT50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="15"/>
-      <c r="E51" s="15"/>
+      <c r="A51" s="9"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="14"/>
+      <c r="E51" s="14"/>
       <c r="J51" s="1"/>
       <c r="M51" s="1"/>
       <c r="P51" s="1"/>
@@ -4391,57 +4382,57 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="AG51" s="1"/>
-      <c r="AM51" s="13"/>
+      <c r="AM51" s="9"/>
       <c r="AN51" s="10"/>
       <c r="AP51" s="1"/>
-      <c r="AQ51" s="13"/>
+      <c r="AQ51" s="9"/>
       <c r="AR51" s="1"/>
-      <c r="AT51" s="13"/>
+      <c r="AT51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="13"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="9"/>
       <c r="J52" s="1"/>
       <c r="M52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-      <c r="W52" s="13"/>
+      <c r="W52" s="9"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="AG52" s="1"/>
-      <c r="AM52" s="13"/>
+      <c r="AM52" s="9"/>
       <c r="AR52" s="1"/>
-      <c r="AT52" s="13"/>
+      <c r="AT52" s="9"/>
     </row>
     <row r="53" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="16"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="14"/>
       <c r="J53" s="1"/>
       <c r="M53" s="1"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
-      <c r="U53" s="13"/>
-      <c r="V53" s="13"/>
+      <c r="U53" s="9"/>
+      <c r="V53" s="9"/>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="AB53" s="13"/>
+      <c r="AB53" s="9"/>
       <c r="AG53" s="1"/>
       <c r="AM53" s="1"/>
       <c r="AT53" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F69" s="13"/>
+      <c r="F69" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4467,133 +4458,133 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="24" t="s">
         <v>128</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -4601,10 +4592,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27"/>
+      <c r="A5" s="26"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="1"/>
       <c r="D6" s="1"/>
     </row>
@@ -4644,437 +4635,437 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30" t="s">
+      <c r="C4" s="29"/>
+      <c r="D4" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="13"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
-      <c r="U12" s="13"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="13"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
-      <c r="W13" s="13"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="13"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="13"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -5098,10 +5089,10 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -5125,64 +5116,64 @@
       <c r="Y17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="30"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="13"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -5206,10 +5197,10 @@
       <c r="Y20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -5233,97 +5224,97 @@
       <c r="Y21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
-      <c r="U23" s="13"/>
-      <c r="V23" s="13"/>
-      <c r="W23" s="13"/>
-      <c r="X23" s="13"/>
-      <c r="Y23" s="13"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
-      <c r="U24" s="13"/>
-      <c r="V24" s="13"/>
-      <c r="W24" s="13"/>
-      <c r="X24" s="13"/>
-      <c r="Y24" s="13"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="13"/>
-      <c r="T25" s="13"/>
-      <c r="U25" s="13"/>
-      <c r="V25" s="13"/>
-      <c r="W25" s="13"/>
-      <c r="X25" s="13"/>
-      <c r="Y25" s="13"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
+      <c r="A26" s="29"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -5347,10 +5338,10 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -5374,172 +5365,172 @@
       <c r="Y27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="13"/>
-      <c r="U28" s="13"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="13"/>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="13"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="13"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="13"/>
-      <c r="R30" s="13"/>
-      <c r="S30" s="13"/>
-      <c r="T30" s="13"/>
-      <c r="U30" s="13"/>
-      <c r="V30" s="13"/>
-      <c r="W30" s="13"/>
-      <c r="X30" s="13"/>
-      <c r="Y30" s="13"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="30"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="13"/>
-      <c r="U31" s="13"/>
-      <c r="V31" s="13"/>
-      <c r="W31" s="13"/>
-      <c r="X31" s="13"/>
-      <c r="Y31" s="13"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="13"/>
-      <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="13"/>
-      <c r="U32" s="13"/>
-      <c r="V32" s="13"/>
-      <c r="W32" s="13"/>
-      <c r="X32" s="13"/>
-      <c r="Y32" s="13"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="34"/>
-      <c r="V33" s="34"/>
-      <c r="W33" s="34"/>
-      <c r="X33" s="34"/>
-      <c r="Y33" s="34"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="33"/>
+      <c r="S33" s="33"/>
+      <c r="T33" s="33"/>
+      <c r="U33" s="33"/>
+      <c r="V33" s="33"/>
+      <c r="W33" s="33"/>
+      <c r="X33" s="33"/>
+      <c r="Y33" s="33"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -5563,10 +5554,10 @@
       <c r="Y34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -5590,10 +5581,10 @@
       <c r="Y35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="30"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -5617,10 +5608,10 @@
       <c r="Y36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -5644,10 +5635,10 @@
       <c r="Y37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="30"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="35"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -5671,201 +5662,201 @@
       <c r="Y38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="30"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="35"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="34"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="30"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="35"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="34"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="35"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="34"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="35"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="34"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="35"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="34"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="35"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="34"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="35"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="34"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="35"/>
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="34"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="35"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="34"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="30"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="35"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="34"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="30"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="35"/>
+      <c r="A49" s="29"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="34"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="30"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="35"/>
+      <c r="A50" s="29"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="34"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="30"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="35"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="34"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="30"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="35"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="34"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="35"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="34"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="30"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="35"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="34"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="35"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="34"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="35"/>
+      <c r="A56" s="29"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="34"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="35"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="34"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="30"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="35"/>
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="34"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="35"/>
+      <c r="A59" s="29"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="34"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="30"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="35"/>
+      <c r="A60" s="29"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="34"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="35"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="34"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="30"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="35"/>
+      <c r="A62" s="29"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="34"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="35"/>
+      <c r="A63" s="29"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="34"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="30"/>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="35"/>
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="34"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="30"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="30"/>
-      <c r="D65" s="35"/>
+      <c r="A65" s="29"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="34"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="30"/>
-      <c r="B66" s="30"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="35"/>
+      <c r="A66" s="29"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="34"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="30"/>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="35"/>
+      <c r="A67" s="29"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="34"/>
     </row>
     <row r="68" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="14"/>
+      <c r="A68" s="13"/>
       <c r="B68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="14"/>
+      <c r="A69" s="13"/>
       <c r="B69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="14"/>
+      <c r="A70" s="13"/>
       <c r="B70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="14"/>
+      <c r="A71" s="13"/>
       <c r="B71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="14"/>
+      <c r="A72" s="13"/>
       <c r="B72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="14"/>
+      <c r="A73" s="13"/>
       <c r="B73" s="1"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5881,31 +5872,31 @@
       <c r="B77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="14"/>
+      <c r="A78" s="13"/>
       <c r="B78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="36"/>
+      <c r="A79" s="35"/>
       <c r="B79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="14"/>
+      <c r="A80" s="13"/>
       <c r="B80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="14"/>
+      <c r="A81" s="13"/>
       <c r="B81" s="1"/>
     </row>
     <row r="82" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="14"/>
+      <c r="A82" s="13"/>
       <c r="B82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="14"/>
+      <c r="A83" s="13"/>
       <c r="B83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="14"/>
+      <c r="A84" s="13"/>
       <c r="B84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
+++ b/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Thing" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Chara" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Game" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="General" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Thing" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Chara" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Game" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="General" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="136">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -208,7 +208,7 @@
     <t xml:space="preserve">Evolution Heart Type A</t>
   </si>
   <si>
-    <t xml:space="preserve">_item</t>
+    <t xml:space="preserve">currency</t>
   </si>
   <si>
     <t xml:space="preserve">@obj_S flat</t>
@@ -220,136 +220,139 @@
     <t xml:space="preserve"> -</t>
   </si>
   <si>
+    <t xml:space="preserve">diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EvolutionHeart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noWish,noShop,noDrop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSERT DESCRIPTION HERE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evolution_heart_b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evolution Heart Type B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evolution_heart_c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evolution Heart Type C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aka_JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idActor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tiles_snow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hostility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">race</t>
+  </si>
+  <si>
+    <t xml:space="preserve">job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tactics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aiIdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aiParam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actCombat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mainElement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gachaFilter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actIdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hobbies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idText</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moveAnime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!meat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">norland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testchara_evo_stage1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Miko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@chara</t>
+  </si>
+  <si>
     <t xml:space="preserve">meat</t>
   </si>
   <si>
-    <t xml:space="preserve">Currency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noWish,noShop,noDrop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">supply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSERT DESCRIPTION HERE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evolution_heart_b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evolution Heart Type B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evolution_heart_c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evolution Heart Type C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aka_JP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">idActor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tiles_snow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hostility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">biome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">race</t>
-  </si>
-  <si>
-    <t xml:space="preserve">job</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tactics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aiIdle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aiParam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">actCombat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mainElement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">loot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gachaFilter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">actIdle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">works</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hobbies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">idText</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moveAnime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!meat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">norland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">none</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testchara_evo_stage1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tester1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@chara</t>
-  </si>
-  <si>
     <t xml:space="preserve">Friend</t>
   </si>
   <si>
-    <t xml:space="preserve">evolve#testchara_evo_stage2#evolution_heart_a,addDrama_evoDialog</t>
+    <t xml:space="preserve">evolve#testchara_evo_stage2#evolution_heart_a,evolve#testchara_evo_stage3#evolution_heart_b</t>
   </si>
   <si>
     <t xml:space="preserve">UniqueChara</t>
@@ -370,16 +373,16 @@
     <t xml:space="preserve">testchara_evo_stage2</t>
   </si>
   <si>
-    <t xml:space="preserve">Tester2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evolve#testchara_evo_stage3#evolution_heart_b,addDrama_evoDialog</t>
+    <t xml:space="preserve">Awakened Dragon Miko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evolve#testchara_evo_stage3#evolution_heart_b</t>
   </si>
   <si>
     <t xml:space="preserve">testchara_evo_stage3</t>
   </si>
   <si>
-    <t xml:space="preserve">Tester3</t>
+    <t xml:space="preserve">Water Goddess</t>
   </si>
   <si>
     <t xml:space="preserve">group</t>
@@ -415,13 +418,19 @@
     <t xml:space="preserve">#1 the #2 has evolved into #3!</t>
   </si>
   <si>
-    <t xml:space="preserve">daEvolve</t>
+    <t xml:space="preserve">evolutionConfirmation</t>
   </si>
   <si>
     <t xml:space="preserve">info</t>
   </si>
   <si>
-    <t xml:space="preserve">Use #3 to evolve #1 into #2?</t>
+    <t xml:space="preserve">Are you sure you want to evolve #1 into a #2?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evolveChara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evolve into #1.</t>
   </si>
 </sst>
 </file>
@@ -433,7 +442,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -476,6 +485,11 @@
       <name val="Cascadia Code"/>
       <family val="3"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -565,6 +579,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFC9A26D"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FFC9A26D"/>
       <name val="Arial"/>
@@ -632,7 +652,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -661,11 +681,23 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -673,20 +705,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -697,12 +717,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -721,31 +741,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -753,15 +777,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -773,7 +797,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -850,119 +874,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AZ69"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.79"/>
@@ -1383,23 +1301,23 @@
       <c r="F4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="7" t="s">
         <v>61</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="9" t="s">
         <v>63</v>
       </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Y4" s="9" t="s">
+      <c r="Y4" s="7" t="s">
         <v>65</v>
       </c>
       <c r="Z4" s="10"/>
@@ -1415,21 +1333,21 @@
       <c r="AD4" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AE4" s="8"/>
+      <c r="AE4" s="9"/>
       <c r="AF4" s="1" t="n">
         <v>200</v>
       </c>
       <c r="AG4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" s="9" t="s">
+      <c r="AH4" s="12" t="s">
         <v>66</v>
       </c>
       <c r="AJ4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AP4" s="1"/>
-      <c r="AT4" s="8" t="s">
+      <c r="AT4" s="9" t="s">
         <v>67</v>
       </c>
       <c r="AV4" s="1" t="s">
@@ -1437,7 +1355,7 @@
       </c>
       <c r="AW4" s="1"/>
       <c r="AX4" s="1"/>
-      <c r="AZ4" s="12" t="s">
+      <c r="AZ4" s="13" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1450,23 +1368,23 @@
       <c r="F5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="7" t="s">
         <v>61</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="S5" s="9" t="s">
         <v>63</v>
       </c>
       <c r="T5" s="1"/>
       <c r="U5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Y5" s="9" t="s">
+      <c r="Y5" s="7" t="s">
         <v>65</v>
       </c>
       <c r="Z5" s="10"/>
@@ -1482,21 +1400,21 @@
       <c r="AD5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AE5" s="8"/>
+      <c r="AE5" s="9"/>
       <c r="AF5" s="1" t="n">
         <v>200</v>
       </c>
       <c r="AG5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="9" t="s">
+      <c r="AH5" s="7" t="s">
         <v>66</v>
       </c>
       <c r="AJ5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AP5" s="1"/>
-      <c r="AT5" s="8" t="s">
+      <c r="AT5" s="9" t="s">
         <v>67</v>
       </c>
       <c r="AV5" s="1" t="s">
@@ -1504,7 +1422,7 @@
       </c>
       <c r="AW5" s="1"/>
       <c r="AX5" s="1"/>
-      <c r="AZ5" s="12" t="s">
+      <c r="AZ5" s="13" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1517,23 +1435,23 @@
       <c r="F6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="7" t="s">
         <v>61</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="S6" s="9" t="s">
         <v>63</v>
       </c>
       <c r="T6" s="1"/>
       <c r="U6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Y6" s="9" t="s">
+      <c r="Y6" s="7" t="s">
         <v>65</v>
       </c>
       <c r="Z6" s="10"/>
@@ -1549,21 +1467,21 @@
       <c r="AD6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AE6" s="8"/>
+      <c r="AE6" s="9"/>
       <c r="AF6" s="1" t="n">
         <v>200</v>
       </c>
       <c r="AG6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH6" s="9" t="s">
+      <c r="AH6" s="7" t="s">
         <v>66</v>
       </c>
       <c r="AJ6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AP6" s="1"/>
-      <c r="AT6" s="8" t="s">
+      <c r="AT6" s="9" t="s">
         <v>67</v>
       </c>
       <c r="AV6" s="1" t="s">
@@ -1571,7 +1489,7 @@
       </c>
       <c r="AW6" s="1"/>
       <c r="AX6" s="1"/>
-      <c r="AZ6" s="12" t="s">
+      <c r="AZ6" s="13" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1580,8 +1498,8 @@
       <c r="C7" s="1"/>
       <c r="I7" s="10"/>
       <c r="K7" s="1"/>
-      <c r="M7" s="7"/>
-      <c r="S7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="S7" s="9"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="Z7" s="10"/>
@@ -1589,26 +1507,26 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-      <c r="AE7" s="8"/>
+      <c r="AE7" s="9"/>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
       <c r="AJ7" s="1"/>
       <c r="AP7" s="1"/>
-      <c r="AT7" s="8"/>
+      <c r="AT7" s="9"/>
       <c r="AV7" s="1"/>
       <c r="AW7" s="1"/>
       <c r="AX7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="9"/>
+      <c r="I8" s="12"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="9"/>
+      <c r="L8" s="12"/>
       <c r="M8" s="1"/>
-      <c r="S8" s="8"/>
+      <c r="S8" s="9"/>
       <c r="U8" s="1"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="Y8" s="9"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="Y8" s="12"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
@@ -1617,26 +1535,26 @@
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
       <c r="AJ8" s="1"/>
-      <c r="AT8" s="8"/>
+      <c r="AT8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13"/>
+      <c r="A9" s="14"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="M9" s="7"/>
-      <c r="S9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="S9" s="9"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
-      <c r="W9" s="9"/>
-      <c r="Y9" s="9"/>
+      <c r="W9" s="12"/>
+      <c r="Y9" s="12"/>
       <c r="Z9" s="10"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="9"/>
+      <c r="AB9" s="12"/>
       <c r="AC9" s="1"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="8"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="9"/>
       <c r="AF9" s="1"/>
       <c r="AJ9" s="1"/>
       <c r="AP9" s="1"/>
@@ -1645,23 +1563,23 @@
       <c r="AX9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13"/>
+      <c r="A10" s="14"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="I10" s="1"/>
       <c r="K10" s="1"/>
-      <c r="M10" s="7"/>
-      <c r="S10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="S10" s="9"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
-      <c r="W10" s="9"/>
-      <c r="Y10" s="9"/>
+      <c r="W10" s="12"/>
+      <c r="Y10" s="12"/>
       <c r="Z10" s="10"/>
       <c r="AA10" s="1"/>
-      <c r="AB10" s="9"/>
+      <c r="AB10" s="12"/>
       <c r="AC10" s="1"/>
-      <c r="AD10" s="13"/>
-      <c r="AE10" s="8"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="9"/>
       <c r="AF10" s="1"/>
       <c r="AJ10" s="1"/>
       <c r="AP10" s="1"/>
@@ -1670,23 +1588,23 @@
       <c r="AX10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13"/>
+      <c r="A11" s="14"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="I11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="M11" s="7"/>
-      <c r="S11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="S11" s="9"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
-      <c r="W11" s="9"/>
-      <c r="Y11" s="9"/>
+      <c r="W11" s="12"/>
+      <c r="Y11" s="12"/>
       <c r="Z11" s="10"/>
       <c r="AA11" s="1"/>
-      <c r="AB11" s="9"/>
+      <c r="AB11" s="12"/>
       <c r="AC11" s="1"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="8"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="9"/>
       <c r="AF11" s="1"/>
       <c r="AJ11" s="1"/>
       <c r="AP11" s="1"/>
@@ -1696,23 +1614,23 @@
       <c r="AZ11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="I12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="M12" s="7"/>
-      <c r="S12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="S12" s="9"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-      <c r="W12" s="9"/>
-      <c r="Y12" s="9"/>
+      <c r="W12" s="12"/>
+      <c r="Y12" s="12"/>
       <c r="Z12" s="10"/>
       <c r="AA12" s="1"/>
-      <c r="AB12" s="9"/>
+      <c r="AB12" s="12"/>
       <c r="AC12" s="1"/>
-      <c r="AD12" s="13"/>
-      <c r="AE12" s="8"/>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="9"/>
       <c r="AF12" s="1"/>
       <c r="AJ12" s="1"/>
       <c r="AP12" s="1"/>
@@ -1721,23 +1639,23 @@
       <c r="AX12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="I13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="M13" s="7"/>
-      <c r="S13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="S13" s="9"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
-      <c r="W13" s="9"/>
-      <c r="Y13" s="9"/>
+      <c r="W13" s="12"/>
+      <c r="Y13" s="12"/>
       <c r="Z13" s="10"/>
       <c r="AA13" s="1"/>
-      <c r="AB13" s="9"/>
+      <c r="AB13" s="12"/>
       <c r="AC13" s="1"/>
-      <c r="AD13" s="13"/>
-      <c r="AE13" s="8"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="9"/>
       <c r="AF13" s="1"/>
       <c r="AJ13" s="1"/>
       <c r="AP13" s="1"/>
@@ -1746,23 +1664,23 @@
       <c r="AX13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13"/>
+      <c r="A14" s="14"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="I14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="M14" s="7"/>
-      <c r="S14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="S14" s="9"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
-      <c r="W14" s="9"/>
-      <c r="Y14" s="9"/>
+      <c r="W14" s="12"/>
+      <c r="Y14" s="12"/>
       <c r="Z14" s="10"/>
       <c r="AA14" s="1"/>
-      <c r="AB14" s="9"/>
+      <c r="AB14" s="12"/>
       <c r="AC14" s="1"/>
-      <c r="AD14" s="13"/>
-      <c r="AE14" s="8"/>
+      <c r="AD14" s="14"/>
+      <c r="AE14" s="9"/>
       <c r="AF14" s="1"/>
       <c r="AJ14" s="1"/>
       <c r="AP14" s="1"/>
@@ -1775,11 +1693,11 @@
       <c r="C15" s="1"/>
       <c r="I15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="M15" s="7"/>
-      <c r="S15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="S15" s="9"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
-      <c r="V15" s="9"/>
+      <c r="V15" s="12"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
@@ -1788,52 +1706,52 @@
       <c r="AF15" s="1"/>
       <c r="AJ15" s="1"/>
       <c r="AP15" s="1"/>
-      <c r="AT15" s="8"/>
+      <c r="AT15" s="9"/>
       <c r="AV15" s="1"/>
       <c r="AW15" s="1"/>
       <c r="AX15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13"/>
+      <c r="A16" s="14"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="I16" s="9"/>
+      <c r="I16" s="12"/>
       <c r="K16" s="1"/>
-      <c r="M16" s="7"/>
-      <c r="S16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="S16" s="9"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="Y16" s="9"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="Y16" s="12"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
       <c r="AF16" s="1"/>
-      <c r="AH16" s="9"/>
-      <c r="AI16" s="13"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="14"/>
       <c r="AJ16" s="1"/>
       <c r="AP16" s="1"/>
-      <c r="AT16" s="8"/>
+      <c r="AT16" s="9"/>
       <c r="AV16" s="1"/>
       <c r="AW16" s="1"/>
       <c r="AX16" s="1"/>
-      <c r="AY16" s="13"/>
+      <c r="AY16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="15"/>
+      <c r="D17" s="15"/>
       <c r="E17" s="1"/>
-      <c r="I17" s="9"/>
+      <c r="I17" s="12"/>
       <c r="K17" s="1"/>
-      <c r="M17" s="7"/>
+      <c r="M17" s="8"/>
       <c r="N17" s="1"/>
-      <c r="S17" s="8"/>
+      <c r="S17" s="9"/>
       <c r="U17" s="1"/>
-      <c r="V17" s="9"/>
+      <c r="V17" s="12"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
@@ -1841,28 +1759,28 @@
       <c r="AD17" s="1"/>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1"/>
-      <c r="AI17" s="13"/>
+      <c r="AI17" s="14"/>
       <c r="AJ17" s="1"/>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
-      <c r="AT17" s="8"/>
-      <c r="AY17" s="13"/>
+      <c r="AT17" s="9"/>
+      <c r="AY17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="14"/>
+      <c r="D18" s="15"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="9"/>
+      <c r="I18" s="12"/>
       <c r="K18" s="1"/>
-      <c r="M18" s="7"/>
+      <c r="M18" s="8"/>
       <c r="N18" s="1"/>
-      <c r="S18" s="8"/>
+      <c r="S18" s="9"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
-      <c r="V18" s="9"/>
-      <c r="Y18" s="9"/>
+      <c r="V18" s="12"/>
+      <c r="Y18" s="12"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
@@ -1870,491 +1788,491 @@
       <c r="AD18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
-      <c r="AI18" s="13"/>
+      <c r="AI18" s="14"/>
       <c r="AJ18" s="1"/>
-      <c r="AT18" s="8"/>
+      <c r="AT18" s="9"/>
       <c r="AV18" s="1"/>
-      <c r="AY18" s="13"/>
+      <c r="AY18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="I19" s="9"/>
+      <c r="I19" s="12"/>
       <c r="K19" s="1"/>
-      <c r="M19" s="7"/>
-      <c r="S19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="S19" s="9"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
-      <c r="V19" s="9"/>
+      <c r="V19" s="12"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
       <c r="AF19" s="1"/>
-      <c r="AI19" s="13"/>
+      <c r="AI19" s="14"/>
       <c r="AJ19" s="1"/>
       <c r="AP19" s="1"/>
-      <c r="AT19" s="8"/>
+      <c r="AT19" s="9"/>
       <c r="AV19" s="1"/>
       <c r="AW19" s="1"/>
       <c r="AX19" s="1"/>
-      <c r="AY19" s="13"/>
+      <c r="AY19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13"/>
-      <c r="I20" s="9"/>
+      <c r="A20" s="14"/>
+      <c r="I20" s="12"/>
       <c r="K20" s="1"/>
-      <c r="M20" s="7"/>
-      <c r="S20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="S20" s="9"/>
       <c r="U20" s="1"/>
-      <c r="V20" s="9"/>
-      <c r="Y20" s="9"/>
+      <c r="V20" s="12"/>
+      <c r="Y20" s="12"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
       <c r="AF20" s="1"/>
-      <c r="AI20" s="13"/>
-      <c r="AT20" s="8"/>
-      <c r="AY20" s="13"/>
+      <c r="AI20" s="14"/>
+      <c r="AT20" s="9"/>
+      <c r="AY20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13"/>
-      <c r="I21" s="9"/>
+      <c r="A21" s="14"/>
+      <c r="I21" s="12"/>
       <c r="K21" s="1"/>
-      <c r="M21" s="7"/>
-      <c r="S21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="S21" s="9"/>
       <c r="U21" s="1"/>
-      <c r="V21" s="9"/>
+      <c r="V21" s="12"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
       <c r="AF21" s="1"/>
-      <c r="AI21" s="13"/>
-      <c r="AT21" s="8"/>
-      <c r="AY21" s="13"/>
+      <c r="AI21" s="14"/>
+      <c r="AT21" s="9"/>
+      <c r="AY21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="I22" s="9"/>
+      <c r="A22" s="14"/>
+      <c r="I22" s="12"/>
       <c r="K22" s="1"/>
-      <c r="M22" s="7"/>
-      <c r="S22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="S22" s="9"/>
       <c r="U22" s="1"/>
-      <c r="V22" s="9"/>
-      <c r="Y22" s="9"/>
+      <c r="V22" s="12"/>
+      <c r="Y22" s="12"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
       <c r="AF22" s="1"/>
-      <c r="AI22" s="13"/>
-      <c r="AT22" s="8"/>
-      <c r="AY22" s="13"/>
+      <c r="AI22" s="14"/>
+      <c r="AT22" s="9"/>
+      <c r="AY22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="I23" s="9"/>
+      <c r="A23" s="14"/>
+      <c r="I23" s="12"/>
       <c r="K23" s="1"/>
-      <c r="M23" s="7"/>
-      <c r="S23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="S23" s="9"/>
       <c r="U23" s="1"/>
-      <c r="V23" s="9"/>
+      <c r="V23" s="12"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
       <c r="AF23" s="1"/>
-      <c r="AI23" s="13"/>
-      <c r="AT23" s="8"/>
-      <c r="AY23" s="13"/>
+      <c r="AI23" s="14"/>
+      <c r="AT23" s="9"/>
+      <c r="AY23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="I24" s="9"/>
+      <c r="A24" s="14"/>
+      <c r="I24" s="12"/>
       <c r="K24" s="1"/>
-      <c r="M24" s="7"/>
-      <c r="S24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="S24" s="9"/>
       <c r="U24" s="1"/>
-      <c r="V24" s="9"/>
+      <c r="V24" s="12"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
       <c r="AF24" s="1"/>
-      <c r="AI24" s="13"/>
-      <c r="AT24" s="8"/>
-      <c r="AY24" s="13"/>
+      <c r="AI24" s="14"/>
+      <c r="AT24" s="9"/>
+      <c r="AY24" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
-      <c r="I25" s="9"/>
+      <c r="A25" s="14"/>
+      <c r="I25" s="12"/>
       <c r="K25" s="1"/>
-      <c r="M25" s="7"/>
-      <c r="S25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="S25" s="9"/>
       <c r="U25" s="1"/>
-      <c r="V25" s="9"/>
+      <c r="V25" s="12"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
       <c r="AF25" s="1"/>
-      <c r="AI25" s="13"/>
-      <c r="AT25" s="8"/>
-      <c r="AY25" s="13"/>
+      <c r="AI25" s="14"/>
+      <c r="AT25" s="9"/>
+      <c r="AY25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13"/>
-      <c r="I26" s="9"/>
+      <c r="A26" s="14"/>
+      <c r="I26" s="12"/>
       <c r="K26" s="1"/>
-      <c r="M26" s="7"/>
-      <c r="S26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="S26" s="9"/>
       <c r="U26" s="1"/>
-      <c r="V26" s="9"/>
+      <c r="V26" s="12"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
       <c r="AF26" s="1"/>
-      <c r="AI26" s="13"/>
-      <c r="AT26" s="8"/>
-      <c r="AY26" s="13"/>
+      <c r="AI26" s="14"/>
+      <c r="AT26" s="9"/>
+      <c r="AY26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="I27" s="9"/>
+      <c r="A27" s="14"/>
+      <c r="I27" s="12"/>
       <c r="K27" s="1"/>
-      <c r="M27" s="7"/>
-      <c r="S27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="S27" s="9"/>
       <c r="U27" s="1"/>
-      <c r="V27" s="9"/>
+      <c r="V27" s="12"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
       <c r="AF27" s="1"/>
-      <c r="AI27" s="13"/>
-      <c r="AT27" s="8"/>
-      <c r="AY27" s="13"/>
+      <c r="AI27" s="14"/>
+      <c r="AT27" s="9"/>
+      <c r="AY27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="9"/>
+      <c r="I28" s="12"/>
       <c r="K28" s="1"/>
-      <c r="M28" s="7"/>
-      <c r="S28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="S28" s="9"/>
       <c r="U28" s="1"/>
-      <c r="V28" s="9"/>
-      <c r="Y28" s="9"/>
+      <c r="V28" s="12"/>
+      <c r="Y28" s="12"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
       <c r="AF28" s="1"/>
-      <c r="AT28" s="8"/>
+      <c r="AT28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I29" s="9"/>
+      <c r="I29" s="12"/>
       <c r="K29" s="1"/>
-      <c r="M29" s="7"/>
-      <c r="S29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="S29" s="9"/>
       <c r="U29" s="1"/>
-      <c r="V29" s="9"/>
-      <c r="Y29" s="9"/>
+      <c r="V29" s="12"/>
+      <c r="Y29" s="12"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
       <c r="AF29" s="1"/>
-      <c r="AT29" s="8"/>
+      <c r="AT29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I30" s="9"/>
+      <c r="I30" s="12"/>
       <c r="K30" s="1"/>
-      <c r="M30" s="7"/>
-      <c r="S30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="S30" s="9"/>
       <c r="U30" s="1"/>
-      <c r="V30" s="9"/>
-      <c r="Y30" s="9"/>
+      <c r="V30" s="12"/>
+      <c r="Y30" s="12"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
       <c r="AF30" s="1"/>
-      <c r="AT30" s="8"/>
+      <c r="AT30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I31" s="9"/>
+      <c r="I31" s="12"/>
       <c r="K31" s="1"/>
-      <c r="M31" s="7"/>
-      <c r="S31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="S31" s="9"/>
       <c r="U31" s="1"/>
-      <c r="V31" s="9"/>
-      <c r="Y31" s="9"/>
+      <c r="V31" s="12"/>
+      <c r="Y31" s="12"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
       <c r="AF31" s="1"/>
-      <c r="AT31" s="8"/>
+      <c r="AT31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I32" s="9"/>
+      <c r="I32" s="12"/>
       <c r="K32" s="1"/>
-      <c r="M32" s="7"/>
-      <c r="S32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="S32" s="9"/>
       <c r="U32" s="1"/>
-      <c r="V32" s="9"/>
-      <c r="Y32" s="9"/>
+      <c r="V32" s="12"/>
+      <c r="Y32" s="12"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
       <c r="AF32" s="1"/>
-      <c r="AT32" s="8"/>
+      <c r="AT32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F33" s="9"/>
-      <c r="I33" s="9"/>
+      <c r="F33" s="12"/>
+      <c r="I33" s="12"/>
       <c r="K33" s="1"/>
-      <c r="M33" s="7"/>
-      <c r="S33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="S33" s="9"/>
       <c r="U33" s="1"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="Y33" s="9"/>
+      <c r="V33" s="12"/>
+      <c r="W33" s="12"/>
+      <c r="Y33" s="12"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
       <c r="AF33" s="1"/>
-      <c r="AT33" s="8"/>
+      <c r="AT33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F34" s="9"/>
-      <c r="I34" s="9"/>
+      <c r="F34" s="12"/>
+      <c r="I34" s="12"/>
       <c r="K34" s="1"/>
-      <c r="M34" s="7"/>
-      <c r="S34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="S34" s="9"/>
       <c r="U34" s="1"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="Y34" s="9"/>
+      <c r="V34" s="12"/>
+      <c r="W34" s="12"/>
+      <c r="Y34" s="12"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
       <c r="AF34" s="1"/>
-      <c r="AT34" s="8"/>
+      <c r="AT34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F35" s="9"/>
-      <c r="I35" s="9"/>
+      <c r="F35" s="12"/>
+      <c r="I35" s="12"/>
       <c r="K35" s="1"/>
-      <c r="M35" s="7"/>
-      <c r="S35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="S35" s="9"/>
       <c r="U35" s="1"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="Y35" s="9"/>
+      <c r="V35" s="12"/>
+      <c r="W35" s="12"/>
+      <c r="Y35" s="12"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
       <c r="AF35" s="1"/>
-      <c r="AT35" s="8"/>
+      <c r="AT35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F36" s="9"/>
-      <c r="I36" s="9"/>
+      <c r="F36" s="12"/>
+      <c r="I36" s="12"/>
       <c r="K36" s="1"/>
-      <c r="M36" s="7"/>
-      <c r="S36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="S36" s="9"/>
       <c r="U36" s="1"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="Y36" s="9"/>
+      <c r="V36" s="12"/>
+      <c r="W36" s="12"/>
+      <c r="Y36" s="12"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
       <c r="AF36" s="1"/>
-      <c r="AT36" s="8"/>
+      <c r="AT36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F37" s="9"/>
-      <c r="I37" s="9"/>
+      <c r="F37" s="12"/>
+      <c r="I37" s="12"/>
       <c r="K37" s="1"/>
-      <c r="M37" s="7"/>
-      <c r="S37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="S37" s="9"/>
       <c r="U37" s="1"/>
-      <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
       <c r="AF37" s="1"/>
-      <c r="AT37" s="8"/>
-      <c r="AY37" s="9"/>
+      <c r="AT37" s="9"/>
+      <c r="AY37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F38" s="9"/>
-      <c r="I38" s="9"/>
+      <c r="F38" s="12"/>
+      <c r="I38" s="12"/>
       <c r="K38" s="1"/>
-      <c r="M38" s="7"/>
-      <c r="S38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="S38" s="9"/>
       <c r="U38" s="1"/>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
       <c r="AF38" s="1"/>
-      <c r="AT38" s="8"/>
-      <c r="AY38" s="9"/>
+      <c r="AT38" s="9"/>
+      <c r="AY38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F39" s="9"/>
-      <c r="I39" s="9"/>
+      <c r="F39" s="12"/>
+      <c r="I39" s="12"/>
       <c r="K39" s="1"/>
-      <c r="M39" s="7"/>
-      <c r="S39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="S39" s="9"/>
       <c r="U39" s="1"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
+      <c r="V39" s="12"/>
+      <c r="W39" s="12"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
       <c r="AF39" s="1"/>
-      <c r="AT39" s="8"/>
-      <c r="AY39" s="9"/>
+      <c r="AT39" s="9"/>
+      <c r="AY39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="I40" s="9"/>
+      <c r="A40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="I40" s="12"/>
       <c r="K40" s="1"/>
-      <c r="M40" s="7"/>
-      <c r="S40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="S40" s="9"/>
       <c r="U40" s="1"/>
-      <c r="V40" s="9"/>
-      <c r="W40" s="9"/>
-      <c r="Y40" s="9"/>
+      <c r="V40" s="12"/>
+      <c r="W40" s="12"/>
+      <c r="Y40" s="12"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
       <c r="AF40" s="1"/>
-      <c r="AI40" s="9"/>
-      <c r="AT40" s="8"/>
-      <c r="AY40" s="9"/>
+      <c r="AI40" s="12"/>
+      <c r="AT40" s="9"/>
+      <c r="AY40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13"/>
-      <c r="F41" s="9"/>
-      <c r="I41" s="9"/>
+      <c r="A41" s="14"/>
+      <c r="F41" s="12"/>
+      <c r="I41" s="12"/>
       <c r="K41" s="1"/>
-      <c r="M41" s="7"/>
-      <c r="S41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="S41" s="9"/>
       <c r="U41" s="1"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="Y41" s="9"/>
+      <c r="V41" s="12"/>
+      <c r="W41" s="12"/>
+      <c r="Y41" s="12"/>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
       <c r="AF41" s="1"/>
-      <c r="AI41" s="13"/>
-      <c r="AT41" s="8"/>
-      <c r="AY41" s="13"/>
+      <c r="AI41" s="14"/>
+      <c r="AT41" s="9"/>
+      <c r="AY41" s="14"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13"/>
-      <c r="I42" s="9"/>
+      <c r="A42" s="14"/>
+      <c r="I42" s="12"/>
       <c r="K42" s="1"/>
-      <c r="M42" s="7"/>
-      <c r="S42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="S42" s="9"/>
       <c r="U42" s="1"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="Y42" s="9"/>
+      <c r="V42" s="12"/>
+      <c r="W42" s="12"/>
+      <c r="Y42" s="12"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
       <c r="AF42" s="1"/>
-      <c r="AI42" s="13"/>
-      <c r="AT42" s="8"/>
-      <c r="AY42" s="13"/>
+      <c r="AI42" s="14"/>
+      <c r="AT42" s="9"/>
+      <c r="AY42" s="14"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F43" s="9"/>
+      <c r="F43" s="12"/>
       <c r="I43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="M43" s="7"/>
-      <c r="S43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="S43" s="9"/>
       <c r="U43" s="1"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
+      <c r="V43" s="12"/>
+      <c r="W43" s="12"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
       <c r="AF43" s="1"/>
-      <c r="AT43" s="8"/>
+      <c r="AT43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F44" s="9"/>
+      <c r="F44" s="12"/>
       <c r="I44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="M44" s="7"/>
-      <c r="S44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="S44" s="9"/>
       <c r="U44" s="1"/>
-      <c r="V44" s="9"/>
-      <c r="W44" s="9"/>
+      <c r="V44" s="12"/>
+      <c r="W44" s="12"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
       <c r="AF44" s="1"/>
-      <c r="AH44" s="9"/>
-      <c r="AT44" s="8"/>
+      <c r="AH44" s="12"/>
+      <c r="AT44" s="9"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="M45" s="7"/>
-      <c r="S45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="S45" s="9"/>
       <c r="U45" s="1"/>
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
@@ -2362,13 +2280,13 @@
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
       <c r="AF45" s="1"/>
-      <c r="AT45" s="8"/>
+      <c r="AT45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="M46" s="7"/>
-      <c r="S46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="S46" s="9"/>
       <c r="U46" s="1"/>
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
@@ -2376,17 +2294,17 @@
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
       <c r="AF46" s="1"/>
-      <c r="AL46" s="9"/>
-      <c r="AM46" s="9"/>
-      <c r="AT46" s="8"/>
+      <c r="AL46" s="12"/>
+      <c r="AM46" s="12"/>
+      <c r="AT46" s="9"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I47" s="1"/>
       <c r="K47" s="1"/>
-      <c r="M47" s="7"/>
-      <c r="S47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="S47" s="9"/>
       <c r="U47" s="1"/>
-      <c r="Y47" s="9"/>
+      <c r="Y47" s="12"/>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
@@ -2395,16 +2313,16 @@
       <c r="AF47" s="1"/>
       <c r="AL47" s="1"/>
       <c r="AN47" s="1"/>
-      <c r="AT47" s="8"/>
+      <c r="AT47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="M48" s="7"/>
-      <c r="S48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="S48" s="9"/>
       <c r="U48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AA48" s="9"/>
+      <c r="AA48" s="12"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
@@ -2417,16 +2335,16 @@
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="M49" s="7"/>
-      <c r="S49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="S49" s="9"/>
       <c r="U49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AA49" s="9"/>
+      <c r="AA49" s="12"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
       <c r="AF49" s="1"/>
-      <c r="AI49" s="9"/>
+      <c r="AI49" s="12"/>
       <c r="AL49" s="1"/>
       <c r="AN49" s="1"/>
       <c r="AP49" s="1"/>
@@ -2435,8 +2353,8 @@
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I50" s="1"/>
       <c r="K50" s="1"/>
-      <c r="M50" s="7"/>
-      <c r="S50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="S50" s="9"/>
       <c r="U50" s="1"/>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
@@ -2444,7 +2362,7 @@
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
       <c r="AF50" s="1"/>
-      <c r="AI50" s="9"/>
+      <c r="AI50" s="12"/>
       <c r="AL50" s="1"/>
       <c r="AN50" s="1"/>
       <c r="AP50" s="1"/>
@@ -2453,17 +2371,17 @@
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I51" s="1"/>
       <c r="K51" s="1"/>
-      <c r="M51" s="7"/>
-      <c r="S51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="S51" s="9"/>
       <c r="U51" s="1"/>
-      <c r="Y51" s="9"/>
+      <c r="Y51" s="12"/>
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
       <c r="AF51" s="1"/>
-      <c r="AI51" s="9"/>
+      <c r="AI51" s="12"/>
       <c r="AL51" s="1"/>
       <c r="AM51" s="1"/>
       <c r="AN51" s="1"/>
@@ -2473,16 +2391,16 @@
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I52" s="1"/>
       <c r="K52" s="1"/>
-      <c r="M52" s="7"/>
-      <c r="S52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="S52" s="9"/>
       <c r="U52" s="1"/>
       <c r="Z52" s="1"/>
-      <c r="AA52" s="9"/>
+      <c r="AA52" s="12"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
       <c r="AF52" s="1"/>
-      <c r="AI52" s="9"/>
+      <c r="AI52" s="12"/>
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
       <c r="AN52" s="1"/>
@@ -2492,8 +2410,8 @@
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I53" s="1"/>
       <c r="K53" s="1"/>
-      <c r="M53" s="7"/>
-      <c r="S53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="S53" s="9"/>
       <c r="U53" s="1"/>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
@@ -2501,7 +2419,7 @@
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
       <c r="AF53" s="1"/>
-      <c r="AI53" s="9"/>
+      <c r="AI53" s="12"/>
       <c r="AL53" s="1"/>
       <c r="AM53" s="1"/>
       <c r="AN53" s="1"/>
@@ -2511,17 +2429,17 @@
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I54" s="1"/>
       <c r="K54" s="1"/>
-      <c r="M54" s="7"/>
-      <c r="S54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="S54" s="9"/>
       <c r="U54" s="1"/>
-      <c r="Y54" s="9"/>
+      <c r="Y54" s="12"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
       <c r="AF54" s="1"/>
-      <c r="AI54" s="9"/>
+      <c r="AI54" s="12"/>
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
       <c r="AN54" s="1"/>
@@ -2531,16 +2449,16 @@
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I55" s="1"/>
       <c r="K55" s="1"/>
-      <c r="M55" s="7"/>
-      <c r="S55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="S55" s="9"/>
       <c r="U55" s="1"/>
       <c r="Z55" s="1"/>
-      <c r="AA55" s="9"/>
+      <c r="AA55" s="12"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
       <c r="AF55" s="1"/>
-      <c r="AI55" s="9"/>
+      <c r="AI55" s="12"/>
       <c r="AL55" s="1"/>
       <c r="AM55" s="1"/>
       <c r="AN55" s="1"/>
@@ -2550,8 +2468,8 @@
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I56" s="1"/>
       <c r="K56" s="1"/>
-      <c r="M56" s="7"/>
-      <c r="S56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="S56" s="9"/>
       <c r="U56" s="1"/>
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
@@ -2559,7 +2477,7 @@
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
       <c r="AF56" s="1"/>
-      <c r="AI56" s="9"/>
+      <c r="AI56" s="12"/>
       <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
       <c r="AN56" s="1"/>
@@ -2569,17 +2487,17 @@
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I57" s="1"/>
       <c r="K57" s="1"/>
-      <c r="M57" s="7"/>
-      <c r="S57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="S57" s="9"/>
       <c r="U57" s="1"/>
-      <c r="Y57" s="9"/>
+      <c r="Y57" s="12"/>
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
       <c r="AF57" s="1"/>
-      <c r="AI57" s="9"/>
+      <c r="AI57" s="12"/>
       <c r="AL57" s="1"/>
       <c r="AM57" s="1"/>
       <c r="AN57" s="1"/>
@@ -2589,8 +2507,8 @@
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I58" s="1"/>
       <c r="K58" s="1"/>
-      <c r="M58" s="7"/>
-      <c r="S58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="S58" s="9"/>
       <c r="U58" s="1"/>
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
@@ -2598,7 +2516,7 @@
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
       <c r="AF58" s="1"/>
-      <c r="AI58" s="9"/>
+      <c r="AI58" s="12"/>
       <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
       <c r="AN58" s="1"/>
@@ -2608,17 +2526,17 @@
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I59" s="1"/>
       <c r="K59" s="1"/>
-      <c r="M59" s="7"/>
-      <c r="S59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="S59" s="9"/>
       <c r="U59" s="1"/>
-      <c r="Y59" s="9"/>
+      <c r="Y59" s="12"/>
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
       <c r="AF59" s="1"/>
-      <c r="AI59" s="9"/>
+      <c r="AI59" s="12"/>
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
       <c r="AN59" s="1"/>
@@ -2628,8 +2546,8 @@
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I60" s="1"/>
       <c r="K60" s="1"/>
-      <c r="M60" s="7"/>
-      <c r="S60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="S60" s="9"/>
       <c r="U60" s="1"/>
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
@@ -2637,7 +2555,7 @@
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
       <c r="AF60" s="1"/>
-      <c r="AI60" s="9"/>
+      <c r="AI60" s="12"/>
       <c r="AL60" s="1"/>
       <c r="AM60" s="1"/>
       <c r="AP60" s="1"/>
@@ -2646,8 +2564,8 @@
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I61" s="1"/>
       <c r="K61" s="1"/>
-      <c r="M61" s="7"/>
-      <c r="S61" s="8"/>
+      <c r="M61" s="8"/>
+      <c r="S61" s="9"/>
       <c r="U61" s="1"/>
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
@@ -2655,7 +2573,7 @@
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
       <c r="AF61" s="1"/>
-      <c r="AI61" s="9"/>
+      <c r="AI61" s="12"/>
       <c r="AL61" s="1"/>
       <c r="AM61" s="1"/>
       <c r="AP61" s="1"/>
@@ -2664,41 +2582,41 @@
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I62" s="1"/>
       <c r="K62" s="1"/>
-      <c r="M62" s="7"/>
-      <c r="S62" s="8"/>
+      <c r="M62" s="8"/>
+      <c r="S62" s="9"/>
       <c r="U62" s="1"/>
-      <c r="Y62" s="9"/>
+      <c r="Y62" s="12"/>
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
       <c r="AF62" s="1"/>
-      <c r="AI62" s="9"/>
-      <c r="AL62" s="9"/>
-      <c r="AM62" s="9"/>
+      <c r="AI62" s="12"/>
+      <c r="AL62" s="12"/>
+      <c r="AM62" s="12"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I63" s="1"/>
       <c r="K63" s="1"/>
-      <c r="M63" s="7"/>
-      <c r="S63" s="8"/>
+      <c r="M63" s="8"/>
+      <c r="S63" s="9"/>
       <c r="U63" s="1"/>
-      <c r="Y63" s="9"/>
+      <c r="Y63" s="12"/>
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
       <c r="AF63" s="1"/>
-      <c r="AI63" s="9"/>
-      <c r="AK63" s="9"/>
+      <c r="AI63" s="12"/>
+      <c r="AK63" s="12"/>
       <c r="AL63" s="1"/>
       <c r="AM63" s="1"/>
     </row>
     <row r="64" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="15"/>
-      <c r="C64" s="14"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="15"/>
       <c r="E64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -2707,12 +2625,12 @@
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
-      <c r="S64" s="16"/>
+      <c r="S64" s="17"/>
       <c r="U64" s="1"/>
-      <c r="V64" s="17"/>
-      <c r="W64" s="9"/>
-      <c r="Z64" s="9"/>
-      <c r="AA64" s="9"/>
+      <c r="V64" s="18"/>
+      <c r="W64" s="12"/>
+      <c r="Z64" s="12"/>
+      <c r="AA64" s="12"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
@@ -2722,11 +2640,11 @@
       <c r="AJ64" s="1"/>
       <c r="AL64" s="1"/>
       <c r="AN64" s="1"/>
-      <c r="AT64" s="8"/>
+      <c r="AT64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="15"/>
-      <c r="C65" s="14"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="15"/>
       <c r="E65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -2735,12 +2653,12 @@
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
-      <c r="S65" s="16"/>
+      <c r="S65" s="17"/>
       <c r="U65" s="1"/>
-      <c r="V65" s="17"/>
-      <c r="W65" s="9"/>
-      <c r="Z65" s="9"/>
-      <c r="AA65" s="9"/>
+      <c r="V65" s="18"/>
+      <c r="W65" s="12"/>
+      <c r="Z65" s="12"/>
+      <c r="AA65" s="12"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
@@ -2750,11 +2668,11 @@
       <c r="AJ65" s="1"/>
       <c r="AL65" s="1"/>
       <c r="AN65" s="1"/>
-      <c r="AT65" s="8"/>
+      <c r="AT65" s="9"/>
     </row>
     <row r="66" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="15"/>
-      <c r="C66" s="14"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="15"/>
       <c r="E66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -2763,12 +2681,12 @@
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
-      <c r="S66" s="16"/>
+      <c r="S66" s="17"/>
       <c r="U66" s="1"/>
-      <c r="V66" s="17"/>
-      <c r="W66" s="9"/>
-      <c r="Z66" s="9"/>
-      <c r="AA66" s="9"/>
+      <c r="V66" s="18"/>
+      <c r="W66" s="12"/>
+      <c r="Z66" s="12"/>
+      <c r="AA66" s="12"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
@@ -2778,13 +2696,13 @@
       <c r="AJ66" s="1"/>
       <c r="AL66" s="1"/>
       <c r="AN66" s="1"/>
-      <c r="AT66" s="8"/>
+      <c r="AT66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I67" s="1"/>
       <c r="K67" s="1"/>
       <c r="M67" s="1"/>
-      <c r="S67" s="16"/>
+      <c r="S67" s="17"/>
       <c r="U67" s="1"/>
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
@@ -2792,13 +2710,13 @@
       <c r="AD67" s="1"/>
       <c r="AE67" s="1"/>
       <c r="AF67" s="1"/>
-      <c r="AT67" s="8"/>
+      <c r="AT67" s="9"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I68" s="1"/>
       <c r="K68" s="1"/>
       <c r="M68" s="1"/>
-      <c r="S68" s="16"/>
+      <c r="S68" s="17"/>
       <c r="U68" s="1"/>
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
@@ -2807,14 +2725,14 @@
       <c r="AD68" s="1"/>
       <c r="AE68" s="1"/>
       <c r="AF68" s="1"/>
-      <c r="AT68" s="8"/>
+      <c r="AT68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D69" s="14"/>
+      <c r="D69" s="15"/>
       <c r="I69" s="1"/>
       <c r="K69" s="1"/>
       <c r="M69" s="1"/>
-      <c r="S69" s="16"/>
+      <c r="S69" s="17"/>
       <c r="U69" s="1"/>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
@@ -2843,7 +2761,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AW69"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.25"/>
@@ -3228,319 +3146,319 @@
       <c r="AW3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="16" t="n">
         <v>7869001</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="15"/>
+      <c r="D4" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
       <c r="M4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P4" s="9" t="n">
+      <c r="N4" s="12"/>
+      <c r="O4" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="P4" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="S4" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9" t="s">
+      <c r="S4" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="T4" s="12"/>
+      <c r="U4" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="W4" s="9" t="s">
+      <c r="V4" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="X4" s="9" t="s">
+      <c r="W4" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="Y4" s="9" t="s">
+      <c r="X4" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="9" t="s">
+      <c r="Y4" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9" t="s">
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AF4" s="9"/>
-      <c r="AG4" s="9" t="s">
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="9"/>
-      <c r="AI4" s="9"/>
-      <c r="AJ4" s="9"/>
-      <c r="AK4" s="9"/>
-      <c r="AL4" s="9"/>
-      <c r="AM4" s="9"/>
+      <c r="AH4" s="12"/>
+      <c r="AI4" s="12"/>
+      <c r="AJ4" s="12"/>
+      <c r="AK4" s="12"/>
+      <c r="AL4" s="12"/>
+      <c r="AM4" s="12"/>
       <c r="AN4" s="10"/>
-      <c r="AO4" s="9"/>
-      <c r="AP4" s="9"/>
-      <c r="AQ4" s="9"/>
-      <c r="AR4" s="9"/>
-      <c r="AS4" s="9"/>
-      <c r="AT4" s="9"/>
-      <c r="AU4" s="9"/>
-      <c r="AV4" s="9"/>
-      <c r="AW4" s="9"/>
+      <c r="AO4" s="12"/>
+      <c r="AP4" s="12"/>
+      <c r="AQ4" s="12"/>
+      <c r="AR4" s="12"/>
+      <c r="AS4" s="12"/>
+      <c r="AT4" s="12"/>
+      <c r="AU4" s="12"/>
+      <c r="AV4" s="12"/>
+      <c r="AW4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" s="15" t="n">
+      <c r="A5" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="16" t="n">
         <v>7869002</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9" t="s">
+      <c r="C5" s="12"/>
+      <c r="D5" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="15"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
       <c r="M5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P5" s="9" t="n">
+      <c r="N5" s="12"/>
+      <c r="O5" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="P5" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="S5" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="V5" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="W5" s="9" t="s">
+      <c r="S5" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="V5" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="X5" s="9" t="s">
+      <c r="W5" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="Y5" s="9" t="s">
+      <c r="X5" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="9" t="s">
+      <c r="Y5" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9" t="s">
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AF5" s="9"/>
-      <c r="AG5" s="9" t="s">
+      <c r="AF5" s="12"/>
+      <c r="AG5" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AH5" s="9"/>
-      <c r="AI5" s="9"/>
-      <c r="AJ5" s="9"/>
-      <c r="AK5" s="9"/>
-      <c r="AL5" s="9"/>
-      <c r="AM5" s="9"/>
+      <c r="AH5" s="12"/>
+      <c r="AI5" s="12"/>
+      <c r="AJ5" s="12"/>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="12"/>
+      <c r="AM5" s="12"/>
       <c r="AN5" s="10"/>
-      <c r="AO5" s="9"/>
-      <c r="AP5" s="9"/>
-      <c r="AQ5" s="9"/>
-      <c r="AR5" s="9"/>
-      <c r="AS5" s="9"/>
-      <c r="AT5" s="9"/>
-      <c r="AU5" s="9"/>
-      <c r="AV5" s="9"/>
-      <c r="AW5" s="9"/>
+      <c r="AO5" s="12"/>
+      <c r="AP5" s="12"/>
+      <c r="AQ5" s="12"/>
+      <c r="AR5" s="12"/>
+      <c r="AS5" s="12"/>
+      <c r="AT5" s="12"/>
+      <c r="AU5" s="12"/>
+      <c r="AV5" s="12"/>
+      <c r="AW5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="15" t="n">
+      <c r="A6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="16" t="n">
         <v>7869003</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9" t="s">
+      <c r="C6" s="15"/>
+      <c r="D6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
       <c r="M6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P6" s="9" t="n">
+      <c r="N6" s="12"/>
+      <c r="O6" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="P6" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="S6" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="W6" s="9" t="s">
+      <c r="S6" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="X6" s="9" t="s">
+      <c r="W6" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="Y6" s="9" t="s">
+      <c r="X6" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9" t="s">
+      <c r="Y6" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9" t="s">
+      <c r="Z6" s="12"/>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AF6" s="9"/>
-      <c r="AG6" s="9" t="s">
+      <c r="AF6" s="12"/>
+      <c r="AG6" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AH6" s="9"/>
-      <c r="AI6" s="9"/>
-      <c r="AJ6" s="9"/>
-      <c r="AK6" s="9"/>
-      <c r="AL6" s="9"/>
-      <c r="AM6" s="9"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="9"/>
-      <c r="AP6" s="9"/>
-      <c r="AQ6" s="9"/>
-      <c r="AR6" s="9"/>
-      <c r="AS6" s="9"/>
-      <c r="AT6" s="9"/>
-      <c r="AU6" s="9"/>
-      <c r="AV6" s="9"/>
-      <c r="AW6" s="9"/>
+      <c r="AH6" s="12"/>
+      <c r="AI6" s="12"/>
+      <c r="AJ6" s="12"/>
+      <c r="AK6" s="12"/>
+      <c r="AL6" s="12"/>
+      <c r="AM6" s="12"/>
+      <c r="AN6" s="12"/>
+      <c r="AO6" s="12"/>
+      <c r="AP6" s="12"/>
+      <c r="AQ6" s="12"/>
+      <c r="AR6" s="12"/>
+      <c r="AS6" s="12"/>
+      <c r="AT6" s="12"/>
+      <c r="AU6" s="12"/>
+      <c r="AV6" s="12"/>
+      <c r="AW6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="15"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="12"/>
+      <c r="J7" s="12"/>
       <c r="M7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="V7" s="18"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="V7" s="19"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="9"/>
+      <c r="Y7" s="12"/>
       <c r="Z7" s="1"/>
-      <c r="AB7" s="9"/>
-      <c r="AD7" s="9"/>
+      <c r="AB7" s="12"/>
+      <c r="AD7" s="12"/>
       <c r="AE7" s="1"/>
-      <c r="AG7" s="9"/>
-      <c r="AR7" s="9"/>
+      <c r="AG7" s="12"/>
+      <c r="AR7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="9"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="9"/>
+      <c r="J8" s="12"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
       <c r="T8" s="1"/>
-      <c r="V8" s="18"/>
+      <c r="V8" s="19"/>
       <c r="W8" s="1"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
       <c r="AA8" s="1"/>
-      <c r="AB8" s="9"/>
-      <c r="AC8" s="9"/>
-      <c r="AD8" s="9"/>
-      <c r="AE8" s="9"/>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="12"/>
+      <c r="AE8" s="12"/>
       <c r="AF8" s="1"/>
-      <c r="AG8" s="9"/>
+      <c r="AG8" s="12"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
@@ -3550,7 +3468,7 @@
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
-      <c r="AR8" s="9"/>
+      <c r="AR8" s="12"/>
       <c r="AS8" s="1"/>
       <c r="AT8" s="1"/>
       <c r="AU8" s="1"/>
@@ -3558,439 +3476,439 @@
       <c r="AW8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="15"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="12"/>
+      <c r="J9" s="12"/>
       <c r="M9" s="1"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="V9" s="18"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="V9" s="19"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AB9" s="9"/>
-      <c r="AD9" s="9"/>
-      <c r="AG9" s="9"/>
-      <c r="AR9" s="9"/>
+      <c r="AB9" s="12"/>
+      <c r="AD9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AR9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="15"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="12"/>
+      <c r="J10" s="12"/>
       <c r="M10" s="1"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="V10" s="18"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="V10" s="19"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AB10" s="9"/>
-      <c r="AD10" s="9"/>
-      <c r="AG10" s="9"/>
-      <c r="AR10" s="9"/>
+      <c r="AB10" s="12"/>
+      <c r="AD10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AR10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="15"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="12"/>
+      <c r="J11" s="12"/>
       <c r="M11" s="1"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="V11" s="18"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="V11" s="19"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AB11" s="9"/>
-      <c r="AD11" s="9"/>
-      <c r="AG11" s="9"/>
-      <c r="AR11" s="9"/>
+      <c r="AB11" s="12"/>
+      <c r="AD11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AR11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="15"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="12"/>
+      <c r="J12" s="12"/>
       <c r="M12" s="1"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="V12" s="18"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="V12" s="19"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-      <c r="AB12" s="9"/>
-      <c r="AD12" s="9"/>
-      <c r="AG12" s="9"/>
-      <c r="AR12" s="9"/>
+      <c r="AB12" s="12"/>
+      <c r="AD12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AR12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="15"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="14"/>
-      <c r="J13" s="9"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="15"/>
+      <c r="J13" s="12"/>
       <c r="M13" s="1"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="9"/>
+      <c r="S13" s="12"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
-      <c r="AB13" s="9"/>
-      <c r="AD13" s="9"/>
-      <c r="AE13" s="9"/>
-      <c r="AG13" s="9"/>
+      <c r="AB13" s="12"/>
+      <c r="AD13" s="12"/>
+      <c r="AE13" s="12"/>
+      <c r="AG13" s="12"/>
       <c r="AQ13" s="1"/>
       <c r="AR13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="14"/>
-      <c r="J14" s="9"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="15"/>
+      <c r="J14" s="12"/>
       <c r="M14" s="1"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
       <c r="R14" s="1"/>
-      <c r="S14" s="9"/>
+      <c r="S14" s="12"/>
       <c r="W14" s="1"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="9"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="12"/>
       <c r="Z14" s="1"/>
-      <c r="AB14" s="9"/>
-      <c r="AD14" s="9"/>
-      <c r="AE14" s="9"/>
-      <c r="AG14" s="9"/>
+      <c r="AB14" s="12"/>
+      <c r="AD14" s="12"/>
+      <c r="AE14" s="12"/>
+      <c r="AG14" s="12"/>
       <c r="AQ14" s="1"/>
       <c r="AR14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="15"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="14"/>
-      <c r="J15" s="9"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="15"/>
+      <c r="J15" s="12"/>
       <c r="M15" s="1"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="9"/>
+      <c r="S15" s="12"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
-      <c r="AB15" s="9"/>
-      <c r="AD15" s="9"/>
-      <c r="AE15" s="9"/>
-      <c r="AG15" s="9"/>
+      <c r="AB15" s="12"/>
+      <c r="AD15" s="12"/>
+      <c r="AE15" s="12"/>
+      <c r="AG15" s="12"/>
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="15"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="14"/>
-      <c r="J16" s="9"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="15"/>
+      <c r="J16" s="12"/>
       <c r="M16" s="1"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
       <c r="R16" s="1"/>
-      <c r="S16" s="9"/>
+      <c r="S16" s="12"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-      <c r="Y16" s="9"/>
+      <c r="Y16" s="12"/>
       <c r="Z16" s="1"/>
-      <c r="AB16" s="9"/>
-      <c r="AD16" s="9"/>
-      <c r="AE16" s="9"/>
-      <c r="AG16" s="9"/>
+      <c r="AB16" s="12"/>
+      <c r="AD16" s="12"/>
+      <c r="AE16" s="12"/>
+      <c r="AG16" s="12"/>
       <c r="AQ16" s="1"/>
       <c r="AR16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="15"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="14"/>
-      <c r="J17" s="9"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="15"/>
+      <c r="J17" s="12"/>
       <c r="M17" s="1"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
       <c r="R17" s="1"/>
-      <c r="S17" s="9"/>
+      <c r="S17" s="12"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-      <c r="AB17" s="9"/>
-      <c r="AD17" s="9"/>
-      <c r="AE17" s="9"/>
-      <c r="AG17" s="9"/>
+      <c r="AB17" s="12"/>
+      <c r="AD17" s="12"/>
+      <c r="AE17" s="12"/>
+      <c r="AG17" s="12"/>
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="15"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="14"/>
-      <c r="J18" s="9"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="15"/>
+      <c r="J18" s="12"/>
       <c r="M18" s="1"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
       <c r="R18" s="1"/>
-      <c r="S18" s="9"/>
+      <c r="S18" s="12"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
-      <c r="AB18" s="9"/>
-      <c r="AD18" s="9"/>
-      <c r="AE18" s="9"/>
-      <c r="AG18" s="9"/>
+      <c r="AB18" s="12"/>
+      <c r="AD18" s="12"/>
+      <c r="AE18" s="12"/>
+      <c r="AG18" s="12"/>
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="15"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="14"/>
-      <c r="J19" s="9"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="15"/>
+      <c r="J19" s="12"/>
       <c r="M19" s="1"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
       <c r="R19" s="1"/>
-      <c r="S19" s="9"/>
+      <c r="S19" s="12"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
-      <c r="AB19" s="9"/>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="9"/>
-      <c r="AG19" s="9"/>
+      <c r="AB19" s="12"/>
+      <c r="AD19" s="12"/>
+      <c r="AE19" s="12"/>
+      <c r="AG19" s="12"/>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="15"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="12"/>
+      <c r="J20" s="12"/>
       <c r="M20" s="1"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
       <c r="R20" s="1"/>
-      <c r="S20" s="9"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="9"/>
+      <c r="S20" s="12"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="12"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
-      <c r="AB20" s="9"/>
-      <c r="AD20" s="9"/>
-      <c r="AG20" s="9"/>
+      <c r="AB20" s="12"/>
+      <c r="AD20" s="12"/>
+      <c r="AG20" s="12"/>
       <c r="AQ20" s="1"/>
       <c r="AR20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="15"/>
-      <c r="C21" s="22"/>
-      <c r="J21" s="9"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="23"/>
+      <c r="J21" s="12"/>
       <c r="M21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="9"/>
+      <c r="Q21" s="12"/>
       <c r="R21" s="1"/>
-      <c r="S21" s="9"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="9"/>
+      <c r="S21" s="12"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="12"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="9"/>
-      <c r="AA21" s="9"/>
+      <c r="Z21" s="12"/>
+      <c r="AA21" s="12"/>
       <c r="AE21" s="1"/>
-      <c r="AG21" s="9"/>
+      <c r="AG21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="15"/>
-      <c r="C22" s="22"/>
-      <c r="J22" s="9"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="23"/>
+      <c r="J22" s="12"/>
       <c r="M22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="9"/>
+      <c r="Q22" s="12"/>
       <c r="R22" s="1"/>
-      <c r="S22" s="9"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="9"/>
+      <c r="S22" s="12"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="12"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
+      <c r="Z22" s="12"/>
+      <c r="AA22" s="12"/>
+      <c r="AB22" s="12"/>
       <c r="AE22" s="1"/>
-      <c r="AG22" s="9"/>
+      <c r="AG22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="15"/>
-      <c r="C23" s="22"/>
-      <c r="J23" s="9"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="23"/>
+      <c r="J23" s="12"/>
       <c r="M23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="9"/>
+      <c r="Q23" s="12"/>
       <c r="R23" s="1"/>
-      <c r="S23" s="9"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="9"/>
+      <c r="S23" s="12"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="12"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
+      <c r="Z23" s="12"/>
+      <c r="AA23" s="12"/>
+      <c r="AB23" s="12"/>
       <c r="AE23" s="1"/>
-      <c r="AG23" s="9"/>
+      <c r="AG23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="15"/>
-      <c r="C24" s="22"/>
-      <c r="J24" s="9"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="23"/>
+      <c r="J24" s="12"/>
       <c r="M24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="9"/>
+      <c r="Q24" s="12"/>
       <c r="R24" s="1"/>
-      <c r="S24" s="9"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="9"/>
+      <c r="S24" s="12"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="12"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="9"/>
-      <c r="AA24" s="9"/>
-      <c r="AB24" s="9"/>
+      <c r="Z24" s="12"/>
+      <c r="AA24" s="12"/>
+      <c r="AB24" s="12"/>
       <c r="AE24" s="1"/>
-      <c r="AG24" s="9"/>
+      <c r="AG24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="15"/>
-      <c r="C25" s="22"/>
-      <c r="J25" s="9"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="23"/>
+      <c r="J25" s="12"/>
       <c r="M25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="9"/>
+      <c r="Q25" s="12"/>
       <c r="R25" s="1"/>
-      <c r="S25" s="9"/>
-      <c r="V25" s="17"/>
-      <c r="W25" s="9"/>
+      <c r="S25" s="12"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="12"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="Z25" s="9"/>
-      <c r="AA25" s="9"/>
-      <c r="AB25" s="9"/>
+      <c r="Z25" s="12"/>
+      <c r="AA25" s="12"/>
+      <c r="AB25" s="12"/>
       <c r="AE25" s="1"/>
-      <c r="AG25" s="9"/>
+      <c r="AG25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="15"/>
-      <c r="C26" s="22"/>
-      <c r="J26" s="9"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="23"/>
+      <c r="J26" s="12"/>
       <c r="M26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="9"/>
+      <c r="Q26" s="12"/>
       <c r="R26" s="1"/>
-      <c r="S26" s="9"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="9"/>
+      <c r="S26" s="12"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="12"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="Z26" s="9"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
+      <c r="Z26" s="12"/>
+      <c r="AA26" s="12"/>
+      <c r="AB26" s="12"/>
       <c r="AE26" s="1"/>
-      <c r="AG26" s="9"/>
+      <c r="AG26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="15"/>
-      <c r="C27" s="22"/>
-      <c r="J27" s="9"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="23"/>
+      <c r="J27" s="12"/>
       <c r="M27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="9"/>
+      <c r="Q27" s="12"/>
       <c r="R27" s="1"/>
-      <c r="S27" s="9"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="9"/>
+      <c r="S27" s="12"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="12"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
+      <c r="Z27" s="12"/>
+      <c r="AA27" s="12"/>
+      <c r="AB27" s="12"/>
       <c r="AE27" s="1"/>
-      <c r="AG27" s="9"/>
+      <c r="AG27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="15"/>
-      <c r="C28" s="22"/>
-      <c r="J28" s="9"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="23"/>
+      <c r="J28" s="12"/>
       <c r="M28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="9"/>
+      <c r="Q28" s="12"/>
       <c r="R28" s="1"/>
-      <c r="S28" s="9"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="9"/>
+      <c r="S28" s="12"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="12"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="AB28" s="9"/>
-      <c r="AD28" s="9"/>
+      <c r="AB28" s="12"/>
+      <c r="AD28" s="12"/>
       <c r="AE28" s="1"/>
-      <c r="AG28" s="9"/>
+      <c r="AG28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="15"/>
-      <c r="C29" s="22"/>
-      <c r="J29" s="9"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="23"/>
+      <c r="J29" s="12"/>
       <c r="M29" s="1"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="9"/>
+      <c r="Q29" s="12"/>
       <c r="R29" s="1"/>
-      <c r="S29" s="9"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="9"/>
+      <c r="S29" s="12"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="12"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="9"/>
-      <c r="AB29" s="9"/>
-      <c r="AD29" s="9"/>
+      <c r="Y29" s="12"/>
+      <c r="AB29" s="12"/>
+      <c r="AD29" s="12"/>
       <c r="AE29" s="1"/>
-      <c r="AG29" s="9"/>
+      <c r="AG29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="15"/>
-      <c r="C30" s="9"/>
-      <c r="J30" s="9"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="12"/>
+      <c r="J30" s="12"/>
       <c r="M30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="V30" s="17"/>
+      <c r="V30" s="18"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
@@ -3999,161 +3917,161 @@
       <c r="AL30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="15"/>
-      <c r="C31" s="9"/>
-      <c r="J31" s="9"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="12"/>
+      <c r="J31" s="12"/>
       <c r="M31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="V31" s="17"/>
+      <c r="V31" s="18"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="AA31" s="1"/>
-      <c r="AB31" s="9"/>
+      <c r="AB31" s="12"/>
       <c r="AG31" s="1"/>
       <c r="AL31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="9"/>
-      <c r="J32" s="9"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="12"/>
+      <c r="J32" s="12"/>
       <c r="M32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="V32" s="17"/>
+      <c r="V32" s="18"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-      <c r="Y32" s="9"/>
+      <c r="Y32" s="12"/>
       <c r="AA32" s="1"/>
       <c r="AG32" s="1"/>
       <c r="AL32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="15"/>
-      <c r="C33" s="14"/>
-      <c r="J33" s="9"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="15"/>
+      <c r="J33" s="12"/>
       <c r="M33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="9"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="12"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="AG33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="15"/>
-      <c r="C34" s="14"/>
-      <c r="J34" s="9"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="15"/>
+      <c r="J34" s="12"/>
       <c r="M34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="9"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="12"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="AB34" s="9"/>
+      <c r="AB34" s="12"/>
       <c r="AG34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="15"/>
-      <c r="C35" s="14"/>
-      <c r="J35" s="9"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="15"/>
+      <c r="J35" s="12"/>
       <c r="M35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="9"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="12"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="AD35" s="9"/>
+      <c r="AD35" s="12"/>
       <c r="AG35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="14"/>
-      <c r="J36" s="9"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="15"/>
+      <c r="J36" s="12"/>
       <c r="M36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="V36" s="17"/>
-      <c r="W36" s="9"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="12"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="AG36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="14"/>
-      <c r="J37" s="9"/>
+      <c r="A37" s="14"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="15"/>
+      <c r="J37" s="12"/>
       <c r="M37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="9"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="12"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
       <c r="AG37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="14"/>
-      <c r="J38" s="9"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="15"/>
+      <c r="J38" s="12"/>
       <c r="M38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-      <c r="V38" s="17"/>
-      <c r="W38" s="9"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="12"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="AB38" s="9"/>
+      <c r="AB38" s="12"/>
       <c r="AG38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="14"/>
-      <c r="J39" s="9"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="15"/>
+      <c r="J39" s="12"/>
       <c r="M39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
-      <c r="V39" s="17"/>
-      <c r="W39" s="9"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="12"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="AB39" s="9"/>
-      <c r="AD39" s="9"/>
+      <c r="AB39" s="12"/>
+      <c r="AD39" s="12"/>
       <c r="AG39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="15"/>
-      <c r="C40" s="14"/>
-      <c r="J40" s="9"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="15"/>
+      <c r="J40" s="12"/>
       <c r="M40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -4165,190 +4083,190 @@
       <c r="AG40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="15"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="9"/>
-      <c r="J41" s="9"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="12"/>
+      <c r="J41" s="12"/>
       <c r="M41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="W41" s="1"/>
-      <c r="X41" s="9"/>
+      <c r="X41" s="12"/>
       <c r="Y41" s="1"/>
-      <c r="AD41" s="9"/>
+      <c r="AD41" s="12"/>
       <c r="AG41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="15"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="9"/>
-      <c r="J42" s="9"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="12"/>
+      <c r="J42" s="12"/>
       <c r="M42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="W42" s="1"/>
-      <c r="X42" s="9"/>
+      <c r="X42" s="12"/>
       <c r="Y42" s="1"/>
-      <c r="AD42" s="9"/>
+      <c r="AD42" s="12"/>
       <c r="AG42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="15"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="9"/>
-      <c r="J43" s="9"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="12"/>
+      <c r="J43" s="12"/>
       <c r="M43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="W43" s="1"/>
-      <c r="X43" s="9"/>
+      <c r="X43" s="12"/>
       <c r="Y43" s="1"/>
-      <c r="AD43" s="9"/>
+      <c r="AD43" s="12"/>
       <c r="AG43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="15"/>
-      <c r="C44" s="14"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="15"/>
       <c r="J44" s="1"/>
       <c r="M44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
-      <c r="V44" s="17"/>
-      <c r="W44" s="9"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="12"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
-      <c r="Z44" s="9"/>
-      <c r="AA44" s="9"/>
-      <c r="AB44" s="9"/>
+      <c r="Z44" s="12"/>
+      <c r="AA44" s="12"/>
+      <c r="AB44" s="12"/>
       <c r="AG44" s="1"/>
       <c r="AL44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="15"/>
-      <c r="C45" s="14"/>
-      <c r="E45" s="14"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="15"/>
+      <c r="E45" s="15"/>
       <c r="J45" s="1"/>
       <c r="M45" s="1"/>
-      <c r="P45" s="9"/>
+      <c r="P45" s="12"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
-      <c r="U45" s="9"/>
-      <c r="V45" s="9"/>
-      <c r="W45" s="9"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
       <c r="X45" s="1"/>
-      <c r="Y45" s="9"/>
-      <c r="AD45" s="9"/>
+      <c r="Y45" s="12"/>
+      <c r="AD45" s="12"/>
       <c r="AG45" s="1"/>
       <c r="AM45" s="1"/>
       <c r="AN45" s="10"/>
       <c r="AP45" s="1"/>
-      <c r="AQ45" s="9"/>
+      <c r="AQ45" s="12"/>
       <c r="AR45" s="1"/>
       <c r="AT45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="15"/>
-      <c r="C46" s="14"/>
-      <c r="E46" s="14"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="15"/>
+      <c r="E46" s="15"/>
       <c r="J46" s="1"/>
       <c r="M46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="9"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
       <c r="X46" s="1"/>
-      <c r="Y46" s="9"/>
+      <c r="Y46" s="12"/>
       <c r="AG46" s="1"/>
       <c r="AM46" s="1"/>
       <c r="AN46" s="10"/>
-      <c r="AP46" s="9"/>
-      <c r="AQ46" s="9"/>
+      <c r="AP46" s="12"/>
+      <c r="AQ46" s="12"/>
       <c r="AR46" s="1"/>
       <c r="AT46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="15"/>
-      <c r="C47" s="14"/>
-      <c r="E47" s="14"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="15"/>
+      <c r="E47" s="15"/>
       <c r="J47" s="1"/>
       <c r="M47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-      <c r="V47" s="9"/>
-      <c r="W47" s="9"/>
+      <c r="V47" s="12"/>
+      <c r="W47" s="12"/>
       <c r="X47" s="1"/>
-      <c r="Y47" s="9"/>
+      <c r="Y47" s="12"/>
       <c r="AG47" s="1"/>
       <c r="AM47" s="1"/>
       <c r="AN47" s="10"/>
-      <c r="AP47" s="9"/>
+      <c r="AP47" s="12"/>
       <c r="AQ47" s="1"/>
       <c r="AR47" s="1"/>
       <c r="AT47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="15"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="14"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="15"/>
       <c r="J48" s="1"/>
       <c r="M48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
-      <c r="V48" s="9"/>
-      <c r="W48" s="9"/>
+      <c r="V48" s="12"/>
+      <c r="W48" s="12"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="AB48" s="9"/>
+      <c r="AB48" s="12"/>
       <c r="AG48" s="1"/>
       <c r="AM48" s="1"/>
       <c r="AN48" s="10"/>
-      <c r="AP48" s="9"/>
-      <c r="AQ48" s="9"/>
+      <c r="AP48" s="12"/>
+      <c r="AQ48" s="12"/>
       <c r="AT48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="15"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="14"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="15"/>
       <c r="J49" s="1"/>
       <c r="M49" s="1"/>
-      <c r="P49" s="9"/>
+      <c r="P49" s="12"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-      <c r="W49" s="9"/>
-      <c r="X49" s="9"/>
-      <c r="Y49" s="9"/>
-      <c r="AD49" s="9"/>
+      <c r="W49" s="12"/>
+      <c r="X49" s="12"/>
+      <c r="Y49" s="12"/>
+      <c r="AD49" s="12"/>
       <c r="AG49" s="1"/>
       <c r="AM49" s="1"/>
       <c r="AN49" s="10"/>
-      <c r="AP49" s="9"/>
-      <c r="AQ49" s="9"/>
+      <c r="AP49" s="12"/>
+      <c r="AQ49" s="12"/>
       <c r="AR49" s="1"/>
       <c r="AT49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="15"/>
-      <c r="C50" s="14"/>
-      <c r="E50" s="14"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="15"/>
+      <c r="E50" s="15"/>
       <c r="J50" s="1"/>
       <c r="M50" s="1"/>
       <c r="P50" s="1"/>
@@ -4358,20 +4276,20 @@
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="AB50" s="9"/>
+      <c r="AB50" s="12"/>
       <c r="AG50" s="1"/>
       <c r="AM50" s="1"/>
       <c r="AN50" s="10"/>
-      <c r="AP50" s="9"/>
-      <c r="AQ50" s="9"/>
+      <c r="AP50" s="12"/>
+      <c r="AQ50" s="12"/>
       <c r="AR50" s="1"/>
       <c r="AT50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="14"/>
-      <c r="E51" s="14"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="15"/>
+      <c r="E51" s="15"/>
       <c r="J51" s="1"/>
       <c r="M51" s="1"/>
       <c r="P51" s="1"/>
@@ -4382,57 +4300,57 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="AG51" s="1"/>
-      <c r="AM51" s="9"/>
+      <c r="AM51" s="12"/>
       <c r="AN51" s="10"/>
       <c r="AP51" s="1"/>
-      <c r="AQ51" s="9"/>
+      <c r="AQ51" s="12"/>
       <c r="AR51" s="1"/>
-      <c r="AT51" s="9"/>
+      <c r="AT51" s="12"/>
     </row>
     <row r="52" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="9"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="12"/>
       <c r="J52" s="1"/>
       <c r="M52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-      <c r="W52" s="9"/>
+      <c r="W52" s="12"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="AG52" s="1"/>
-      <c r="AM52" s="9"/>
+      <c r="AM52" s="12"/>
       <c r="AR52" s="1"/>
-      <c r="AT52" s="9"/>
+      <c r="AT52" s="12"/>
     </row>
     <row r="53" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="15"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="14"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="15"/>
       <c r="J53" s="1"/>
       <c r="M53" s="1"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
+      <c r="U53" s="12"/>
+      <c r="V53" s="12"/>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="AB53" s="9"/>
+      <c r="AB53" s="12"/>
       <c r="AG53" s="1"/>
       <c r="AM53" s="1"/>
       <c r="AT53" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F69" s="9"/>
+      <c r="F69" s="12"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4451,151 +4369,151 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="126.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="H1" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
+      <c r="I1" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
+      <c r="A2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D4" s="24" t="s">
+      <c r="A4" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="D4" s="25" t="s">
         <v>128</v>
       </c>
+      <c r="E4" s="25" t="s">
+        <v>129</v>
+      </c>
       <c r="I4" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="1"/>
       <c r="D6" s="1"/>
     </row>
@@ -4627,445 +4545,451 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y86"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Y85"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="80.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
+      <c r="D1" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
+      <c r="A2" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29" t="s">
+      <c r="B4" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="33"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -5089,91 +5013,91 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -5197,124 +5121,124 @@
       <c r="Y20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="9"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="9"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="9"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="29"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -5338,199 +5262,199 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="9"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12"/>
+      <c r="Y31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="29"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="9"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="34"/>
+      <c r="V32" s="34"/>
+      <c r="W32" s="34"/>
+      <c r="X32" s="34"/>
+      <c r="Y32" s="34"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="33"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="33"/>
-      <c r="V33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="33"/>
-      <c r="Y33" s="33"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="29"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -5554,10 +5478,10 @@
       <c r="Y34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -5581,10 +5505,10 @@
       <c r="Y35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="29"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -5608,10 +5532,10 @@
       <c r="Y36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="29"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -5635,228 +5559,204 @@
       <c r="Y37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="29"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="35"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="29"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="34"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="35"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="29"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="34"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="35"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="29"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="34"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="29"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="34"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="29"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="34"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="35"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="29"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="34"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="29"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="34"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="35"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="29"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="34"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="35"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="29"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="34"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="35"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="29"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="34"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="35"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="29"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="34"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="35"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="29"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="34"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="35"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="29"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="34"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="35"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="29"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="34"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="35"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="34"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="35"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="34"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="35"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="29"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="34"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="35"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="29"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="34"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="35"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="34"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="35"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="29"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="34"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="35"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="29"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="34"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="35"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="29"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="34"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="35"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="29"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="34"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="35"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="29"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="34"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="35"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="29"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="34"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="35"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="29"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="34"/>
+      <c r="A64" s="30"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="35"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="29"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="34"/>
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="35"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="29"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="34"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="29"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="34"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="35"/>
+    </row>
+    <row r="67" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="14"/>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="13"/>
+      <c r="A68" s="14"/>
       <c r="B68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="13"/>
+      <c r="A69" s="14"/>
       <c r="B69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="13"/>
+      <c r="A70" s="14"/>
       <c r="B70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="13"/>
+      <c r="A71" s="14"/>
       <c r="B71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="13"/>
+      <c r="A72" s="14"/>
       <c r="B72" s="1"/>
     </row>
-    <row r="73" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="13"/>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="1"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5868,42 +5768,39 @@
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="1"/>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="14"/>
       <c r="B77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="13"/>
+      <c r="A78" s="36"/>
       <c r="B78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="35"/>
+      <c r="A79" s="14"/>
       <c r="B79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="13"/>
+      <c r="A80" s="14"/>
       <c r="B80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="13"/>
+      <c r="A81" s="14"/>
       <c r="B81" s="1"/>
     </row>
     <row r="82" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="13"/>
+      <c r="A82" s="14"/>
       <c r="B82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="13"/>
+      <c r="A83" s="14"/>
       <c r="B83" s="1"/>
     </row>
-    <row r="84" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="13"/>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="1"/>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
+++ b/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Thing" sheetId="1" state="visible" r:id="rId2"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="138">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -431,6 +431,12 @@
   </si>
   <si>
     <t xml:space="preserve">Evolve into #1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evolutionAffinityRequirementNotMet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1 doesn’t trust you enough for evolution. Try again after befriending them.</t>
   </si>
 </sst>
 </file>
@@ -442,7 +448,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -485,11 +491,6 @@
       <name val="Cascadia Code"/>
       <family val="3"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -681,7 +682,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -689,24 +690,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -717,12 +718,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -741,35 +742,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -777,15 +774,19 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -797,7 +798,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1340,7 +1341,7 @@
       <c r="AG4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" s="12" t="s">
+      <c r="AH4" s="7" t="s">
         <v>66</v>
       </c>
       <c r="AJ4" s="1" t="n">
@@ -1355,7 +1356,7 @@
       </c>
       <c r="AW4" s="1"/>
       <c r="AX4" s="1"/>
-      <c r="AZ4" s="13" t="s">
+      <c r="AZ4" s="12" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1422,7 +1423,7 @@
       </c>
       <c r="AW5" s="1"/>
       <c r="AX5" s="1"/>
-      <c r="AZ5" s="13" t="s">
+      <c r="AZ5" s="12" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1489,7 +1490,7 @@
       </c>
       <c r="AW6" s="1"/>
       <c r="AX6" s="1"/>
-      <c r="AZ6" s="13" t="s">
+      <c r="AZ6" s="12" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1518,15 +1519,15 @@
       <c r="AX7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="12"/>
+      <c r="I8" s="7"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="12"/>
+      <c r="L8" s="7"/>
       <c r="M8" s="1"/>
       <c r="S8" s="9"/>
       <c r="U8" s="1"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="Y8" s="12"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="Y8" s="7"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
@@ -1538,7 +1539,7 @@
       <c r="AT8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="I9" s="1"/>
@@ -1547,13 +1548,13 @@
       <c r="S9" s="9"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
-      <c r="W9" s="12"/>
-      <c r="Y9" s="12"/>
+      <c r="W9" s="7"/>
+      <c r="Y9" s="7"/>
       <c r="Z9" s="10"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="12"/>
+      <c r="AB9" s="7"/>
       <c r="AC9" s="1"/>
-      <c r="AD9" s="14"/>
+      <c r="AD9" s="13"/>
       <c r="AE9" s="9"/>
       <c r="AF9" s="1"/>
       <c r="AJ9" s="1"/>
@@ -1563,7 +1564,7 @@
       <c r="AX9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="I10" s="1"/>
@@ -1572,13 +1573,13 @@
       <c r="S10" s="9"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
-      <c r="W10" s="12"/>
-      <c r="Y10" s="12"/>
+      <c r="W10" s="7"/>
+      <c r="Y10" s="7"/>
       <c r="Z10" s="10"/>
       <c r="AA10" s="1"/>
-      <c r="AB10" s="12"/>
+      <c r="AB10" s="7"/>
       <c r="AC10" s="1"/>
-      <c r="AD10" s="14"/>
+      <c r="AD10" s="13"/>
       <c r="AE10" s="9"/>
       <c r="AF10" s="1"/>
       <c r="AJ10" s="1"/>
@@ -1588,7 +1589,7 @@
       <c r="AX10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="I11" s="1"/>
@@ -1597,13 +1598,13 @@
       <c r="S11" s="9"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
-      <c r="W11" s="12"/>
-      <c r="Y11" s="12"/>
+      <c r="W11" s="7"/>
+      <c r="Y11" s="7"/>
       <c r="Z11" s="10"/>
       <c r="AA11" s="1"/>
-      <c r="AB11" s="12"/>
+      <c r="AB11" s="7"/>
       <c r="AC11" s="1"/>
-      <c r="AD11" s="14"/>
+      <c r="AD11" s="13"/>
       <c r="AE11" s="9"/>
       <c r="AF11" s="1"/>
       <c r="AJ11" s="1"/>
@@ -1614,7 +1615,7 @@
       <c r="AZ11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="I12" s="1"/>
@@ -1623,13 +1624,13 @@
       <c r="S12" s="9"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-      <c r="W12" s="12"/>
-      <c r="Y12" s="12"/>
+      <c r="W12" s="7"/>
+      <c r="Y12" s="7"/>
       <c r="Z12" s="10"/>
       <c r="AA12" s="1"/>
-      <c r="AB12" s="12"/>
+      <c r="AB12" s="7"/>
       <c r="AC12" s="1"/>
-      <c r="AD12" s="14"/>
+      <c r="AD12" s="13"/>
       <c r="AE12" s="9"/>
       <c r="AF12" s="1"/>
       <c r="AJ12" s="1"/>
@@ -1639,7 +1640,7 @@
       <c r="AX12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="I13" s="1"/>
@@ -1648,13 +1649,13 @@
       <c r="S13" s="9"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
-      <c r="W13" s="12"/>
-      <c r="Y13" s="12"/>
+      <c r="W13" s="7"/>
+      <c r="Y13" s="7"/>
       <c r="Z13" s="10"/>
       <c r="AA13" s="1"/>
-      <c r="AB13" s="12"/>
+      <c r="AB13" s="7"/>
       <c r="AC13" s="1"/>
-      <c r="AD13" s="14"/>
+      <c r="AD13" s="13"/>
       <c r="AE13" s="9"/>
       <c r="AF13" s="1"/>
       <c r="AJ13" s="1"/>
@@ -1664,7 +1665,7 @@
       <c r="AX13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14"/>
+      <c r="A14" s="13"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="I14" s="1"/>
@@ -1673,13 +1674,13 @@
       <c r="S14" s="9"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
-      <c r="W14" s="12"/>
-      <c r="Y14" s="12"/>
+      <c r="W14" s="7"/>
+      <c r="Y14" s="7"/>
       <c r="Z14" s="10"/>
       <c r="AA14" s="1"/>
-      <c r="AB14" s="12"/>
+      <c r="AB14" s="7"/>
       <c r="AC14" s="1"/>
-      <c r="AD14" s="14"/>
+      <c r="AD14" s="13"/>
       <c r="AE14" s="9"/>
       <c r="AF14" s="1"/>
       <c r="AJ14" s="1"/>
@@ -1697,7 +1698,7 @@
       <c r="S15" s="9"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
-      <c r="V15" s="12"/>
+      <c r="V15" s="7"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
@@ -1712,46 +1713,46 @@
       <c r="AX15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="I16" s="12"/>
+      <c r="I16" s="7"/>
       <c r="K16" s="1"/>
       <c r="M16" s="8"/>
       <c r="S16" s="9"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="Y16" s="12"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="Y16" s="7"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
       <c r="AF16" s="1"/>
-      <c r="AH16" s="12"/>
-      <c r="AI16" s="14"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="13"/>
       <c r="AJ16" s="1"/>
       <c r="AP16" s="1"/>
       <c r="AT16" s="9"/>
       <c r="AV16" s="1"/>
       <c r="AW16" s="1"/>
       <c r="AX16" s="1"/>
-      <c r="AY16" s="14"/>
+      <c r="AY16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15"/>
-      <c r="D17" s="15"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="D17" s="14"/>
       <c r="E17" s="1"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="7"/>
       <c r="K17" s="1"/>
       <c r="M17" s="8"/>
       <c r="N17" s="1"/>
       <c r="S17" s="9"/>
       <c r="U17" s="1"/>
-      <c r="V17" s="12"/>
+      <c r="V17" s="7"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
@@ -1759,28 +1760,28 @@
       <c r="AD17" s="1"/>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1"/>
-      <c r="AI17" s="14"/>
+      <c r="AI17" s="13"/>
       <c r="AJ17" s="1"/>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
       <c r="AT17" s="9"/>
-      <c r="AY17" s="14"/>
+      <c r="AY17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="15"/>
+      <c r="D18" s="14"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="7"/>
       <c r="K18" s="1"/>
       <c r="M18" s="8"/>
       <c r="N18" s="1"/>
       <c r="S18" s="9"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
-      <c r="V18" s="12"/>
-      <c r="Y18" s="12"/>
+      <c r="V18" s="7"/>
+      <c r="Y18" s="7"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
@@ -1788,192 +1789,192 @@
       <c r="AD18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
-      <c r="AI18" s="14"/>
+      <c r="AI18" s="13"/>
       <c r="AJ18" s="1"/>
       <c r="AT18" s="9"/>
       <c r="AV18" s="1"/>
-      <c r="AY18" s="14"/>
+      <c r="AY18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14"/>
+      <c r="A19" s="13"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="I19" s="12"/>
+      <c r="I19" s="7"/>
       <c r="K19" s="1"/>
       <c r="M19" s="8"/>
       <c r="S19" s="9"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
-      <c r="V19" s="12"/>
+      <c r="V19" s="7"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
       <c r="AF19" s="1"/>
-      <c r="AI19" s="14"/>
+      <c r="AI19" s="13"/>
       <c r="AJ19" s="1"/>
       <c r="AP19" s="1"/>
       <c r="AT19" s="9"/>
       <c r="AV19" s="1"/>
       <c r="AW19" s="1"/>
       <c r="AX19" s="1"/>
-      <c r="AY19" s="14"/>
+      <c r="AY19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14"/>
-      <c r="I20" s="12"/>
+      <c r="A20" s="13"/>
+      <c r="I20" s="7"/>
       <c r="K20" s="1"/>
       <c r="M20" s="8"/>
       <c r="S20" s="9"/>
       <c r="U20" s="1"/>
-      <c r="V20" s="12"/>
-      <c r="Y20" s="12"/>
+      <c r="V20" s="7"/>
+      <c r="Y20" s="7"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
       <c r="AF20" s="1"/>
-      <c r="AI20" s="14"/>
+      <c r="AI20" s="13"/>
       <c r="AT20" s="9"/>
-      <c r="AY20" s="14"/>
+      <c r="AY20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14"/>
-      <c r="I21" s="12"/>
+      <c r="A21" s="13"/>
+      <c r="I21" s="7"/>
       <c r="K21" s="1"/>
       <c r="M21" s="8"/>
       <c r="S21" s="9"/>
       <c r="U21" s="1"/>
-      <c r="V21" s="12"/>
+      <c r="V21" s="7"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
       <c r="AF21" s="1"/>
-      <c r="AI21" s="14"/>
+      <c r="AI21" s="13"/>
       <c r="AT21" s="9"/>
-      <c r="AY21" s="14"/>
+      <c r="AY21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14"/>
-      <c r="I22" s="12"/>
+      <c r="A22" s="13"/>
+      <c r="I22" s="7"/>
       <c r="K22" s="1"/>
       <c r="M22" s="8"/>
       <c r="S22" s="9"/>
       <c r="U22" s="1"/>
-      <c r="V22" s="12"/>
-      <c r="Y22" s="12"/>
+      <c r="V22" s="7"/>
+      <c r="Y22" s="7"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
       <c r="AF22" s="1"/>
-      <c r="AI22" s="14"/>
+      <c r="AI22" s="13"/>
       <c r="AT22" s="9"/>
-      <c r="AY22" s="14"/>
+      <c r="AY22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14"/>
-      <c r="I23" s="12"/>
+      <c r="A23" s="13"/>
+      <c r="I23" s="7"/>
       <c r="K23" s="1"/>
       <c r="M23" s="8"/>
       <c r="S23" s="9"/>
       <c r="U23" s="1"/>
-      <c r="V23" s="12"/>
+      <c r="V23" s="7"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
       <c r="AF23" s="1"/>
-      <c r="AI23" s="14"/>
+      <c r="AI23" s="13"/>
       <c r="AT23" s="9"/>
-      <c r="AY23" s="14"/>
+      <c r="AY23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14"/>
-      <c r="I24" s="12"/>
+      <c r="A24" s="13"/>
+      <c r="I24" s="7"/>
       <c r="K24" s="1"/>
       <c r="M24" s="8"/>
       <c r="S24" s="9"/>
       <c r="U24" s="1"/>
-      <c r="V24" s="12"/>
+      <c r="V24" s="7"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
       <c r="AF24" s="1"/>
-      <c r="AI24" s="14"/>
+      <c r="AI24" s="13"/>
       <c r="AT24" s="9"/>
-      <c r="AY24" s="14"/>
+      <c r="AY24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14"/>
-      <c r="I25" s="12"/>
+      <c r="A25" s="13"/>
+      <c r="I25" s="7"/>
       <c r="K25" s="1"/>
       <c r="M25" s="8"/>
       <c r="S25" s="9"/>
       <c r="U25" s="1"/>
-      <c r="V25" s="12"/>
+      <c r="V25" s="7"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
       <c r="AF25" s="1"/>
-      <c r="AI25" s="14"/>
+      <c r="AI25" s="13"/>
       <c r="AT25" s="9"/>
-      <c r="AY25" s="14"/>
+      <c r="AY25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14"/>
-      <c r="I26" s="12"/>
+      <c r="A26" s="13"/>
+      <c r="I26" s="7"/>
       <c r="K26" s="1"/>
       <c r="M26" s="8"/>
       <c r="S26" s="9"/>
       <c r="U26" s="1"/>
-      <c r="V26" s="12"/>
+      <c r="V26" s="7"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
       <c r="AF26" s="1"/>
-      <c r="AI26" s="14"/>
+      <c r="AI26" s="13"/>
       <c r="AT26" s="9"/>
-      <c r="AY26" s="14"/>
+      <c r="AY26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14"/>
-      <c r="I27" s="12"/>
+      <c r="A27" s="13"/>
+      <c r="I27" s="7"/>
       <c r="K27" s="1"/>
       <c r="M27" s="8"/>
       <c r="S27" s="9"/>
       <c r="U27" s="1"/>
-      <c r="V27" s="12"/>
+      <c r="V27" s="7"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
       <c r="AF27" s="1"/>
-      <c r="AI27" s="14"/>
+      <c r="AI27" s="13"/>
       <c r="AT27" s="9"/>
-      <c r="AY27" s="14"/>
+      <c r="AY27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="12"/>
+      <c r="I28" s="7"/>
       <c r="K28" s="1"/>
       <c r="M28" s="8"/>
       <c r="S28" s="9"/>
       <c r="U28" s="1"/>
-      <c r="V28" s="12"/>
-      <c r="Y28" s="12"/>
+      <c r="V28" s="7"/>
+      <c r="Y28" s="7"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
@@ -1983,13 +1984,13 @@
       <c r="AT28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I29" s="12"/>
+      <c r="I29" s="7"/>
       <c r="K29" s="1"/>
       <c r="M29" s="8"/>
       <c r="S29" s="9"/>
       <c r="U29" s="1"/>
-      <c r="V29" s="12"/>
-      <c r="Y29" s="12"/>
+      <c r="V29" s="7"/>
+      <c r="Y29" s="7"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
@@ -1999,13 +2000,13 @@
       <c r="AT29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I30" s="12"/>
+      <c r="I30" s="7"/>
       <c r="K30" s="1"/>
       <c r="M30" s="8"/>
       <c r="S30" s="9"/>
       <c r="U30" s="1"/>
-      <c r="V30" s="12"/>
-      <c r="Y30" s="12"/>
+      <c r="V30" s="7"/>
+      <c r="Y30" s="7"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
@@ -2015,13 +2016,13 @@
       <c r="AT30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I31" s="12"/>
+      <c r="I31" s="7"/>
       <c r="K31" s="1"/>
       <c r="M31" s="8"/>
       <c r="S31" s="9"/>
       <c r="U31" s="1"/>
-      <c r="V31" s="12"/>
-      <c r="Y31" s="12"/>
+      <c r="V31" s="7"/>
+      <c r="Y31" s="7"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -2031,13 +2032,13 @@
       <c r="AT31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I32" s="12"/>
+      <c r="I32" s="7"/>
       <c r="K32" s="1"/>
       <c r="M32" s="8"/>
       <c r="S32" s="9"/>
       <c r="U32" s="1"/>
-      <c r="V32" s="12"/>
-      <c r="Y32" s="12"/>
+      <c r="V32" s="7"/>
+      <c r="Y32" s="7"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
@@ -2047,15 +2048,15 @@
       <c r="AT32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F33" s="12"/>
-      <c r="I33" s="12"/>
+      <c r="F33" s="7"/>
+      <c r="I33" s="7"/>
       <c r="K33" s="1"/>
       <c r="M33" s="8"/>
       <c r="S33" s="9"/>
       <c r="U33" s="1"/>
-      <c r="V33" s="12"/>
-      <c r="W33" s="12"/>
-      <c r="Y33" s="12"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="Y33" s="7"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -2065,15 +2066,15 @@
       <c r="AT33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F34" s="12"/>
-      <c r="I34" s="12"/>
+      <c r="F34" s="7"/>
+      <c r="I34" s="7"/>
       <c r="K34" s="1"/>
       <c r="M34" s="8"/>
       <c r="S34" s="9"/>
       <c r="U34" s="1"/>
-      <c r="V34" s="12"/>
-      <c r="W34" s="12"/>
-      <c r="Y34" s="12"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
+      <c r="Y34" s="7"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
@@ -2083,15 +2084,15 @@
       <c r="AT34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F35" s="12"/>
-      <c r="I35" s="12"/>
+      <c r="F35" s="7"/>
+      <c r="I35" s="7"/>
       <c r="K35" s="1"/>
       <c r="M35" s="8"/>
       <c r="S35" s="9"/>
       <c r="U35" s="1"/>
-      <c r="V35" s="12"/>
-      <c r="W35" s="12"/>
-      <c r="Y35" s="12"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="Y35" s="7"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
@@ -2101,15 +2102,15 @@
       <c r="AT35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F36" s="12"/>
-      <c r="I36" s="12"/>
+      <c r="F36" s="7"/>
+      <c r="I36" s="7"/>
       <c r="K36" s="1"/>
       <c r="M36" s="8"/>
       <c r="S36" s="9"/>
       <c r="U36" s="1"/>
-      <c r="V36" s="12"/>
-      <c r="W36" s="12"/>
-      <c r="Y36" s="12"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7"/>
+      <c r="Y36" s="7"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
@@ -2119,14 +2120,14 @@
       <c r="AT36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F37" s="12"/>
-      <c r="I37" s="12"/>
+      <c r="F37" s="7"/>
+      <c r="I37" s="7"/>
       <c r="K37" s="1"/>
       <c r="M37" s="8"/>
       <c r="S37" s="9"/>
       <c r="U37" s="1"/>
-      <c r="V37" s="12"/>
-      <c r="W37" s="12"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
@@ -2134,17 +2135,17 @@
       <c r="AD37" s="1"/>
       <c r="AF37" s="1"/>
       <c r="AT37" s="9"/>
-      <c r="AY37" s="12"/>
+      <c r="AY37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F38" s="12"/>
-      <c r="I38" s="12"/>
+      <c r="F38" s="7"/>
+      <c r="I38" s="7"/>
       <c r="K38" s="1"/>
       <c r="M38" s="8"/>
       <c r="S38" s="9"/>
       <c r="U38" s="1"/>
-      <c r="V38" s="12"/>
-      <c r="W38" s="12"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
@@ -2152,17 +2153,17 @@
       <c r="AD38" s="1"/>
       <c r="AF38" s="1"/>
       <c r="AT38" s="9"/>
-      <c r="AY38" s="12"/>
+      <c r="AY38" s="7"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F39" s="12"/>
-      <c r="I39" s="12"/>
+      <c r="F39" s="7"/>
+      <c r="I39" s="7"/>
       <c r="K39" s="1"/>
       <c r="M39" s="8"/>
       <c r="S39" s="9"/>
       <c r="U39" s="1"/>
-      <c r="V39" s="12"/>
-      <c r="W39" s="12"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
@@ -2170,79 +2171,79 @@
       <c r="AD39" s="1"/>
       <c r="AF39" s="1"/>
       <c r="AT39" s="9"/>
-      <c r="AY39" s="12"/>
+      <c r="AY39" s="7"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="I40" s="12"/>
+      <c r="A40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="I40" s="7"/>
       <c r="K40" s="1"/>
       <c r="M40" s="8"/>
       <c r="S40" s="9"/>
       <c r="U40" s="1"/>
-      <c r="V40" s="12"/>
-      <c r="W40" s="12"/>
-      <c r="Y40" s="12"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
+      <c r="Y40" s="7"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
       <c r="AF40" s="1"/>
-      <c r="AI40" s="12"/>
+      <c r="AI40" s="7"/>
       <c r="AT40" s="9"/>
-      <c r="AY40" s="12"/>
+      <c r="AY40" s="7"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="14"/>
-      <c r="F41" s="12"/>
-      <c r="I41" s="12"/>
+      <c r="A41" s="13"/>
+      <c r="F41" s="7"/>
+      <c r="I41" s="7"/>
       <c r="K41" s="1"/>
       <c r="M41" s="8"/>
       <c r="S41" s="9"/>
       <c r="U41" s="1"/>
-      <c r="V41" s="12"/>
-      <c r="W41" s="12"/>
-      <c r="Y41" s="12"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="Y41" s="7"/>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
       <c r="AF41" s="1"/>
-      <c r="AI41" s="14"/>
+      <c r="AI41" s="13"/>
       <c r="AT41" s="9"/>
-      <c r="AY41" s="14"/>
+      <c r="AY41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="14"/>
-      <c r="I42" s="12"/>
+      <c r="A42" s="13"/>
+      <c r="I42" s="7"/>
       <c r="K42" s="1"/>
       <c r="M42" s="8"/>
       <c r="S42" s="9"/>
       <c r="U42" s="1"/>
-      <c r="V42" s="12"/>
-      <c r="W42" s="12"/>
-      <c r="Y42" s="12"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="7"/>
+      <c r="Y42" s="7"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
       <c r="AF42" s="1"/>
-      <c r="AI42" s="14"/>
+      <c r="AI42" s="13"/>
       <c r="AT42" s="9"/>
-      <c r="AY42" s="14"/>
+      <c r="AY42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F43" s="12"/>
+      <c r="F43" s="7"/>
       <c r="I43" s="1"/>
       <c r="K43" s="1"/>
       <c r="M43" s="8"/>
       <c r="S43" s="9"/>
       <c r="U43" s="1"/>
-      <c r="V43" s="12"/>
-      <c r="W43" s="12"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
@@ -2252,20 +2253,20 @@
       <c r="AT43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F44" s="12"/>
+      <c r="F44" s="7"/>
       <c r="I44" s="1"/>
       <c r="K44" s="1"/>
       <c r="M44" s="8"/>
       <c r="S44" s="9"/>
       <c r="U44" s="1"/>
-      <c r="V44" s="12"/>
-      <c r="W44" s="12"/>
+      <c r="V44" s="7"/>
+      <c r="W44" s="7"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
       <c r="AF44" s="1"/>
-      <c r="AH44" s="12"/>
+      <c r="AH44" s="7"/>
       <c r="AT44" s="9"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2294,8 +2295,8 @@
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
       <c r="AF46" s="1"/>
-      <c r="AL46" s="12"/>
-      <c r="AM46" s="12"/>
+      <c r="AL46" s="7"/>
+      <c r="AM46" s="7"/>
       <c r="AT46" s="9"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2304,7 +2305,7 @@
       <c r="M47" s="8"/>
       <c r="S47" s="9"/>
       <c r="U47" s="1"/>
-      <c r="Y47" s="12"/>
+      <c r="Y47" s="7"/>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
@@ -2322,7 +2323,7 @@
       <c r="S48" s="9"/>
       <c r="U48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AA48" s="12"/>
+      <c r="AA48" s="7"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
@@ -2339,12 +2340,12 @@
       <c r="S49" s="9"/>
       <c r="U49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AA49" s="12"/>
+      <c r="AA49" s="7"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
       <c r="AF49" s="1"/>
-      <c r="AI49" s="12"/>
+      <c r="AI49" s="7"/>
       <c r="AL49" s="1"/>
       <c r="AN49" s="1"/>
       <c r="AP49" s="1"/>
@@ -2362,7 +2363,7 @@
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
       <c r="AF50" s="1"/>
-      <c r="AI50" s="12"/>
+      <c r="AI50" s="7"/>
       <c r="AL50" s="1"/>
       <c r="AN50" s="1"/>
       <c r="AP50" s="1"/>
@@ -2374,14 +2375,14 @@
       <c r="M51" s="8"/>
       <c r="S51" s="9"/>
       <c r="U51" s="1"/>
-      <c r="Y51" s="12"/>
+      <c r="Y51" s="7"/>
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
       <c r="AF51" s="1"/>
-      <c r="AI51" s="12"/>
+      <c r="AI51" s="7"/>
       <c r="AL51" s="1"/>
       <c r="AM51" s="1"/>
       <c r="AN51" s="1"/>
@@ -2395,12 +2396,12 @@
       <c r="S52" s="9"/>
       <c r="U52" s="1"/>
       <c r="Z52" s="1"/>
-      <c r="AA52" s="12"/>
+      <c r="AA52" s="7"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
       <c r="AF52" s="1"/>
-      <c r="AI52" s="12"/>
+      <c r="AI52" s="7"/>
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
       <c r="AN52" s="1"/>
@@ -2419,7 +2420,7 @@
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
       <c r="AF53" s="1"/>
-      <c r="AI53" s="12"/>
+      <c r="AI53" s="7"/>
       <c r="AL53" s="1"/>
       <c r="AM53" s="1"/>
       <c r="AN53" s="1"/>
@@ -2432,14 +2433,14 @@
       <c r="M54" s="8"/>
       <c r="S54" s="9"/>
       <c r="U54" s="1"/>
-      <c r="Y54" s="12"/>
+      <c r="Y54" s="7"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
       <c r="AF54" s="1"/>
-      <c r="AI54" s="12"/>
+      <c r="AI54" s="7"/>
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
       <c r="AN54" s="1"/>
@@ -2453,12 +2454,12 @@
       <c r="S55" s="9"/>
       <c r="U55" s="1"/>
       <c r="Z55" s="1"/>
-      <c r="AA55" s="12"/>
+      <c r="AA55" s="7"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
       <c r="AF55" s="1"/>
-      <c r="AI55" s="12"/>
+      <c r="AI55" s="7"/>
       <c r="AL55" s="1"/>
       <c r="AM55" s="1"/>
       <c r="AN55" s="1"/>
@@ -2477,7 +2478,7 @@
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
       <c r="AF56" s="1"/>
-      <c r="AI56" s="12"/>
+      <c r="AI56" s="7"/>
       <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
       <c r="AN56" s="1"/>
@@ -2490,14 +2491,14 @@
       <c r="M57" s="8"/>
       <c r="S57" s="9"/>
       <c r="U57" s="1"/>
-      <c r="Y57" s="12"/>
+      <c r="Y57" s="7"/>
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
       <c r="AF57" s="1"/>
-      <c r="AI57" s="12"/>
+      <c r="AI57" s="7"/>
       <c r="AL57" s="1"/>
       <c r="AM57" s="1"/>
       <c r="AN57" s="1"/>
@@ -2516,7 +2517,7 @@
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
       <c r="AF58" s="1"/>
-      <c r="AI58" s="12"/>
+      <c r="AI58" s="7"/>
       <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
       <c r="AN58" s="1"/>
@@ -2529,14 +2530,14 @@
       <c r="M59" s="8"/>
       <c r="S59" s="9"/>
       <c r="U59" s="1"/>
-      <c r="Y59" s="12"/>
+      <c r="Y59" s="7"/>
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
       <c r="AF59" s="1"/>
-      <c r="AI59" s="12"/>
+      <c r="AI59" s="7"/>
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
       <c r="AN59" s="1"/>
@@ -2555,7 +2556,7 @@
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
       <c r="AF60" s="1"/>
-      <c r="AI60" s="12"/>
+      <c r="AI60" s="7"/>
       <c r="AL60" s="1"/>
       <c r="AM60" s="1"/>
       <c r="AP60" s="1"/>
@@ -2573,7 +2574,7 @@
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
       <c r="AF61" s="1"/>
-      <c r="AI61" s="12"/>
+      <c r="AI61" s="7"/>
       <c r="AL61" s="1"/>
       <c r="AM61" s="1"/>
       <c r="AP61" s="1"/>
@@ -2585,16 +2586,16 @@
       <c r="M62" s="8"/>
       <c r="S62" s="9"/>
       <c r="U62" s="1"/>
-      <c r="Y62" s="12"/>
+      <c r="Y62" s="7"/>
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
       <c r="AF62" s="1"/>
-      <c r="AI62" s="12"/>
-      <c r="AL62" s="12"/>
-      <c r="AM62" s="12"/>
+      <c r="AI62" s="7"/>
+      <c r="AL62" s="7"/>
+      <c r="AM62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I63" s="1"/>
@@ -2602,21 +2603,21 @@
       <c r="M63" s="8"/>
       <c r="S63" s="9"/>
       <c r="U63" s="1"/>
-      <c r="Y63" s="12"/>
+      <c r="Y63" s="7"/>
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
       <c r="AF63" s="1"/>
-      <c r="AI63" s="12"/>
-      <c r="AK63" s="12"/>
+      <c r="AI63" s="7"/>
+      <c r="AK63" s="7"/>
       <c r="AL63" s="1"/>
       <c r="AM63" s="1"/>
     </row>
     <row r="64" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="16"/>
-      <c r="C64" s="15"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="14"/>
       <c r="E64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -2625,12 +2626,12 @@
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
-      <c r="S64" s="17"/>
+      <c r="S64" s="16"/>
       <c r="U64" s="1"/>
-      <c r="V64" s="18"/>
-      <c r="W64" s="12"/>
-      <c r="Z64" s="12"/>
-      <c r="AA64" s="12"/>
+      <c r="V64" s="17"/>
+      <c r="W64" s="7"/>
+      <c r="Z64" s="7"/>
+      <c r="AA64" s="7"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
@@ -2643,8 +2644,8 @@
       <c r="AT64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="16"/>
-      <c r="C65" s="15"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="14"/>
       <c r="E65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -2653,12 +2654,12 @@
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
-      <c r="S65" s="17"/>
+      <c r="S65" s="16"/>
       <c r="U65" s="1"/>
-      <c r="V65" s="18"/>
-      <c r="W65" s="12"/>
-      <c r="Z65" s="12"/>
-      <c r="AA65" s="12"/>
+      <c r="V65" s="17"/>
+      <c r="W65" s="7"/>
+      <c r="Z65" s="7"/>
+      <c r="AA65" s="7"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
@@ -2671,8 +2672,8 @@
       <c r="AT65" s="9"/>
     </row>
     <row r="66" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="16"/>
-      <c r="C66" s="15"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="14"/>
       <c r="E66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -2681,12 +2682,12 @@
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
-      <c r="S66" s="17"/>
+      <c r="S66" s="16"/>
       <c r="U66" s="1"/>
-      <c r="V66" s="18"/>
-      <c r="W66" s="12"/>
-      <c r="Z66" s="12"/>
-      <c r="AA66" s="12"/>
+      <c r="V66" s="17"/>
+      <c r="W66" s="7"/>
+      <c r="Z66" s="7"/>
+      <c r="AA66" s="7"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
@@ -2702,7 +2703,7 @@
       <c r="I67" s="1"/>
       <c r="K67" s="1"/>
       <c r="M67" s="1"/>
-      <c r="S67" s="17"/>
+      <c r="S67" s="16"/>
       <c r="U67" s="1"/>
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
@@ -2716,7 +2717,7 @@
       <c r="I68" s="1"/>
       <c r="K68" s="1"/>
       <c r="M68" s="1"/>
-      <c r="S68" s="17"/>
+      <c r="S68" s="16"/>
       <c r="U68" s="1"/>
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
@@ -2728,11 +2729,11 @@
       <c r="AT68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D69" s="15"/>
+      <c r="D69" s="14"/>
       <c r="I69" s="1"/>
       <c r="K69" s="1"/>
       <c r="M69" s="1"/>
-      <c r="S69" s="17"/>
+      <c r="S69" s="16"/>
       <c r="U69" s="1"/>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
@@ -3146,319 +3147,319 @@
       <c r="AW3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="15" t="n">
         <v>7869001</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
       <c r="M4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12" t="s">
+      <c r="N4" s="7"/>
+      <c r="O4" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="P4" s="12" t="n">
+      <c r="P4" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" s="12" t="n">
+      <c r="Q4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="12" t="n">
+      <c r="R4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="S4" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12" t="s">
+      <c r="T4" s="7"/>
+      <c r="U4" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="V4" s="12" t="s">
+      <c r="V4" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="W4" s="12" t="s">
+      <c r="W4" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="X4" s="12" t="s">
+      <c r="X4" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="Y4" s="12" t="s">
+      <c r="Y4" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12" t="s">
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="12" t="s">
+      <c r="AD4" s="7"/>
+      <c r="AE4" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12" t="s">
+      <c r="AF4" s="7"/>
+      <c r="AG4" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="12"/>
-      <c r="AI4" s="12"/>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="12"/>
-      <c r="AL4" s="12"/>
-      <c r="AM4" s="12"/>
+      <c r="AH4" s="7"/>
+      <c r="AI4" s="7"/>
+      <c r="AJ4" s="7"/>
+      <c r="AK4" s="7"/>
+      <c r="AL4" s="7"/>
+      <c r="AM4" s="7"/>
       <c r="AN4" s="10"/>
-      <c r="AO4" s="12"/>
-      <c r="AP4" s="12"/>
-      <c r="AQ4" s="12"/>
-      <c r="AR4" s="12"/>
-      <c r="AS4" s="12"/>
-      <c r="AT4" s="12"/>
-      <c r="AU4" s="12"/>
-      <c r="AV4" s="12"/>
-      <c r="AW4" s="12"/>
+      <c r="AO4" s="7"/>
+      <c r="AP4" s="7"/>
+      <c r="AQ4" s="7"/>
+      <c r="AR4" s="7"/>
+      <c r="AS4" s="7"/>
+      <c r="AT4" s="7"/>
+      <c r="AU4" s="7"/>
+      <c r="AV4" s="7"/>
+      <c r="AW4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="15" t="n">
         <v>7869002</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
       <c r="M5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12" t="s">
+      <c r="N5" s="7"/>
+      <c r="O5" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="P5" s="12" t="n">
+      <c r="P5" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="Q5" s="12" t="n">
+      <c r="Q5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="12" t="n">
+      <c r="R5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="S5" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12" t="s">
+      <c r="T5" s="7"/>
+      <c r="U5" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="V5" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="W5" s="12" t="s">
+      <c r="W5" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="X5" s="12" t="s">
+      <c r="X5" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="Y5" s="12" t="s">
+      <c r="Y5" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12" t="s">
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="12" t="s">
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="AF5" s="12"/>
-      <c r="AG5" s="12" t="s">
+      <c r="AF5" s="7"/>
+      <c r="AG5" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="12"/>
-      <c r="AJ5" s="12"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="12"/>
-      <c r="AM5" s="12"/>
+      <c r="AH5" s="7"/>
+      <c r="AI5" s="7"/>
+      <c r="AJ5" s="7"/>
+      <c r="AK5" s="7"/>
+      <c r="AL5" s="7"/>
+      <c r="AM5" s="7"/>
       <c r="AN5" s="10"/>
-      <c r="AO5" s="12"/>
-      <c r="AP5" s="12"/>
-      <c r="AQ5" s="12"/>
-      <c r="AR5" s="12"/>
-      <c r="AS5" s="12"/>
-      <c r="AT5" s="12"/>
-      <c r="AU5" s="12"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="12"/>
+      <c r="AO5" s="7"/>
+      <c r="AP5" s="7"/>
+      <c r="AQ5" s="7"/>
+      <c r="AR5" s="7"/>
+      <c r="AS5" s="7"/>
+      <c r="AT5" s="7"/>
+      <c r="AU5" s="7"/>
+      <c r="AV5" s="7"/>
+      <c r="AW5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>7869003</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="14"/>
+      <c r="D6" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
       <c r="M6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12" t="s">
+      <c r="N6" s="7"/>
+      <c r="O6" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="P6" s="12" t="n">
+      <c r="P6" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="S6" s="12" t="s">
+      <c r="S6" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12" t="s">
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="W6" s="12" t="s">
+      <c r="W6" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="X6" s="12" t="s">
+      <c r="X6" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="Y6" s="12" t="s">
+      <c r="Y6" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12" t="s">
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="AD6" s="12"/>
-      <c r="AE6" s="12" t="s">
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="12" t="s">
+      <c r="AF6" s="7"/>
+      <c r="AG6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AH6" s="12"/>
-      <c r="AI6" s="12"/>
-      <c r="AJ6" s="12"/>
-      <c r="AK6" s="12"/>
-      <c r="AL6" s="12"/>
-      <c r="AM6" s="12"/>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="12"/>
-      <c r="AQ6" s="12"/>
-      <c r="AR6" s="12"/>
-      <c r="AS6" s="12"/>
-      <c r="AT6" s="12"/>
-      <c r="AU6" s="12"/>
-      <c r="AV6" s="12"/>
-      <c r="AW6" s="12"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="7"/>
+      <c r="AJ6" s="7"/>
+      <c r="AK6" s="7"/>
+      <c r="AL6" s="7"/>
+      <c r="AM6" s="7"/>
+      <c r="AN6" s="7"/>
+      <c r="AO6" s="7"/>
+      <c r="AP6" s="7"/>
+      <c r="AQ6" s="7"/>
+      <c r="AR6" s="7"/>
+      <c r="AS6" s="7"/>
+      <c r="AT6" s="7"/>
+      <c r="AU6" s="7"/>
+      <c r="AV6" s="7"/>
+      <c r="AW6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="16"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="12"/>
-      <c r="J7" s="12"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="7"/>
+      <c r="J7" s="7"/>
       <c r="M7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="V7" s="19"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="V7" s="18"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="12"/>
+      <c r="Y7" s="7"/>
       <c r="Z7" s="1"/>
-      <c r="AB7" s="12"/>
-      <c r="AD7" s="12"/>
+      <c r="AB7" s="7"/>
+      <c r="AD7" s="7"/>
       <c r="AE7" s="1"/>
-      <c r="AG7" s="12"/>
-      <c r="AR7" s="12"/>
+      <c r="AG7" s="7"/>
+      <c r="AR7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="12"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="12"/>
+      <c r="J8" s="7"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
       <c r="T8" s="1"/>
-      <c r="V8" s="19"/>
+      <c r="V8" s="18"/>
       <c r="W8" s="1"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
       <c r="AA8" s="1"/>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="12"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
       <c r="AF8" s="1"/>
-      <c r="AG8" s="12"/>
+      <c r="AG8" s="7"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
@@ -3468,7 +3469,7 @@
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
-      <c r="AR8" s="12"/>
+      <c r="AR8" s="7"/>
       <c r="AS8" s="1"/>
       <c r="AT8" s="1"/>
       <c r="AU8" s="1"/>
@@ -3476,439 +3477,439 @@
       <c r="AW8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="16"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="12"/>
-      <c r="J9" s="12"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="7"/>
+      <c r="J9" s="7"/>
       <c r="M9" s="1"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="V9" s="19"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="V9" s="18"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AB9" s="12"/>
-      <c r="AD9" s="12"/>
-      <c r="AG9" s="12"/>
-      <c r="AR9" s="12"/>
+      <c r="AB9" s="7"/>
+      <c r="AD9" s="7"/>
+      <c r="AG9" s="7"/>
+      <c r="AR9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="16"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="12"/>
-      <c r="J10" s="12"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="7"/>
+      <c r="J10" s="7"/>
       <c r="M10" s="1"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="V10" s="19"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="V10" s="18"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AB10" s="12"/>
-      <c r="AD10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AR10" s="12"/>
+      <c r="AB10" s="7"/>
+      <c r="AD10" s="7"/>
+      <c r="AG10" s="7"/>
+      <c r="AR10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="16"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="12"/>
-      <c r="J11" s="12"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="7"/>
+      <c r="J11" s="7"/>
       <c r="M11" s="1"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="V11" s="19"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="V11" s="18"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AB11" s="12"/>
-      <c r="AD11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AR11" s="12"/>
+      <c r="AB11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AG11" s="7"/>
+      <c r="AR11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="16"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="12"/>
-      <c r="J12" s="12"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="7"/>
+      <c r="J12" s="7"/>
       <c r="M12" s="1"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="V12" s="19"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="V12" s="18"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-      <c r="AB12" s="12"/>
-      <c r="AD12" s="12"/>
-      <c r="AG12" s="12"/>
-      <c r="AR12" s="12"/>
+      <c r="AB12" s="7"/>
+      <c r="AD12" s="7"/>
+      <c r="AG12" s="7"/>
+      <c r="AR12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="15"/>
-      <c r="J13" s="12"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="14"/>
+      <c r="J13" s="7"/>
       <c r="M13" s="1"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="12"/>
+      <c r="S13" s="7"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
-      <c r="AB13" s="12"/>
-      <c r="AD13" s="12"/>
-      <c r="AE13" s="12"/>
-      <c r="AG13" s="12"/>
+      <c r="AB13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
+      <c r="AG13" s="7"/>
       <c r="AQ13" s="1"/>
       <c r="AR13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="16"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="15"/>
-      <c r="J14" s="12"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="14"/>
+      <c r="J14" s="7"/>
       <c r="M14" s="1"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
       <c r="R14" s="1"/>
-      <c r="S14" s="12"/>
+      <c r="S14" s="7"/>
       <c r="W14" s="1"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="12"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="7"/>
       <c r="Z14" s="1"/>
-      <c r="AB14" s="12"/>
-      <c r="AD14" s="12"/>
-      <c r="AE14" s="12"/>
-      <c r="AG14" s="12"/>
+      <c r="AB14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
+      <c r="AG14" s="7"/>
       <c r="AQ14" s="1"/>
       <c r="AR14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="16"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="15"/>
-      <c r="J15" s="12"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="14"/>
+      <c r="J15" s="7"/>
       <c r="M15" s="1"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="12"/>
+      <c r="S15" s="7"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
-      <c r="AB15" s="12"/>
-      <c r="AD15" s="12"/>
-      <c r="AE15" s="12"/>
-      <c r="AG15" s="12"/>
+      <c r="AB15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AG15" s="7"/>
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="16"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="15"/>
-      <c r="J16" s="12"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="14"/>
+      <c r="J16" s="7"/>
       <c r="M16" s="1"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
       <c r="R16" s="1"/>
-      <c r="S16" s="12"/>
+      <c r="S16" s="7"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-      <c r="Y16" s="12"/>
+      <c r="Y16" s="7"/>
       <c r="Z16" s="1"/>
-      <c r="AB16" s="12"/>
-      <c r="AD16" s="12"/>
-      <c r="AE16" s="12"/>
-      <c r="AG16" s="12"/>
+      <c r="AB16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AG16" s="7"/>
       <c r="AQ16" s="1"/>
       <c r="AR16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="16"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="15"/>
-      <c r="J17" s="12"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="14"/>
+      <c r="J17" s="7"/>
       <c r="M17" s="1"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
       <c r="R17" s="1"/>
-      <c r="S17" s="12"/>
+      <c r="S17" s="7"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-      <c r="AB17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AG17" s="12"/>
+      <c r="AB17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="7"/>
+      <c r="AG17" s="7"/>
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="16"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="15"/>
-      <c r="J18" s="12"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="14"/>
+      <c r="J18" s="7"/>
       <c r="M18" s="1"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
       <c r="R18" s="1"/>
-      <c r="S18" s="12"/>
+      <c r="S18" s="7"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
-      <c r="AB18" s="12"/>
-      <c r="AD18" s="12"/>
-      <c r="AE18" s="12"/>
-      <c r="AG18" s="12"/>
+      <c r="AB18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AG18" s="7"/>
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="16"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="15"/>
-      <c r="J19" s="12"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="14"/>
+      <c r="J19" s="7"/>
       <c r="M19" s="1"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
       <c r="R19" s="1"/>
-      <c r="S19" s="12"/>
+      <c r="S19" s="7"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
-      <c r="AB19" s="12"/>
-      <c r="AD19" s="12"/>
-      <c r="AE19" s="12"/>
-      <c r="AG19" s="12"/>
+      <c r="AB19" s="7"/>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="7"/>
+      <c r="AG19" s="7"/>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="16"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="12"/>
-      <c r="J20" s="12"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="7"/>
+      <c r="J20" s="7"/>
       <c r="M20" s="1"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
       <c r="R20" s="1"/>
-      <c r="S20" s="12"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="12"/>
+      <c r="S20" s="7"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="7"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
-      <c r="AB20" s="12"/>
-      <c r="AD20" s="12"/>
-      <c r="AG20" s="12"/>
+      <c r="AB20" s="7"/>
+      <c r="AD20" s="7"/>
+      <c r="AG20" s="7"/>
       <c r="AQ20" s="1"/>
       <c r="AR20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="16"/>
-      <c r="C21" s="23"/>
-      <c r="J21" s="12"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="22"/>
+      <c r="J21" s="7"/>
       <c r="M21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="12"/>
+      <c r="Q21" s="7"/>
       <c r="R21" s="1"/>
-      <c r="S21" s="12"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="12"/>
+      <c r="S21" s="7"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="7"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="12"/>
-      <c r="AA21" s="12"/>
+      <c r="Z21" s="7"/>
+      <c r="AA21" s="7"/>
       <c r="AE21" s="1"/>
-      <c r="AG21" s="12"/>
+      <c r="AG21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="16"/>
-      <c r="C22" s="23"/>
-      <c r="J22" s="12"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="22"/>
+      <c r="J22" s="7"/>
       <c r="M22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="12"/>
+      <c r="Q22" s="7"/>
       <c r="R22" s="1"/>
-      <c r="S22" s="12"/>
-      <c r="V22" s="18"/>
-      <c r="W22" s="12"/>
+      <c r="S22" s="7"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="7"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="12"/>
-      <c r="AA22" s="12"/>
-      <c r="AB22" s="12"/>
+      <c r="Z22" s="7"/>
+      <c r="AA22" s="7"/>
+      <c r="AB22" s="7"/>
       <c r="AE22" s="1"/>
-      <c r="AG22" s="12"/>
+      <c r="AG22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="16"/>
-      <c r="C23" s="23"/>
-      <c r="J23" s="12"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="22"/>
+      <c r="J23" s="7"/>
       <c r="M23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="12"/>
+      <c r="Q23" s="7"/>
       <c r="R23" s="1"/>
-      <c r="S23" s="12"/>
-      <c r="V23" s="18"/>
-      <c r="W23" s="12"/>
+      <c r="S23" s="7"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="7"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="Z23" s="12"/>
-      <c r="AA23" s="12"/>
-      <c r="AB23" s="12"/>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="7"/>
+      <c r="AB23" s="7"/>
       <c r="AE23" s="1"/>
-      <c r="AG23" s="12"/>
+      <c r="AG23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="16"/>
-      <c r="C24" s="23"/>
-      <c r="J24" s="12"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="22"/>
+      <c r="J24" s="7"/>
       <c r="M24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="12"/>
+      <c r="Q24" s="7"/>
       <c r="R24" s="1"/>
-      <c r="S24" s="12"/>
-      <c r="V24" s="18"/>
-      <c r="W24" s="12"/>
+      <c r="S24" s="7"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="7"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="12"/>
-      <c r="AA24" s="12"/>
-      <c r="AB24" s="12"/>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="7"/>
+      <c r="AB24" s="7"/>
       <c r="AE24" s="1"/>
-      <c r="AG24" s="12"/>
+      <c r="AG24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="16"/>
-      <c r="C25" s="23"/>
-      <c r="J25" s="12"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="22"/>
+      <c r="J25" s="7"/>
       <c r="M25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="12"/>
+      <c r="Q25" s="7"/>
       <c r="R25" s="1"/>
-      <c r="S25" s="12"/>
-      <c r="V25" s="18"/>
-      <c r="W25" s="12"/>
+      <c r="S25" s="7"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="7"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="Z25" s="12"/>
-      <c r="AA25" s="12"/>
-      <c r="AB25" s="12"/>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="7"/>
+      <c r="AB25" s="7"/>
       <c r="AE25" s="1"/>
-      <c r="AG25" s="12"/>
+      <c r="AG25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16"/>
-      <c r="C26" s="23"/>
-      <c r="J26" s="12"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="22"/>
+      <c r="J26" s="7"/>
       <c r="M26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="12"/>
+      <c r="Q26" s="7"/>
       <c r="R26" s="1"/>
-      <c r="S26" s="12"/>
-      <c r="V26" s="18"/>
-      <c r="W26" s="12"/>
+      <c r="S26" s="7"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="7"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="Z26" s="12"/>
-      <c r="AA26" s="12"/>
-      <c r="AB26" s="12"/>
+      <c r="Z26" s="7"/>
+      <c r="AA26" s="7"/>
+      <c r="AB26" s="7"/>
       <c r="AE26" s="1"/>
-      <c r="AG26" s="12"/>
+      <c r="AG26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16"/>
-      <c r="C27" s="23"/>
-      <c r="J27" s="12"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="22"/>
+      <c r="J27" s="7"/>
       <c r="M27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="12"/>
+      <c r="Q27" s="7"/>
       <c r="R27" s="1"/>
-      <c r="S27" s="12"/>
-      <c r="V27" s="18"/>
-      <c r="W27" s="12"/>
+      <c r="S27" s="7"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="7"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="12"/>
-      <c r="AA27" s="12"/>
-      <c r="AB27" s="12"/>
+      <c r="Z27" s="7"/>
+      <c r="AA27" s="7"/>
+      <c r="AB27" s="7"/>
       <c r="AE27" s="1"/>
-      <c r="AG27" s="12"/>
+      <c r="AG27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="16"/>
-      <c r="C28" s="23"/>
-      <c r="J28" s="12"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="22"/>
+      <c r="J28" s="7"/>
       <c r="M28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="12"/>
+      <c r="Q28" s="7"/>
       <c r="R28" s="1"/>
-      <c r="S28" s="12"/>
-      <c r="V28" s="18"/>
-      <c r="W28" s="12"/>
+      <c r="S28" s="7"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="7"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="AB28" s="12"/>
-      <c r="AD28" s="12"/>
+      <c r="AB28" s="7"/>
+      <c r="AD28" s="7"/>
       <c r="AE28" s="1"/>
-      <c r="AG28" s="12"/>
+      <c r="AG28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="16"/>
-      <c r="C29" s="23"/>
-      <c r="J29" s="12"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="22"/>
+      <c r="J29" s="7"/>
       <c r="M29" s="1"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="12"/>
+      <c r="Q29" s="7"/>
       <c r="R29" s="1"/>
-      <c r="S29" s="12"/>
-      <c r="V29" s="18"/>
-      <c r="W29" s="12"/>
+      <c r="S29" s="7"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="7"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="12"/>
-      <c r="AB29" s="12"/>
-      <c r="AD29" s="12"/>
+      <c r="Y29" s="7"/>
+      <c r="AB29" s="7"/>
+      <c r="AD29" s="7"/>
       <c r="AE29" s="1"/>
-      <c r="AG29" s="12"/>
+      <c r="AG29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="16"/>
-      <c r="C30" s="12"/>
-      <c r="J30" s="12"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="7"/>
+      <c r="J30" s="7"/>
       <c r="M30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="V30" s="18"/>
+      <c r="V30" s="17"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
@@ -3917,161 +3918,161 @@
       <c r="AL30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="16"/>
-      <c r="C31" s="12"/>
-      <c r="J31" s="12"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="7"/>
+      <c r="J31" s="7"/>
       <c r="M31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="V31" s="18"/>
+      <c r="V31" s="17"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="AA31" s="1"/>
-      <c r="AB31" s="12"/>
+      <c r="AB31" s="7"/>
       <c r="AG31" s="1"/>
       <c r="AL31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="12"/>
-      <c r="J32" s="12"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="7"/>
+      <c r="J32" s="7"/>
       <c r="M32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="V32" s="18"/>
+      <c r="V32" s="17"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-      <c r="Y32" s="12"/>
+      <c r="Y32" s="7"/>
       <c r="AA32" s="1"/>
       <c r="AG32" s="1"/>
       <c r="AL32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="16"/>
-      <c r="C33" s="15"/>
-      <c r="J33" s="12"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="14"/>
+      <c r="J33" s="7"/>
       <c r="M33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="V33" s="18"/>
-      <c r="W33" s="12"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="7"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="AG33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="16"/>
-      <c r="C34" s="15"/>
-      <c r="J34" s="12"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="14"/>
+      <c r="J34" s="7"/>
       <c r="M34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="V34" s="18"/>
-      <c r="W34" s="12"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="7"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="AB34" s="12"/>
+      <c r="AB34" s="7"/>
       <c r="AG34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="16"/>
-      <c r="C35" s="15"/>
-      <c r="J35" s="12"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="14"/>
+      <c r="J35" s="7"/>
       <c r="M35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="V35" s="18"/>
-      <c r="W35" s="12"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="7"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="AD35" s="12"/>
+      <c r="AD35" s="7"/>
       <c r="AG35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="15"/>
-      <c r="J36" s="12"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="14"/>
+      <c r="J36" s="7"/>
       <c r="M36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="V36" s="18"/>
-      <c r="W36" s="12"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="7"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="AG36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="15"/>
-      <c r="J37" s="12"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="14"/>
+      <c r="J37" s="7"/>
       <c r="M37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-      <c r="V37" s="18"/>
-      <c r="W37" s="12"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="7"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
       <c r="AG37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="15"/>
-      <c r="J38" s="12"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="14"/>
+      <c r="J38" s="7"/>
       <c r="M38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-      <c r="V38" s="18"/>
-      <c r="W38" s="12"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="7"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="AB38" s="12"/>
+      <c r="AB38" s="7"/>
       <c r="AG38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="15"/>
-      <c r="J39" s="12"/>
+      <c r="A39" s="13"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="14"/>
+      <c r="J39" s="7"/>
       <c r="M39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
-      <c r="V39" s="18"/>
-      <c r="W39" s="12"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="7"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="AB39" s="12"/>
-      <c r="AD39" s="12"/>
+      <c r="AB39" s="7"/>
+      <c r="AD39" s="7"/>
       <c r="AG39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="16"/>
-      <c r="C40" s="15"/>
-      <c r="J40" s="12"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="14"/>
+      <c r="J40" s="7"/>
       <c r="M40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -4083,190 +4084,190 @@
       <c r="AG40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="16"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="12"/>
-      <c r="J41" s="12"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="7"/>
+      <c r="J41" s="7"/>
       <c r="M41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="W41" s="1"/>
-      <c r="X41" s="12"/>
+      <c r="X41" s="7"/>
       <c r="Y41" s="1"/>
-      <c r="AD41" s="12"/>
+      <c r="AD41" s="7"/>
       <c r="AG41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="16"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="12"/>
-      <c r="J42" s="12"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="7"/>
+      <c r="J42" s="7"/>
       <c r="M42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="W42" s="1"/>
-      <c r="X42" s="12"/>
+      <c r="X42" s="7"/>
       <c r="Y42" s="1"/>
-      <c r="AD42" s="12"/>
+      <c r="AD42" s="7"/>
       <c r="AG42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="16"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="12"/>
-      <c r="J43" s="12"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="7"/>
+      <c r="J43" s="7"/>
       <c r="M43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="W43" s="1"/>
-      <c r="X43" s="12"/>
+      <c r="X43" s="7"/>
       <c r="Y43" s="1"/>
-      <c r="AD43" s="12"/>
+      <c r="AD43" s="7"/>
       <c r="AG43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="16"/>
-      <c r="C44" s="15"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="14"/>
       <c r="J44" s="1"/>
       <c r="M44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
-      <c r="V44" s="18"/>
-      <c r="W44" s="12"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="7"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
-      <c r="Z44" s="12"/>
-      <c r="AA44" s="12"/>
-      <c r="AB44" s="12"/>
+      <c r="Z44" s="7"/>
+      <c r="AA44" s="7"/>
+      <c r="AB44" s="7"/>
       <c r="AG44" s="1"/>
       <c r="AL44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="16"/>
-      <c r="C45" s="15"/>
-      <c r="E45" s="15"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="14"/>
+      <c r="E45" s="14"/>
       <c r="J45" s="1"/>
       <c r="M45" s="1"/>
-      <c r="P45" s="12"/>
+      <c r="P45" s="7"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
-      <c r="U45" s="12"/>
-      <c r="V45" s="12"/>
-      <c r="W45" s="12"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
       <c r="X45" s="1"/>
-      <c r="Y45" s="12"/>
-      <c r="AD45" s="12"/>
+      <c r="Y45" s="7"/>
+      <c r="AD45" s="7"/>
       <c r="AG45" s="1"/>
       <c r="AM45" s="1"/>
       <c r="AN45" s="10"/>
       <c r="AP45" s="1"/>
-      <c r="AQ45" s="12"/>
+      <c r="AQ45" s="7"/>
       <c r="AR45" s="1"/>
       <c r="AT45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="16"/>
-      <c r="C46" s="15"/>
-      <c r="E46" s="15"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="14"/>
+      <c r="E46" s="14"/>
       <c r="J46" s="1"/>
       <c r="M46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-      <c r="V46" s="12"/>
-      <c r="W46" s="12"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
       <c r="X46" s="1"/>
-      <c r="Y46" s="12"/>
+      <c r="Y46" s="7"/>
       <c r="AG46" s="1"/>
       <c r="AM46" s="1"/>
       <c r="AN46" s="10"/>
-      <c r="AP46" s="12"/>
-      <c r="AQ46" s="12"/>
+      <c r="AP46" s="7"/>
+      <c r="AQ46" s="7"/>
       <c r="AR46" s="1"/>
       <c r="AT46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="16"/>
-      <c r="C47" s="15"/>
-      <c r="E47" s="15"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="14"/>
+      <c r="E47" s="14"/>
       <c r="J47" s="1"/>
       <c r="M47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-      <c r="V47" s="12"/>
-      <c r="W47" s="12"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
       <c r="X47" s="1"/>
-      <c r="Y47" s="12"/>
+      <c r="Y47" s="7"/>
       <c r="AG47" s="1"/>
       <c r="AM47" s="1"/>
       <c r="AN47" s="10"/>
-      <c r="AP47" s="12"/>
+      <c r="AP47" s="7"/>
       <c r="AQ47" s="1"/>
       <c r="AR47" s="1"/>
       <c r="AT47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="16"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="14"/>
       <c r="J48" s="1"/>
       <c r="M48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
-      <c r="V48" s="12"/>
-      <c r="W48" s="12"/>
+      <c r="V48" s="7"/>
+      <c r="W48" s="7"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="AB48" s="12"/>
+      <c r="AB48" s="7"/>
       <c r="AG48" s="1"/>
       <c r="AM48" s="1"/>
       <c r="AN48" s="10"/>
-      <c r="AP48" s="12"/>
-      <c r="AQ48" s="12"/>
+      <c r="AP48" s="7"/>
+      <c r="AQ48" s="7"/>
       <c r="AT48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="16"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="14"/>
       <c r="J49" s="1"/>
       <c r="M49" s="1"/>
-      <c r="P49" s="12"/>
+      <c r="P49" s="7"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-      <c r="W49" s="12"/>
-      <c r="X49" s="12"/>
-      <c r="Y49" s="12"/>
-      <c r="AD49" s="12"/>
+      <c r="W49" s="7"/>
+      <c r="X49" s="7"/>
+      <c r="Y49" s="7"/>
+      <c r="AD49" s="7"/>
       <c r="AG49" s="1"/>
       <c r="AM49" s="1"/>
       <c r="AN49" s="10"/>
-      <c r="AP49" s="12"/>
-      <c r="AQ49" s="12"/>
+      <c r="AP49" s="7"/>
+      <c r="AQ49" s="7"/>
       <c r="AR49" s="1"/>
       <c r="AT49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="16"/>
-      <c r="C50" s="15"/>
-      <c r="E50" s="15"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="14"/>
+      <c r="E50" s="14"/>
       <c r="J50" s="1"/>
       <c r="M50" s="1"/>
       <c r="P50" s="1"/>
@@ -4276,20 +4277,20 @@
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="AB50" s="12"/>
+      <c r="AB50" s="7"/>
       <c r="AG50" s="1"/>
       <c r="AM50" s="1"/>
       <c r="AN50" s="10"/>
-      <c r="AP50" s="12"/>
-      <c r="AQ50" s="12"/>
+      <c r="AP50" s="7"/>
+      <c r="AQ50" s="7"/>
       <c r="AR50" s="1"/>
       <c r="AT50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="15"/>
-      <c r="E51" s="15"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="14"/>
+      <c r="E51" s="14"/>
       <c r="J51" s="1"/>
       <c r="M51" s="1"/>
       <c r="P51" s="1"/>
@@ -4300,57 +4301,57 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="AG51" s="1"/>
-      <c r="AM51" s="12"/>
+      <c r="AM51" s="7"/>
       <c r="AN51" s="10"/>
       <c r="AP51" s="1"/>
-      <c r="AQ51" s="12"/>
+      <c r="AQ51" s="7"/>
       <c r="AR51" s="1"/>
-      <c r="AT51" s="12"/>
+      <c r="AT51" s="7"/>
     </row>
     <row r="52" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="12"/>
+      <c r="A52" s="7"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="7"/>
       <c r="J52" s="1"/>
       <c r="M52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-      <c r="W52" s="12"/>
+      <c r="W52" s="7"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="AG52" s="1"/>
-      <c r="AM52" s="12"/>
+      <c r="AM52" s="7"/>
       <c r="AR52" s="1"/>
-      <c r="AT52" s="12"/>
+      <c r="AT52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="16"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="14"/>
       <c r="J53" s="1"/>
       <c r="M53" s="1"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
-      <c r="U53" s="12"/>
-      <c r="V53" s="12"/>
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="AB53" s="12"/>
+      <c r="AB53" s="7"/>
       <c r="AG53" s="1"/>
       <c r="AM53" s="1"/>
       <c r="AT53" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F69" s="12"/>
+      <c r="F69" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4376,133 +4377,133 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
+      <c r="A2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="24" t="s">
         <v>129</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -4510,10 +4511,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27"/>
+      <c r="A5" s="26"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="1"/>
       <c r="D6" s="1"/>
     </row>
@@ -4553,416 +4554,422 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
+      <c r="A2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30" t="s">
+      <c r="C4" s="29"/>
+      <c r="D4" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
+      <c r="A6" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="12"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="12"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -4986,10 +4993,10 @@
       <c r="Y15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -5013,64 +5020,64 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="30"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="12"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -5094,10 +5101,10 @@
       <c r="Y19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -5121,97 +5128,97 @@
       <c r="Y20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="12"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="12"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -5235,10 +5242,10 @@
       <c r="Y25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
+      <c r="A26" s="29"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -5262,145 +5269,145 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="7"/>
+      <c r="Y27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="12"/>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12"/>
-      <c r="Y28" s="12"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="7"/>
+      <c r="Y28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
+      <c r="X30" s="7"/>
+      <c r="Y30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="30"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
-      <c r="W31" s="12"/>
-      <c r="X31" s="12"/>
-      <c r="Y31" s="12"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
       <c r="E32" s="34"/>
       <c r="F32" s="34"/>
       <c r="G32" s="34"/>
@@ -5424,10 +5431,10 @@
       <c r="Y32" s="34"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -5451,10 +5458,10 @@
       <c r="Y33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -5478,10 +5485,10 @@
       <c r="Y34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -5505,10 +5512,10 @@
       <c r="Y35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="30"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -5532,9 +5539,9 @@
       <c r="Y36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
       <c r="D37" s="35"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -5559,201 +5566,201 @@
       <c r="Y37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="30"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
       <c r="D38" s="35"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="30"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
       <c r="D39" s="35"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="30"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
       <c r="D40" s="35"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
       <c r="D41" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
       <c r="D42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
       <c r="D43" s="35"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
       <c r="D44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
       <c r="D45" s="35"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
       <c r="D46" s="35"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
       <c r="D47" s="35"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="30"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
       <c r="D48" s="35"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="30"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
+      <c r="A49" s="29"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
       <c r="D49" s="35"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="30"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
+      <c r="A50" s="29"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
       <c r="D50" s="35"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="30"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
       <c r="D51" s="35"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="30"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
       <c r="D52" s="35"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
       <c r="D53" s="35"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="30"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
       <c r="D54" s="35"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
       <c r="D55" s="35"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
+      <c r="A56" s="29"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
       <c r="D56" s="35"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="35"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="30"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
       <c r="D58" s="35"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
+      <c r="A59" s="29"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
       <c r="D59" s="35"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="30"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
+      <c r="A60" s="29"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
       <c r="D60" s="35"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
       <c r="D61" s="35"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="30"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
+      <c r="A62" s="29"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
       <c r="D62" s="35"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="30"/>
+      <c r="A63" s="29"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="35"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="30"/>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
       <c r="D64" s="35"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="30"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="30"/>
+      <c r="A65" s="29"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
       <c r="D65" s="35"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="30"/>
-      <c r="B66" s="30"/>
-      <c r="C66" s="30"/>
+      <c r="A66" s="29"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
       <c r="D66" s="35"/>
     </row>
     <row r="67" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="14"/>
+      <c r="A67" s="13"/>
       <c r="B67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="14"/>
+      <c r="A68" s="13"/>
       <c r="B68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="14"/>
+      <c r="A69" s="13"/>
       <c r="B69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="14"/>
+      <c r="A70" s="13"/>
       <c r="B70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="14"/>
+      <c r="A71" s="13"/>
       <c r="B71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="14"/>
+      <c r="A72" s="13"/>
       <c r="B72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5769,7 +5776,7 @@
       <c r="B76" s="1"/>
     </row>
     <row r="77" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="14"/>
+      <c r="A77" s="13"/>
       <c r="B77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5777,23 +5784,23 @@
       <c r="B78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="14"/>
+      <c r="A79" s="13"/>
       <c r="B79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="14"/>
+      <c r="A80" s="13"/>
       <c r="B80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="14"/>
+      <c r="A81" s="13"/>
       <c r="B81" s="1"/>
     </row>
     <row r="82" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="14"/>
+      <c r="A82" s="13"/>
       <c r="B82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="14"/>
+      <c r="A83" s="13"/>
       <c r="B83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
+++ b/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Thing" sheetId="1" state="visible" r:id="rId2"/>
@@ -415,7 +415,7 @@
     <t xml:space="preserve">Good</t>
   </si>
   <si>
-    <t xml:space="preserve">#1 the #2 has evolved into #3!</t>
+    <t xml:space="preserve">#1 has evolved into #2!</t>
   </si>
   <si>
     <t xml:space="preserve">evolutionConfirmation</t>
@@ -430,7 +430,7 @@
     <t xml:space="preserve">evolveChara</t>
   </si>
   <si>
-    <t xml:space="preserve">Evolve into #1.</t>
+    <t xml:space="preserve">Evolve into #1</t>
   </si>
   <si>
     <t xml:space="preserve">evolutionAffinityRequirementNotMet</t>
@@ -448,7 +448,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -580,12 +580,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC9A26D"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color rgb="FFC9A26D"/>
       <name val="Arial"/>
@@ -653,7 +647,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -782,10 +776,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -798,7 +788,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4717,7 +4707,7 @@
       <c r="Y5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="30" t="s">
         <v>136</v>
       </c>
       <c r="B6" s="31" t="s">
@@ -4750,7 +4740,7 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="31"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
@@ -5408,27 +5398,27 @@
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
       <c r="D32" s="29"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="34"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="34"/>
-      <c r="V32" s="34"/>
-      <c r="W32" s="34"/>
-      <c r="X32" s="34"/>
-      <c r="Y32" s="34"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="33"/>
+      <c r="S32" s="33"/>
+      <c r="T32" s="33"/>
+      <c r="U32" s="33"/>
+      <c r="V32" s="33"/>
+      <c r="W32" s="33"/>
+      <c r="X32" s="33"/>
+      <c r="Y32" s="33"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29"/>
@@ -5542,7 +5532,7 @@
       <c r="A37" s="29"/>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
-      <c r="D37" s="35"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -5569,175 +5559,175 @@
       <c r="A38" s="29"/>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>
-      <c r="D38" s="35"/>
+      <c r="D38" s="34"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29"/>
       <c r="B39" s="29"/>
       <c r="C39" s="29"/>
-      <c r="D39" s="35"/>
+      <c r="D39" s="34"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="29"/>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
-      <c r="D40" s="35"/>
+      <c r="D40" s="34"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="29"/>
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
-      <c r="D41" s="35"/>
+      <c r="D41" s="34"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="29"/>
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
-      <c r="D42" s="35"/>
+      <c r="D42" s="34"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="29"/>
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
-      <c r="D43" s="35"/>
+      <c r="D43" s="34"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="29"/>
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
-      <c r="D44" s="35"/>
+      <c r="D44" s="34"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="29"/>
       <c r="B45" s="29"/>
       <c r="C45" s="29"/>
-      <c r="D45" s="35"/>
+      <c r="D45" s="34"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="29"/>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
-      <c r="D46" s="35"/>
+      <c r="D46" s="34"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="29"/>
       <c r="B47" s="29"/>
       <c r="C47" s="29"/>
-      <c r="D47" s="35"/>
+      <c r="D47" s="34"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="29"/>
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
-      <c r="D48" s="35"/>
+      <c r="D48" s="34"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="29"/>
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
-      <c r="D49" s="35"/>
+      <c r="D49" s="34"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="29"/>
       <c r="B50" s="29"/>
       <c r="C50" s="29"/>
-      <c r="D50" s="35"/>
+      <c r="D50" s="34"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="29"/>
       <c r="B51" s="29"/>
       <c r="C51" s="29"/>
-      <c r="D51" s="35"/>
+      <c r="D51" s="34"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="29"/>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
-      <c r="D52" s="35"/>
+      <c r="D52" s="34"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="29"/>
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
-      <c r="D53" s="35"/>
+      <c r="D53" s="34"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="29"/>
       <c r="B54" s="29"/>
       <c r="C54" s="29"/>
-      <c r="D54" s="35"/>
+      <c r="D54" s="34"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="29"/>
       <c r="B55" s="29"/>
       <c r="C55" s="29"/>
-      <c r="D55" s="35"/>
+      <c r="D55" s="34"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="29"/>
       <c r="B56" s="29"/>
       <c r="C56" s="29"/>
-      <c r="D56" s="35"/>
+      <c r="D56" s="34"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="29"/>
       <c r="B57" s="29"/>
       <c r="C57" s="29"/>
-      <c r="D57" s="35"/>
+      <c r="D57" s="34"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="29"/>
       <c r="B58" s="29"/>
       <c r="C58" s="29"/>
-      <c r="D58" s="35"/>
+      <c r="D58" s="34"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="29"/>
       <c r="B59" s="29"/>
       <c r="C59" s="29"/>
-      <c r="D59" s="35"/>
+      <c r="D59" s="34"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="29"/>
       <c r="B60" s="29"/>
       <c r="C60" s="29"/>
-      <c r="D60" s="35"/>
+      <c r="D60" s="34"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="29"/>
       <c r="B61" s="29"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="35"/>
+      <c r="D61" s="34"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="29"/>
       <c r="B62" s="29"/>
       <c r="C62" s="29"/>
-      <c r="D62" s="35"/>
+      <c r="D62" s="34"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="29"/>
       <c r="B63" s="29"/>
       <c r="C63" s="29"/>
-      <c r="D63" s="35"/>
+      <c r="D63" s="34"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="29"/>
       <c r="B64" s="29"/>
       <c r="C64" s="29"/>
-      <c r="D64" s="35"/>
+      <c r="D64" s="34"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="29"/>
       <c r="B65" s="29"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="35"/>
+      <c r="D65" s="34"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="29"/>
       <c r="B66" s="29"/>
       <c r="C66" s="29"/>
-      <c r="D66" s="35"/>
+      <c r="D66" s="34"/>
     </row>
     <row r="67" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13"/>
@@ -5780,7 +5770,7 @@
       <c r="B77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="36"/>
+      <c r="A78" s="35"/>
       <c r="B78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
+++ b/EvolutionPOC/LangMod/EN/SourceSheet.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="143">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -340,6 +340,9 @@
     <t xml:space="preserve">testchara_evo_stage1</t>
   </si>
   <si>
+    <t xml:space="preserve">*r</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dragon Miko</t>
   </si>
   <si>
@@ -376,7 +379,7 @@
     <t xml:space="preserve">Awakened Dragon Miko</t>
   </si>
   <si>
-    <t xml:space="preserve">evolve#testchara_evo_stage3#evolution_heart_b</t>
+    <t xml:space="preserve">evolve#testchara_evo_stage3#evolution_heart_b,noEgg</t>
   </si>
   <si>
     <t xml:space="preserve">testchara_evo_stage3</t>
@@ -385,6 +388,9 @@
     <t xml:space="preserve">Water Goddess</t>
   </si>
   <si>
+    <t xml:space="preserve">noEgg</t>
+  </si>
+  <si>
     <t xml:space="preserve">group</t>
   </si>
   <si>
@@ -415,7 +421,16 @@
     <t xml:space="preserve">Good</t>
   </si>
   <si>
-    <t xml:space="preserve">#1 has evolved into #2!</t>
+    <t xml:space="preserve">#1 the #2 has evolved into #3!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noEgg_Tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This character cannot produce eggs.</t>
   </si>
   <si>
     <t xml:space="preserve">evolutionConfirmation</t>
@@ -430,7 +445,7 @@
     <t xml:space="preserve">evolveChara</t>
   </si>
   <si>
-    <t xml:space="preserve">Evolve into #1</t>
+    <t xml:space="preserve">Evolve into #1.</t>
   </si>
   <si>
     <t xml:space="preserve">evolutionAffinityRequirementNotMet</t>
@@ -448,7 +463,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -527,6 +542,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FFD0D0D0"/>
       <name val="JetBrains Mono"/>
       <family val="3"/>
@@ -572,6 +592,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC9A26D"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="10"/>
@@ -647,7 +673,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -736,31 +762,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -768,11 +802,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -788,7 +822,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3144,16 +3178,18 @@
         <v>7869001</v>
       </c>
       <c r="C4" s="14"/>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>105</v>
       </c>
       <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="F4" s="7" t="s">
+        <v>106</v>
+      </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -3162,7 +3198,7 @@
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P4" s="7" t="n">
         <v>10</v>
@@ -3174,29 +3210,29 @@
         <v>4</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T4" s="7"/>
       <c r="U4" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="X4" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y4" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD4" s="7"/>
       <c r="AE4" s="7" t="s">
@@ -3225,22 +3261,24 @@
     </row>
     <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>7869002</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="7" t="s">
-        <v>116</v>
+      <c r="D5" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="E5" s="14"/>
-      <c r="F5" s="7"/>
+      <c r="F5" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
@@ -3249,7 +3287,7 @@
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P5" s="7" t="n">
         <v>20</v>
@@ -3261,29 +3299,29 @@
         <v>4</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T5" s="7"/>
       <c r="U5" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD5" s="7"/>
       <c r="AE5" s="7" t="s">
@@ -3312,22 +3350,24 @@
     </row>
     <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>7869003</v>
       </c>
       <c r="C6" s="14"/>
-      <c r="D6" s="7" t="s">
-        <v>119</v>
+      <c r="D6" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="F6" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
@@ -3336,7 +3376,7 @@
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P6" s="7" t="n">
         <v>30</v>
@@ -3348,27 +3388,29 @@
         <v>4</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
+      <c r="U6" s="18" t="s">
+        <v>121</v>
+      </c>
       <c r="V6" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="X6" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD6" s="7"/>
       <c r="AE6" s="7" t="s">
@@ -3406,7 +3448,7 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
-      <c r="V7" s="18"/>
+      <c r="V7" s="19"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="7"/>
@@ -3420,9 +3462,9 @@
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
       <c r="B8" s="15"/>
-      <c r="C8" s="19"/>
+      <c r="C8" s="20"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="20"/>
+      <c r="E8" s="21"/>
       <c r="F8" s="7"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -3438,7 +3480,7 @@
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="1"/>
-      <c r="V8" s="18"/>
+      <c r="V8" s="19"/>
       <c r="W8" s="1"/>
       <c r="X8" s="13"/>
       <c r="Y8" s="7"/>
@@ -3476,7 +3518,7 @@
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
-      <c r="V9" s="18"/>
+      <c r="V9" s="19"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
@@ -3496,7 +3538,7 @@
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
-      <c r="V10" s="18"/>
+      <c r="V10" s="19"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
@@ -3516,7 +3558,7 @@
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
-      <c r="V11" s="18"/>
+      <c r="V11" s="19"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
@@ -3536,7 +3578,7 @@
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
-      <c r="V12" s="18"/>
+      <c r="V12" s="19"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
@@ -3580,7 +3622,7 @@
       <c r="R14" s="1"/>
       <c r="S14" s="7"/>
       <c r="W14" s="1"/>
-      <c r="X14" s="21"/>
+      <c r="X14" s="22"/>
       <c r="Y14" s="7"/>
       <c r="Z14" s="1"/>
       <c r="AB14" s="7"/>
@@ -3702,7 +3744,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="15"/>
-      <c r="C20" s="22"/>
+      <c r="C20" s="23"/>
       <c r="D20" s="7"/>
       <c r="J20" s="7"/>
       <c r="M20" s="1"/>
@@ -3723,7 +3765,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="15"/>
-      <c r="C21" s="22"/>
+      <c r="C21" s="23"/>
       <c r="J21" s="7"/>
       <c r="M21" s="1"/>
       <c r="P21" s="1"/>
@@ -3741,7 +3783,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="15"/>
-      <c r="C22" s="22"/>
+      <c r="C22" s="23"/>
       <c r="J22" s="7"/>
       <c r="M22" s="1"/>
       <c r="P22" s="1"/>
@@ -3760,7 +3802,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="15"/>
-      <c r="C23" s="22"/>
+      <c r="C23" s="23"/>
       <c r="J23" s="7"/>
       <c r="M23" s="1"/>
       <c r="P23" s="1"/>
@@ -3779,7 +3821,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="15"/>
-      <c r="C24" s="22"/>
+      <c r="C24" s="23"/>
       <c r="J24" s="7"/>
       <c r="M24" s="1"/>
       <c r="P24" s="1"/>
@@ -3798,7 +3840,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="15"/>
-      <c r="C25" s="22"/>
+      <c r="C25" s="23"/>
       <c r="J25" s="7"/>
       <c r="M25" s="1"/>
       <c r="P25" s="1"/>
@@ -3817,7 +3859,7 @@
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="15"/>
-      <c r="C26" s="22"/>
+      <c r="C26" s="23"/>
       <c r="J26" s="7"/>
       <c r="M26" s="1"/>
       <c r="P26" s="1"/>
@@ -3836,7 +3878,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="15"/>
-      <c r="C27" s="22"/>
+      <c r="C27" s="23"/>
       <c r="J27" s="7"/>
       <c r="M27" s="1"/>
       <c r="P27" s="1"/>
@@ -3855,7 +3897,7 @@
     </row>
     <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="15"/>
-      <c r="C28" s="22"/>
+      <c r="C28" s="23"/>
       <c r="J28" s="7"/>
       <c r="M28" s="1"/>
       <c r="P28" s="1"/>
@@ -3873,7 +3915,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="15"/>
-      <c r="C29" s="22"/>
+      <c r="C29" s="23"/>
       <c r="J29" s="7"/>
       <c r="M29" s="1"/>
       <c r="P29" s="1"/>
@@ -3927,7 +3969,7 @@
       <c r="AL31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="15"/>
       <c r="C32" s="7"/>
       <c r="J32" s="7"/>
@@ -4367,96 +4409,96 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="G1" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
+      <c r="H1" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
+      <c r="A2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7"/>
@@ -4468,43 +4510,51 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" s="24" t="s">
         <v>129</v>
       </c>
+      <c r="D4" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>131</v>
+      </c>
       <c r="I4" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="1"/>
       <c r="D6" s="1"/>
     </row>
@@ -4544,112 +4594,112 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D1" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
+      <c r="C1" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
+      <c r="A2" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29" t="s">
-        <v>133</v>
+      <c r="A4" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31" t="s">
+        <v>138</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -4674,15 +4724,15 @@
       <c r="Y4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31" t="s">
-        <v>135</v>
+      <c r="A5" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33" t="s">
+        <v>140</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -4707,15 +4757,15 @@
       <c r="Y5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31" t="s">
+      <c r="A6" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="33" t="s">
         <v>137</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33" t="s">
+        <v>142</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
@@ -4740,10 +4790,10 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -4767,10 +4817,10 @@
       <c r="Y7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="29"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
@@ -4794,10 +4844,10 @@
       <c r="Y8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -4821,10 +4871,10 @@
       <c r="Y9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -4848,10 +4898,10 @@
       <c r="Y10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -4875,10 +4925,10 @@
       <c r="Y11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -4902,10 +4952,10 @@
       <c r="Y12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -4929,10 +4979,10 @@
       <c r="Y13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -4956,10 +5006,10 @@
       <c r="Y14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -4983,10 +5033,10 @@
       <c r="Y15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -5010,10 +5060,10 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
@@ -5037,10 +5087,10 @@
       <c r="Y17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -5064,10 +5114,10 @@
       <c r="Y18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -5091,10 +5141,10 @@
       <c r="Y19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -5118,16 +5168,16 @@
       <c r="Y20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -5151,10 +5201,10 @@
       <c r="Y22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
+      <c r="A23" s="31"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
@@ -5178,10 +5228,10 @@
       <c r="Y23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
+      <c r="A24" s="31"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -5205,10 +5255,10 @@
       <c r="Y24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
+      <c r="A25" s="31"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -5232,10 +5282,10 @@
       <c r="Y25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="29"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
+      <c r="A26" s="31"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -5259,10 +5309,10 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -5286,10 +5336,10 @@
       <c r="Y27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
+      <c r="A28" s="31"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -5313,10 +5363,10 @@
       <c r="Y28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
+      <c r="A29" s="31"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -5340,10 +5390,10 @@
       <c r="Y29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
@@ -5367,10 +5417,10 @@
       <c r="Y30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
+      <c r="A31" s="31"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
@@ -5394,37 +5444,37 @@
       <c r="Y31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="29"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="33"/>
-      <c r="R32" s="33"/>
-      <c r="S32" s="33"/>
-      <c r="T32" s="33"/>
-      <c r="U32" s="33"/>
-      <c r="V32" s="33"/>
-      <c r="W32" s="33"/>
-      <c r="X32" s="33"/>
-      <c r="Y32" s="33"/>
+      <c r="A32" s="31"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
+      <c r="T32" s="35"/>
+      <c r="U32" s="35"/>
+      <c r="V32" s="35"/>
+      <c r="W32" s="35"/>
+      <c r="X32" s="35"/>
+      <c r="Y32" s="35"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
+      <c r="A33" s="31"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -5448,10 +5498,10 @@
       <c r="Y33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="29"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
+      <c r="A34" s="31"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -5475,10 +5525,10 @@
       <c r="Y34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
+      <c r="A35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -5502,10 +5552,10 @@
       <c r="Y35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="29"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
+      <c r="A36" s="31"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -5529,10 +5579,10 @@
       <c r="Y36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="29"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="34"/>
+      <c r="A37" s="31"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="36"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -5556,178 +5606,178 @@
       <c r="Y37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="29"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="34"/>
+      <c r="A38" s="31"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="36"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="29"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="34"/>
+      <c r="A39" s="31"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="36"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="29"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="34"/>
+      <c r="A40" s="31"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="36"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="29"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="34"/>
+      <c r="A41" s="31"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="36"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="29"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="34"/>
+      <c r="A42" s="31"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="36"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="29"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="34"/>
+      <c r="A43" s="31"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="36"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="29"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="34"/>
+      <c r="A44" s="31"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="36"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="29"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="34"/>
+      <c r="A45" s="31"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="36"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="29"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="34"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="36"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="29"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="34"/>
+      <c r="A47" s="31"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="36"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="29"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="34"/>
+      <c r="A48" s="31"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="36"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="29"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="34"/>
+      <c r="A49" s="31"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="36"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="29"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="34"/>
+      <c r="A50" s="31"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="36"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="29"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="34"/>
+      <c r="A51" s="31"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="36"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="29"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="34"/>
+      <c r="A52" s="31"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="36"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="34"/>
+      <c r="A53" s="31"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="36"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="34"/>
+      <c r="A54" s="31"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="36"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="29"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="34"/>
+      <c r="A55" s="31"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="36"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="29"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="34"/>
+      <c r="A56" s="31"/>
+      <c r="B56" s="31"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="36"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="34"/>
+      <c r="A57" s="31"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="36"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="29"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="34"/>
+      <c r="A58" s="31"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="36"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="29"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="34"/>
+      <c r="A59" s="31"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="36"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="29"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="34"/>
+      <c r="A60" s="31"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="36"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="29"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="34"/>
+      <c r="A61" s="31"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="36"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="29"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="34"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="36"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="29"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="34"/>
+      <c r="A63" s="31"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="36"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="29"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="34"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="36"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="29"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="34"/>
+      <c r="A65" s="31"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="36"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="29"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="34"/>
+      <c r="A66" s="31"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="36"/>
     </row>
     <row r="67" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13"/>
@@ -5770,7 +5820,7 @@
       <c r="B77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="35"/>
+      <c r="A78" s="37"/>
       <c r="B78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
